--- a/data_u1/LSR3_H_2025-01-16.xlsx
+++ b/data_u1/LSR3_H_2025-01-16.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10402"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sksiafis/Desktop/LSR3_taar1_H_2025.04.01/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sksiafis/Documents/GitHub/LSR3_taar1_H/data_u1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28FF52DE-2EE7-E549-8193-48B166C5B601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35B00FF1-2DC1-4B4D-933A-2292B07EF117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19560" yWindow="-17600" windowWidth="30180" windowHeight="17720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
     <author>tc={63125C18-1CF7-5340-80AF-3F079B6ADA33}</author>
   </authors>
   <commentList>
-    <comment ref="AV4" authorId="0" shapeId="0" xr:uid="{F49B5693-3906-8543-B427-4EC42AF420FE}">
+    <comment ref="AZ4" authorId="0" shapeId="0" xr:uid="{F49B5693-3906-8543-B427-4EC42AF420FE}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -46,7 +46,7 @@
     Changed from first version because BNSS total has been recently been show that has a better validity compared to PANSS negative (Weigel et al)</t>
       </text>
     </comment>
-    <comment ref="N29" authorId="1" shapeId="0" xr:uid="{63125C18-1CF7-5340-80AF-3F079B6ADA33}">
+    <comment ref="Q29" authorId="1" shapeId="0" xr:uid="{63125C18-1CF7-5340-80AF-3F079B6ADA33}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1097" uniqueCount="283">
   <si>
     <t>arm_name</t>
   </si>
@@ -869,13 +869,52 @@
   </si>
   <si>
     <t>Schizophrenia spectrum (clinically stable, MetS)</t>
+  </si>
+  <si>
+    <t>study_year</t>
+  </si>
+  <si>
+    <t>study_doi</t>
+  </si>
+  <si>
+    <t>10.1212/CPJ.0000000000200175</t>
+  </si>
+  <si>
+    <t>https://dx.doi.org/10.1016/j.sleep.2023.04.019</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1038/s41398-021-01331-9</t>
+  </si>
+  <si>
+    <t>overall_baseline_n</t>
+  </si>
+  <si>
+    <t>depression_baseline_n</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1056/nejmoa1911772</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1038/s41537-023-00385-6</t>
+  </si>
+  <si>
+    <t>https://dx.doi.org/10.1111/cts.13512</t>
+  </si>
+  <si>
+    <t>https://dx.doi.org/10.1111/dom.15569</t>
+  </si>
+  <si>
+    <t>duration_unit</t>
+  </si>
+  <si>
+    <t>weeks</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -904,8 +943,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -960,6 +1007,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -970,10 +1023,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -993,8 +1047,14 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1303,10 +1363,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="AV4" dT="2025-01-16T13:52:36.05" personId="{9C02175C-AB95-C54D-8A67-708063150B15}" id="{F49B5693-3906-8543-B427-4EC42AF420FE}">
+  <threadedComment ref="AZ4" dT="2025-01-16T13:52:36.05" personId="{9C02175C-AB95-C54D-8A67-708063150B15}" id="{F49B5693-3906-8543-B427-4EC42AF420FE}">
     <text>Changed from first version because BNSS total has been recently been show that has a better validity compared to PANSS negative (Weigel et al)</text>
   </threadedComment>
-  <threadedComment ref="N29" dT="2025-01-16T13:52:04.57" personId="{9C02175C-AB95-C54D-8A67-708063150B15}" id="{63125C18-1CF7-5340-80AF-3F079B6ADA33}">
+  <threadedComment ref="Q29" dT="2025-01-16T13:52:04.57" personId="{9C02175C-AB95-C54D-8A67-708063150B15}" id="{63125C18-1CF7-5340-80AF-3F079B6ADA33}">
     <text>Imputed from panss total</text>
   </threadedComment>
 </ThreadedComments>
@@ -1314,481 +1374,501 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DY36"/>
+  <dimension ref="A1:ED36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.6640625" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="34" max="34" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" customWidth="1"/>
+    <col min="3" max="4" width="17.6640625" style="16" customWidth="1"/>
+    <col min="6" max="6" width="21.6640625" customWidth="1"/>
+    <col min="16" max="16" width="8.83203125" style="16"/>
+    <col min="37" max="37" width="8.83203125" style="16"/>
+    <col min="38" max="38" width="12.83203125" customWidth="1"/>
+    <col min="78" max="78" width="8.83203125" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:129" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:134" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AK1" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="AL1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BE1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BF1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BG1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BH1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BI1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BJ1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BK1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BL1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BM1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BN1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BO1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BP1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BQ1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BR1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BS1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BT1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BU1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BV1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BW1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BX1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BY1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BZ1" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="CA1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="CB1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="CC1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="CD1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="CE1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CF1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CG1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CH1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CI1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CJ1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="CK1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CL1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="CH1" s="1" t="s">
+      <c r="CM1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CN1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="CJ1" s="1" t="s">
+      <c r="CO1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="CK1" s="1" t="s">
+      <c r="CP1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="CL1" s="1" t="s">
+      <c r="CQ1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="CM1" s="1" t="s">
+      <c r="CR1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="CN1" s="1" t="s">
+      <c r="CS1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="CO1" s="1" t="s">
+      <c r="CT1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="CP1" s="1" t="s">
+      <c r="CU1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="CQ1" s="1" t="s">
+      <c r="CV1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="CR1" s="1" t="s">
+      <c r="CW1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="CS1" s="1" t="s">
+      <c r="CX1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="CT1" s="1" t="s">
+      <c r="CY1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="CU1" s="7" t="s">
+      <c r="CZ1" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="CV1" s="7" t="s">
+      <c r="DA1" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="CW1" s="1" t="s">
+      <c r="DB1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="CX1" s="1" t="s">
+      <c r="DC1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="CY1" s="1" t="s">
+      <c r="DD1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="CZ1" s="1" t="s">
+      <c r="DE1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="DA1" s="1" t="s">
+      <c r="DF1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="DB1" s="1" t="s">
+      <c r="DG1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="DC1" s="1" t="s">
+      <c r="DH1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="DD1" s="1" t="s">
+      <c r="DI1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="DE1" s="1" t="s">
+      <c r="DJ1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="DF1" s="1" t="s">
+      <c r="DK1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="DG1" s="1" t="s">
+      <c r="DL1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="DH1" s="1" t="s">
+      <c r="DM1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="DI1" s="1" t="s">
+      <c r="DN1" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="DJ1" s="1" t="s">
+      <c r="DO1" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="DK1" s="1" t="s">
+      <c r="DP1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="DL1" s="1" t="s">
+      <c r="DQ1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="DM1" s="1" t="s">
+      <c r="DR1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="DN1" s="1" t="s">
+      <c r="DS1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="DO1" s="1" t="s">
+      <c r="DT1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="DP1" s="1" t="s">
+      <c r="DU1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="DQ1" s="1" t="s">
+      <c r="DV1" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="DR1" s="1" t="s">
+      <c r="DW1" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="DS1" s="1" t="s">
+      <c r="DX1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="DT1" s="1" t="s">
+      <c r="DY1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="DU1" s="1" t="s">
+      <c r="DZ1" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="DV1" s="1" t="s">
+      <c r="EA1" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="DW1" s="1" t="s">
+      <c r="EB1" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="DX1" s="1" t="s">
+      <c r="EC1" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="DY1" s="1" t="s">
+      <c r="ED1" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:129" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:134" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>127</v>
       </c>
       <c r="B2" t="s">
         <v>143</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="E2">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>144</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>127</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>145</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>146</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>147</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>148</v>
       </c>
-      <c r="J2">
+      <c r="L2">
         <v>25</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>149</v>
       </c>
-      <c r="L2">
+      <c r="N2">
         <v>4</v>
       </c>
-      <c r="M2">
+      <c r="O2">
         <v>6</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q2" t="s">
         <v>150</v>
       </c>
-      <c r="O2" t="s">
+      <c r="R2" t="s">
         <v>151</v>
       </c>
-      <c r="R2" t="s">
+      <c r="U2" t="s">
         <v>152</v>
       </c>
-      <c r="S2" t="s">
+      <c r="V2" t="s">
         <v>141</v>
       </c>
-      <c r="T2" t="s">
+      <c r="W2" t="s">
         <v>153</v>
       </c>
-      <c r="U2" t="s">
+      <c r="X2" t="s">
         <v>141</v>
       </c>
-      <c r="V2" t="s">
+      <c r="Y2" t="s">
         <v>128</v>
       </c>
-      <c r="W2" t="s">
+      <c r="Z2" t="s">
         <v>141</v>
       </c>
-      <c r="X2" t="s">
+      <c r="AA2" t="s">
         <v>154</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AB2" t="s">
         <v>141</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>155</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>156</v>
       </c>
       <c r="AC2" t="s">
         <v>155</v>
@@ -1800,199 +1880,208 @@
         <v>156</v>
       </c>
       <c r="AF2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>156</v>
+      </c>
+      <c r="AI2" t="s">
         <v>158</v>
       </c>
-      <c r="AG2">
+      <c r="AJ2">
         <v>23</v>
       </c>
-      <c r="AI2">
+      <c r="AM2">
         <v>-11.5</v>
       </c>
-      <c r="AJ2">
+      <c r="AN2">
         <v>20.12</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AO2" t="s">
         <v>130</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AP2" t="s">
         <v>131</v>
       </c>
-      <c r="AM2" t="s">
-        <v>132</v>
-      </c>
-      <c r="AN2" t="s">
+      <c r="AQ2" t="s">
+        <v>132</v>
+      </c>
+      <c r="AR2" t="s">
         <v>159</v>
       </c>
-      <c r="AO2">
+      <c r="AS2">
         <v>24</v>
       </c>
-      <c r="AP2">
+      <c r="AT2">
         <v>13.1</v>
       </c>
-      <c r="AQ2">
+      <c r="AU2">
         <v>-2.5</v>
       </c>
-      <c r="AR2">
+      <c r="AV2">
         <v>7.94</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AW2" t="s">
         <v>130</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AX2" t="s">
         <v>131</v>
       </c>
-      <c r="AU2" t="s">
-        <v>132</v>
-      </c>
-      <c r="BL2" t="s">
+      <c r="AY2" t="s">
+        <v>132</v>
+      </c>
+      <c r="BP2" t="s">
         <v>160</v>
       </c>
-      <c r="BM2">
+      <c r="BQ2">
         <v>23</v>
       </c>
-      <c r="BN2">
+      <c r="BR2">
         <v>-25.1</v>
       </c>
-      <c r="BO2">
+      <c r="BS2">
         <v>0.8</v>
       </c>
-      <c r="BP2">
+      <c r="BT2">
         <v>2.2000000000000002</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BU2" t="s">
         <v>130</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BV2" t="s">
         <v>131</v>
       </c>
-      <c r="BS2" t="s">
-        <v>132</v>
-      </c>
-      <c r="CS2">
+      <c r="BW2" t="s">
+        <v>132</v>
+      </c>
+      <c r="CX2">
         <v>18</v>
       </c>
-      <c r="CT2">
+      <c r="CY2">
         <v>25</v>
       </c>
-      <c r="CW2" s="9"/>
-      <c r="CX2" s="9"/>
-      <c r="CY2">
+      <c r="DB2" s="9"/>
+      <c r="DC2" s="9"/>
+      <c r="DD2">
         <v>4</v>
       </c>
-      <c r="CZ2">
+      <c r="DE2">
         <v>25</v>
       </c>
-      <c r="DC2">
+      <c r="DH2">
         <v>3</v>
       </c>
-      <c r="DD2">
+      <c r="DI2">
         <v>25</v>
       </c>
-      <c r="DE2">
+      <c r="DJ2">
         <v>2</v>
       </c>
-      <c r="DF2">
+      <c r="DK2">
         <v>25</v>
       </c>
-      <c r="DK2" s="9"/>
-      <c r="DL2" s="9"/>
-      <c r="DM2">
+      <c r="DP2" s="9"/>
+      <c r="DQ2" s="9"/>
+      <c r="DR2">
         <v>13</v>
       </c>
-      <c r="DN2">
+      <c r="DS2">
         <v>25</v>
       </c>
-      <c r="DO2" s="8">
+      <c r="DT2" s="8">
         <v>2</v>
       </c>
-      <c r="DW2" t="s">
+      <c r="EB2" t="s">
         <v>138</v>
       </c>
-      <c r="DX2" t="s">
+      <c r="EC2" t="s">
         <v>161</v>
       </c>
-      <c r="DY2" t="s">
+      <c r="ED2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="3" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>162</v>
       </c>
       <c r="B3" t="s">
         <v>143</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="E3">
         <v>1</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>144</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>162</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>128</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
         <v>146</v>
       </c>
-      <c r="H3" t="s">
+      <c r="J3" t="s">
         <v>147</v>
       </c>
-      <c r="I3" t="s">
+      <c r="K3" t="s">
         <v>148</v>
       </c>
-      <c r="J3">
+      <c r="L3">
         <v>14</v>
       </c>
-      <c r="K3" t="s">
+      <c r="M3" t="s">
         <v>149</v>
       </c>
-      <c r="L3">
+      <c r="N3">
         <v>1</v>
       </c>
-      <c r="M3">
+      <c r="O3">
         <v>6</v>
       </c>
-      <c r="N3" t="s">
+      <c r="P3" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q3" t="s">
         <v>163</v>
       </c>
-      <c r="O3" t="s">
+      <c r="R3" t="s">
         <v>142</v>
       </c>
-      <c r="R3" t="s">
+      <c r="U3" t="s">
         <v>163</v>
       </c>
-      <c r="S3" t="s">
+      <c r="V3" t="s">
         <v>164</v>
       </c>
-      <c r="T3" t="s">
+      <c r="W3" t="s">
         <v>165</v>
       </c>
-      <c r="U3" t="s">
+      <c r="X3" t="s">
         <v>164</v>
       </c>
-      <c r="V3" t="s">
+      <c r="Y3" t="s">
         <v>128</v>
       </c>
-      <c r="W3" t="s">
+      <c r="Z3" t="s">
         <v>164</v>
       </c>
-      <c r="X3" t="s">
+      <c r="AA3" t="s">
         <v>128</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="AB3" t="s">
         <v>164</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>155</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>156</v>
       </c>
       <c r="AC3" t="s">
         <v>155</v>
@@ -2004,3400 +2093,3637 @@
         <v>156</v>
       </c>
       <c r="AF3" t="s">
+        <v>155</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>155</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>156</v>
+      </c>
+      <c r="AI3" t="s">
         <v>158</v>
       </c>
-      <c r="AG3">
+      <c r="AJ3">
         <v>14</v>
       </c>
-      <c r="AI3">
+      <c r="AM3">
         <v>-17.3</v>
       </c>
-      <c r="AJ3">
+      <c r="AN3">
         <v>19.57</v>
       </c>
-      <c r="AK3" t="s">
+      <c r="AO3" t="s">
         <v>130</v>
       </c>
-      <c r="AL3" t="s">
+      <c r="AP3" t="s">
         <v>131</v>
       </c>
-      <c r="AM3" t="s">
-        <v>132</v>
-      </c>
-      <c r="AN3" t="s">
+      <c r="AQ3" t="s">
+        <v>132</v>
+      </c>
+      <c r="AR3" t="s">
         <v>159</v>
       </c>
-      <c r="AO3">
+      <c r="AS3">
         <v>14</v>
       </c>
-      <c r="AP3">
+      <c r="AT3">
         <v>14.7</v>
       </c>
-      <c r="AQ3">
+      <c r="AU3">
         <v>-1.4</v>
       </c>
-      <c r="AR3">
+      <c r="AV3">
         <v>7.71</v>
       </c>
-      <c r="AS3" t="s">
+      <c r="AW3" t="s">
         <v>130</v>
       </c>
-      <c r="AT3" t="s">
+      <c r="AX3" t="s">
         <v>131</v>
       </c>
-      <c r="AU3" t="s">
-        <v>132</v>
-      </c>
-      <c r="BL3" t="s">
+      <c r="AY3" t="s">
+        <v>132</v>
+      </c>
+      <c r="BP3" t="s">
         <v>160</v>
       </c>
-      <c r="BM3">
+      <c r="BQ3">
         <v>14</v>
       </c>
-      <c r="BN3">
+      <c r="BR3">
         <v>-24.7</v>
       </c>
-      <c r="BO3">
+      <c r="BS3">
         <v>-0.3</v>
       </c>
-      <c r="BP3">
+      <c r="BT3">
         <v>1.99</v>
       </c>
-      <c r="BQ3" t="s">
+      <c r="BU3" t="s">
         <v>130</v>
       </c>
-      <c r="BR3" t="s">
+      <c r="BV3" t="s">
         <v>131</v>
       </c>
-      <c r="BS3" t="s">
-        <v>132</v>
-      </c>
-      <c r="CS3">
+      <c r="BW3" t="s">
+        <v>132</v>
+      </c>
+      <c r="CX3">
         <v>12</v>
       </c>
-      <c r="CT3">
+      <c r="CY3">
         <v>14</v>
       </c>
-      <c r="CW3">
-        <v>0</v>
-      </c>
-      <c r="CX3">
+      <c r="DB3">
+        <v>0</v>
+      </c>
+      <c r="DC3">
         <v>14</v>
       </c>
-      <c r="CY3">
+      <c r="DD3">
         <v>1</v>
       </c>
-      <c r="CZ3">
+      <c r="DE3">
         <v>14</v>
       </c>
-      <c r="DC3">
+      <c r="DH3">
         <v>1</v>
       </c>
-      <c r="DD3">
+      <c r="DI3">
         <v>14</v>
       </c>
-      <c r="DE3">
+      <c r="DJ3">
         <v>2</v>
       </c>
-      <c r="DF3">
+      <c r="DK3">
         <v>14</v>
       </c>
-      <c r="DK3">
+      <c r="DP3">
         <v>1</v>
       </c>
-      <c r="DL3">
+      <c r="DQ3">
         <v>14</v>
       </c>
-      <c r="DM3">
+      <c r="DR3">
         <v>11</v>
       </c>
-      <c r="DN3">
+      <c r="DS3">
         <v>14</v>
       </c>
-      <c r="DO3">
+      <c r="DT3">
         <v>1</v>
       </c>
-      <c r="DP3">
+      <c r="DU3">
         <v>14</v>
       </c>
-      <c r="DW3" t="s">
+      <c r="EB3" t="s">
         <v>162</v>
       </c>
-      <c r="DX3" t="s">
+      <c r="EC3" t="s">
         <v>161</v>
       </c>
-      <c r="DY3" t="s">
+      <c r="ED3" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="4" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>127</v>
       </c>
       <c r="B4" t="s">
         <v>166</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="16">
+        <v>2020</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>277</v>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>144</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
         <v>127</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>167</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="I4" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="H4" t="s">
+      <c r="J4" t="s">
         <v>147</v>
       </c>
-      <c r="I4" t="s">
+      <c r="K4" t="s">
         <v>168</v>
       </c>
-      <c r="J4">
+      <c r="L4">
         <v>120</v>
       </c>
-      <c r="K4" t="s">
+      <c r="M4" t="s">
         <v>169</v>
       </c>
-      <c r="L4">
+      <c r="N4">
         <v>43</v>
       </c>
-      <c r="M4">
+      <c r="O4">
         <v>4</v>
       </c>
-      <c r="N4" t="s">
+      <c r="P4" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q4" t="s">
         <v>139</v>
       </c>
-      <c r="O4" t="s">
+      <c r="R4" t="s">
         <v>170</v>
       </c>
-      <c r="R4" t="s">
+      <c r="U4" t="s">
         <v>171</v>
       </c>
-      <c r="S4" t="s">
+      <c r="V4" t="s">
         <v>170</v>
       </c>
-      <c r="T4" t="s">
+      <c r="W4" t="s">
         <v>152</v>
       </c>
-      <c r="U4" t="s">
+      <c r="X4" t="s">
         <v>170</v>
       </c>
-      <c r="V4" t="s">
+      <c r="Y4" t="s">
         <v>165</v>
       </c>
-      <c r="W4" t="s">
+      <c r="Z4" t="s">
         <v>170</v>
       </c>
-      <c r="X4" t="s">
+      <c r="AA4" t="s">
         <v>154</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="AB4" t="s">
         <v>170</v>
       </c>
-      <c r="Z4" t="s">
-        <v>155</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
+        <v>155</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>155</v>
+      </c>
+      <c r="AE4" t="s">
         <v>157</v>
       </c>
-      <c r="AC4" t="s">
-        <v>155</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>155</v>
-      </c>
-      <c r="AE4" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="AF4" t="s">
+        <v>155</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>155</v>
+      </c>
+      <c r="AH4" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AI4" t="s">
         <v>129</v>
       </c>
-      <c r="AG4">
+      <c r="AJ4">
         <v>120</v>
       </c>
-      <c r="AH4">
+      <c r="AK4" s="16">
+        <v>120</v>
+      </c>
+      <c r="AL4">
         <v>101.4</v>
       </c>
-      <c r="AI4">
+      <c r="AM4">
         <v>-17.2</v>
       </c>
-      <c r="AJ4">
+      <c r="AN4">
         <v>18.63</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AO4" t="s">
         <v>130</v>
       </c>
-      <c r="AL4" t="s">
+      <c r="AP4" t="s">
         <v>131</v>
       </c>
-      <c r="AM4" t="s">
-        <v>132</v>
-      </c>
-      <c r="AN4" t="s">
+      <c r="AQ4" t="s">
+        <v>132</v>
+      </c>
+      <c r="AR4" t="s">
         <v>133</v>
       </c>
-      <c r="AO4">
+      <c r="AS4">
         <v>120</v>
       </c>
-      <c r="AP4">
+      <c r="AT4">
         <v>25.8</v>
       </c>
-      <c r="AQ4">
+      <c r="AU4">
         <v>-5.5</v>
       </c>
-      <c r="AR4">
+      <c r="AV4">
         <v>5.48</v>
       </c>
-      <c r="AS4" t="s">
+      <c r="AW4" t="s">
         <v>130</v>
       </c>
-      <c r="AT4" t="s">
+      <c r="AX4" t="s">
         <v>131</v>
       </c>
-      <c r="AU4" t="s">
-        <v>132</v>
-      </c>
-      <c r="AV4" s="9" t="s">
+      <c r="AY4" t="s">
+        <v>132</v>
+      </c>
+      <c r="AZ4" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="AW4">
+      <c r="BA4">
         <v>120</v>
       </c>
-      <c r="AX4" s="9">
+      <c r="BB4" s="9">
         <v>37.200000000000003</v>
       </c>
-      <c r="AY4" s="9">
+      <c r="BC4" s="9">
         <v>-7.1</v>
       </c>
-      <c r="AZ4" s="9">
+      <c r="BD4" s="9">
         <v>10.95</v>
       </c>
-      <c r="BA4" t="s">
+      <c r="BE4" t="s">
         <v>130</v>
       </c>
-      <c r="BB4" t="s">
+      <c r="BF4" t="s">
         <v>131</v>
       </c>
-      <c r="BC4" t="s">
-        <v>132</v>
-      </c>
-      <c r="BT4" t="s">
+      <c r="BG4" t="s">
+        <v>132</v>
+      </c>
+      <c r="BX4" t="s">
         <v>135</v>
       </c>
-      <c r="BU4">
+      <c r="BY4">
         <v>120</v>
       </c>
-      <c r="BV4">
+      <c r="BZ4" s="16">
+        <v>120</v>
+      </c>
+      <c r="CA4">
         <v>13.1</v>
       </c>
-      <c r="BW4">
+      <c r="CB4">
         <v>-3.3</v>
       </c>
-      <c r="BX4">
+      <c r="CC4">
         <v>6.57</v>
       </c>
-      <c r="BY4" t="s">
+      <c r="CD4" t="s">
         <v>130</v>
       </c>
-      <c r="BZ4" t="s">
+      <c r="CE4" t="s">
         <v>131</v>
       </c>
-      <c r="CA4" t="s">
-        <v>132</v>
-      </c>
-      <c r="CB4" t="s">
+      <c r="CF4" t="s">
+        <v>132</v>
+      </c>
+      <c r="CG4" t="s">
         <v>136</v>
       </c>
-      <c r="CC4">
+      <c r="CH4">
         <v>120</v>
       </c>
-      <c r="CD4">
+      <c r="CI4">
         <v>75.400000000000006</v>
       </c>
-      <c r="CE4">
+      <c r="CJ4">
         <v>0.3</v>
       </c>
-      <c r="CF4">
+      <c r="CK4">
         <v>1.9</v>
       </c>
-      <c r="CG4" t="s">
+      <c r="CL4" t="s">
         <v>130</v>
       </c>
-      <c r="CH4" t="s">
+      <c r="CM4" t="s">
         <v>131</v>
       </c>
-      <c r="CI4" t="s">
-        <v>132</v>
-      </c>
-      <c r="CJ4" t="s">
+      <c r="CN4" t="s">
+        <v>132</v>
+      </c>
+      <c r="CO4" t="s">
         <v>172</v>
       </c>
-      <c r="CK4" t="s">
+      <c r="CP4" t="s">
         <v>137</v>
       </c>
-      <c r="CL4">
+      <c r="CQ4">
         <v>114</v>
       </c>
-      <c r="CN4">
+      <c r="CS4">
         <v>-1.965789473684211</v>
       </c>
-      <c r="CO4">
+      <c r="CT4">
         <v>28</v>
       </c>
-      <c r="CP4" t="s">
+      <c r="CU4" t="s">
         <v>130</v>
       </c>
-      <c r="CQ4" t="s">
-        <v>132</v>
-      </c>
-      <c r="CR4" t="s">
+      <c r="CV4" t="s">
+        <v>132</v>
+      </c>
+      <c r="CW4" t="s">
         <v>131</v>
       </c>
-      <c r="CS4">
+      <c r="CX4">
         <v>55</v>
       </c>
-      <c r="CT4">
+      <c r="CY4">
         <v>120</v>
       </c>
-      <c r="CW4">
+      <c r="DB4">
         <v>2</v>
       </c>
-      <c r="CX4">
+      <c r="DC4">
         <v>120</v>
       </c>
-      <c r="DA4">
+      <c r="DF4">
         <v>11</v>
       </c>
-      <c r="DB4">
+      <c r="DG4">
         <v>120</v>
       </c>
-      <c r="DC4">
+      <c r="DH4">
         <v>6</v>
       </c>
-      <c r="DD4">
+      <c r="DI4">
         <v>120</v>
       </c>
-      <c r="DE4">
+      <c r="DJ4">
         <v>8</v>
       </c>
-      <c r="DF4">
+      <c r="DK4">
         <v>120</v>
       </c>
-      <c r="DI4">
-        <v>0</v>
-      </c>
-      <c r="DJ4">
+      <c r="DN4">
+        <v>0</v>
+      </c>
+      <c r="DO4">
         <v>120</v>
       </c>
-      <c r="DK4">
+      <c r="DP4">
         <v>6</v>
       </c>
-      <c r="DL4">
+      <c r="DQ4">
         <v>120</v>
       </c>
-      <c r="DO4">
+      <c r="DT4">
         <v>4</v>
       </c>
-      <c r="DP4">
+      <c r="DU4">
         <v>120</v>
       </c>
-      <c r="DQ4">
+      <c r="DV4">
         <v>1</v>
       </c>
-      <c r="DR4">
+      <c r="DW4">
         <v>120</v>
       </c>
-      <c r="DS4">
+      <c r="DX4">
         <v>4</v>
       </c>
-      <c r="DT4">
+      <c r="DY4">
         <v>120</v>
       </c>
-      <c r="DU4">
+      <c r="DZ4">
         <v>1</v>
       </c>
-      <c r="DV4">
+      <c r="EA4">
         <v>120</v>
       </c>
-      <c r="DW4" t="s">
+      <c r="EB4" t="s">
         <v>138</v>
       </c>
-      <c r="DX4" t="s">
+      <c r="EC4" t="s">
         <v>161</v>
       </c>
-      <c r="DY4" t="s">
+      <c r="ED4" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="5" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>162</v>
       </c>
       <c r="B5" t="s">
         <v>166</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="16">
+        <v>2020</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>277</v>
+      </c>
+      <c r="E5">
         <v>1</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>144</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>162</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
         <v>128</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="I5" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="H5" t="s">
+      <c r="J5" t="s">
         <v>147</v>
       </c>
-      <c r="I5" t="s">
+      <c r="K5" t="s">
         <v>168</v>
       </c>
-      <c r="J5">
+      <c r="L5">
         <v>125</v>
       </c>
-      <c r="K5" t="s">
+      <c r="M5" t="s">
         <v>169</v>
       </c>
-      <c r="L5">
+      <c r="N5">
         <v>46</v>
       </c>
-      <c r="M5">
+      <c r="O5">
         <v>4</v>
       </c>
-      <c r="N5" t="s">
+      <c r="P5" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q5" t="s">
         <v>173</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="R5" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="R5" t="s">
+      <c r="U5" t="s">
         <v>171</v>
       </c>
-      <c r="S5" t="s">
+      <c r="V5" t="s">
         <v>174</v>
       </c>
-      <c r="T5" t="s">
+      <c r="W5" t="s">
         <v>175</v>
       </c>
-      <c r="U5" t="s">
+      <c r="X5" t="s">
         <v>174</v>
       </c>
-      <c r="V5" t="s">
+      <c r="Y5" t="s">
         <v>128</v>
       </c>
-      <c r="W5" t="s">
+      <c r="Z5" t="s">
         <v>174</v>
       </c>
-      <c r="X5" t="s">
+      <c r="AA5" t="s">
         <v>176</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="AB5" t="s">
         <v>174</v>
       </c>
-      <c r="Z5" t="s">
-        <v>155</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB5" t="s">
+      <c r="AC5" t="s">
+        <v>155</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>155</v>
+      </c>
+      <c r="AE5" t="s">
         <v>157</v>
       </c>
-      <c r="AC5" t="s">
-        <v>155</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>155</v>
-      </c>
-      <c r="AE5" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="AF5" t="s">
+        <v>155</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>155</v>
+      </c>
+      <c r="AH5" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AI5" t="s">
         <v>129</v>
       </c>
-      <c r="AG5">
+      <c r="AJ5">
         <v>125</v>
       </c>
-      <c r="AH5">
+      <c r="AK5" s="16">
+        <v>125</v>
+      </c>
+      <c r="AL5">
         <v>99.7</v>
       </c>
-      <c r="AI5">
+      <c r="AM5">
         <v>-9.6999999999999993</v>
       </c>
-      <c r="AJ5">
+      <c r="AN5">
         <v>17.89</v>
       </c>
-      <c r="AK5" t="s">
+      <c r="AO5" t="s">
         <v>130</v>
       </c>
-      <c r="AL5" t="s">
+      <c r="AP5" t="s">
         <v>131</v>
       </c>
-      <c r="AM5" t="s">
-        <v>132</v>
-      </c>
-      <c r="AN5" t="s">
+      <c r="AQ5" t="s">
+        <v>132</v>
+      </c>
+      <c r="AR5" t="s">
         <v>133</v>
       </c>
-      <c r="AO5">
+      <c r="AS5">
         <v>125</v>
       </c>
-      <c r="AP5">
+      <c r="AT5">
         <v>25.4</v>
       </c>
-      <c r="AQ5">
+      <c r="AU5">
         <v>-3.9</v>
       </c>
-      <c r="AR5">
+      <c r="AV5">
         <v>5.59</v>
       </c>
-      <c r="AS5" t="s">
+      <c r="AW5" t="s">
         <v>130</v>
       </c>
-      <c r="AT5" t="s">
+      <c r="AX5" t="s">
         <v>131</v>
       </c>
-      <c r="AU5" t="s">
-        <v>132</v>
-      </c>
-      <c r="AV5" s="9" t="s">
+      <c r="AY5" t="s">
+        <v>132</v>
+      </c>
+      <c r="AZ5" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="AW5">
+      <c r="BA5">
         <v>125</v>
       </c>
-      <c r="AX5" s="9">
+      <c r="BB5" s="9">
         <v>37.4</v>
       </c>
-      <c r="AY5" s="9">
+      <c r="BC5" s="9">
         <v>-2.7</v>
       </c>
-      <c r="AZ5" s="9">
+      <c r="BD5" s="9">
         <v>10.06</v>
       </c>
-      <c r="BA5" t="s">
+      <c r="BE5" t="s">
         <v>130</v>
       </c>
-      <c r="BB5" t="s">
+      <c r="BF5" t="s">
         <v>131</v>
       </c>
-      <c r="BC5" t="s">
-        <v>132</v>
-      </c>
-      <c r="BT5" t="s">
+      <c r="BG5" t="s">
+        <v>132</v>
+      </c>
+      <c r="BX5" t="s">
         <v>135</v>
       </c>
-      <c r="BU5">
+      <c r="BY5">
         <v>125</v>
       </c>
-      <c r="BV5">
+      <c r="BZ5" s="16">
+        <v>125</v>
+      </c>
+      <c r="CA5">
         <v>12.6</v>
       </c>
-      <c r="BW5">
+      <c r="CB5">
         <v>-1.6</v>
       </c>
-      <c r="BX5">
+      <c r="CC5">
         <v>6.71</v>
       </c>
-      <c r="BY5" t="s">
+      <c r="CD5" t="s">
         <v>130</v>
       </c>
-      <c r="BZ5" t="s">
+      <c r="CE5" t="s">
         <v>131</v>
       </c>
-      <c r="CA5" t="s">
-        <v>132</v>
-      </c>
-      <c r="CB5" t="s">
+      <c r="CF5" t="s">
+        <v>132</v>
+      </c>
+      <c r="CG5" t="s">
         <v>136</v>
       </c>
-      <c r="CC5">
+      <c r="CH5">
         <v>125</v>
       </c>
-      <c r="CD5">
+      <c r="CI5">
         <v>75.400000000000006</v>
       </c>
-      <c r="CE5">
+      <c r="CJ5">
         <v>-0.1</v>
       </c>
-      <c r="CF5">
+      <c r="CK5">
         <v>2.2999999999999998</v>
       </c>
-      <c r="CG5" t="s">
+      <c r="CL5" t="s">
         <v>130</v>
       </c>
-      <c r="CH5" t="s">
+      <c r="CM5" t="s">
         <v>131</v>
       </c>
-      <c r="CI5" t="s">
-        <v>132</v>
-      </c>
-      <c r="CJ5" t="s">
+      <c r="CN5" t="s">
+        <v>132</v>
+      </c>
+      <c r="CO5" t="s">
         <v>172</v>
       </c>
-      <c r="CK5" t="s">
+      <c r="CP5" t="s">
         <v>137</v>
       </c>
-      <c r="CL5">
+      <c r="CQ5">
         <v>113</v>
       </c>
-      <c r="CN5">
+      <c r="CS5">
         <v>-1.3838053097345131</v>
       </c>
-      <c r="CO5">
+      <c r="CT5">
         <v>28</v>
       </c>
-      <c r="CP5" t="s">
+      <c r="CU5" t="s">
         <v>130</v>
       </c>
-      <c r="CQ5" t="s">
-        <v>132</v>
-      </c>
-      <c r="CR5" t="s">
+      <c r="CV5" t="s">
+        <v>132</v>
+      </c>
+      <c r="CW5" t="s">
         <v>131</v>
       </c>
-      <c r="CS5">
+      <c r="CX5">
         <v>63</v>
       </c>
-      <c r="CT5">
+      <c r="CY5">
         <v>125</v>
       </c>
-      <c r="CW5">
+      <c r="DB5">
         <v>9</v>
       </c>
-      <c r="CX5">
+      <c r="DC5">
         <v>125</v>
       </c>
-      <c r="DA5">
+      <c r="DF5">
         <v>15</v>
       </c>
-      <c r="DB5">
+      <c r="DG5">
         <v>125</v>
       </c>
-      <c r="DC5">
+      <c r="DH5">
         <v>4</v>
       </c>
-      <c r="DD5">
+      <c r="DI5">
         <v>125</v>
       </c>
-      <c r="DE5">
+      <c r="DJ5">
         <v>6</v>
       </c>
-      <c r="DF5">
+      <c r="DK5">
         <v>125</v>
       </c>
-      <c r="DI5">
-        <v>0</v>
-      </c>
-      <c r="DJ5">
+      <c r="DN5">
+        <v>0</v>
+      </c>
+      <c r="DO5">
         <v>125</v>
       </c>
-      <c r="DK5">
+      <c r="DP5">
         <v>6</v>
       </c>
-      <c r="DL5">
+      <c r="DQ5">
         <v>125</v>
       </c>
-      <c r="DO5">
+      <c r="DT5">
         <v>13</v>
       </c>
-      <c r="DP5">
+      <c r="DU5">
         <v>125</v>
       </c>
-      <c r="DQ5">
-        <v>0</v>
-      </c>
-      <c r="DR5">
+      <c r="DV5">
+        <v>0</v>
+      </c>
+      <c r="DW5">
         <v>125</v>
       </c>
-      <c r="DS5">
+      <c r="DX5">
         <v>4</v>
       </c>
-      <c r="DT5">
+      <c r="DY5">
         <v>125</v>
       </c>
-      <c r="DU5">
+      <c r="DZ5">
         <v>1</v>
       </c>
-      <c r="DV5">
+      <c r="EA5">
         <v>125</v>
       </c>
-      <c r="DW5" t="s">
+      <c r="EB5" t="s">
         <v>162</v>
       </c>
-      <c r="DX5" t="s">
+      <c r="EC5" t="s">
         <v>161</v>
       </c>
-      <c r="DY5" t="s">
+      <c r="ED5" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>177</v>
       </c>
       <c r="B6" t="s">
         <v>178</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="16">
+        <v>2023</v>
+      </c>
+      <c r="E6">
         <v>1</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
         <v>144</v>
       </c>
-      <c r="E6" t="s">
+      <c r="G6" t="s">
         <v>127</v>
       </c>
-      <c r="F6" t="s">
+      <c r="H6" t="s">
         <v>179</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="I6" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="H6" t="s">
+      <c r="J6" t="s">
         <v>147</v>
       </c>
-      <c r="I6" s="2">
+      <c r="K6" s="2">
         <v>435</v>
       </c>
-      <c r="J6" s="3">
+      <c r="L6" s="3">
         <v>144</v>
       </c>
-      <c r="K6" t="s">
+      <c r="M6" t="s">
         <v>181</v>
       </c>
-      <c r="M6">
+      <c r="O6">
         <v>6</v>
       </c>
-      <c r="N6" s="2">
+      <c r="P6" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q6" s="2">
         <v>22</v>
       </c>
-      <c r="O6" s="3">
+      <c r="R6" s="3">
         <v>144</v>
       </c>
-      <c r="R6" s="2">
+      <c r="U6" s="2">
         <v>34</v>
       </c>
-      <c r="S6" s="2">
+      <c r="V6" s="2">
         <v>144</v>
       </c>
-      <c r="Z6" t="s">
-        <v>155</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB6" s="2" t="s">
+      <c r="AC6" t="s">
+        <v>155</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>155</v>
+      </c>
+      <c r="AE6" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="AC6" t="s">
-        <v>155</v>
-      </c>
-      <c r="AD6" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="AE6" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="AF6" t="s">
+        <v>155</v>
+      </c>
+      <c r="AG6" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AH6" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AI6" t="s">
         <v>129</v>
       </c>
-      <c r="AG6" s="2">
+      <c r="AJ6" s="2">
         <v>142</v>
       </c>
-      <c r="AH6" s="2">
+      <c r="AK6" s="16">
+        <v>142</v>
+      </c>
+      <c r="AL6" s="2">
         <v>102</v>
       </c>
-      <c r="AI6">
+      <c r="AM6">
         <v>-16.899999999999999</v>
       </c>
-      <c r="AJ6" s="2">
+      <c r="AN6" s="2">
         <v>19.07</v>
       </c>
-      <c r="AK6" t="s">
+      <c r="AO6" t="s">
         <v>130</v>
       </c>
-      <c r="AL6" t="s">
+      <c r="AP6" t="s">
         <v>131</v>
       </c>
-      <c r="AM6" t="s">
-        <v>132</v>
-      </c>
-      <c r="DW6" t="s">
+      <c r="AQ6" t="s">
+        <v>132</v>
+      </c>
+      <c r="EB6" t="s">
         <v>138</v>
       </c>
-      <c r="DX6" t="s">
+      <c r="EC6" t="s">
         <v>161</v>
       </c>
-      <c r="DY6" t="s">
+      <c r="ED6" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="7" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>182</v>
       </c>
       <c r="B7" t="s">
         <v>178</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="16">
+        <v>2023</v>
+      </c>
+      <c r="E7">
         <v>1</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7" t="s">
         <v>144</v>
       </c>
-      <c r="E7" t="s">
+      <c r="G7" t="s">
         <v>127</v>
       </c>
-      <c r="F7" t="s">
+      <c r="H7" t="s">
         <v>183</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="I7" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="H7" t="s">
+      <c r="J7" t="s">
         <v>147</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>435</v>
       </c>
-      <c r="J7" s="3">
+      <c r="L7" s="3">
         <v>145</v>
       </c>
-      <c r="K7" t="s">
+      <c r="M7" t="s">
         <v>181</v>
       </c>
-      <c r="M7">
+      <c r="O7">
         <v>6</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q7" s="2">
         <v>29</v>
       </c>
-      <c r="O7" s="3">
+      <c r="R7" s="3">
         <v>145</v>
       </c>
-      <c r="R7" s="2">
+      <c r="U7" s="2">
         <v>27</v>
       </c>
-      <c r="S7" s="2">
+      <c r="V7" s="2">
         <v>145</v>
       </c>
-      <c r="Z7" t="s">
-        <v>155</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB7" s="2" t="s">
+      <c r="AC7" t="s">
+        <v>155</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>155</v>
+      </c>
+      <c r="AE7" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="AC7" t="s">
-        <v>155</v>
-      </c>
-      <c r="AD7" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="AE7" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="AF7" t="s">
+        <v>155</v>
+      </c>
+      <c r="AG7" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AH7" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AI7" t="s">
         <v>129</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AJ7" s="2">
         <v>145</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AK7" s="16">
+        <v>145</v>
+      </c>
+      <c r="AL7" s="2">
         <v>102</v>
       </c>
-      <c r="AI7">
+      <c r="AM7">
         <v>-19.600000000000001</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AN7" s="2">
         <v>19.27</v>
       </c>
-      <c r="AK7" t="s">
+      <c r="AO7" t="s">
         <v>130</v>
       </c>
-      <c r="AL7" t="s">
+      <c r="AP7" t="s">
         <v>131</v>
       </c>
-      <c r="AM7" t="s">
-        <v>132</v>
-      </c>
-      <c r="DW7" t="s">
+      <c r="AQ7" t="s">
+        <v>132</v>
+      </c>
+      <c r="EB7" t="s">
         <v>138</v>
       </c>
-      <c r="DX7" t="s">
+      <c r="EC7" t="s">
         <v>161</v>
       </c>
-      <c r="DY7" t="s">
+      <c r="ED7" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="8" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>184</v>
       </c>
       <c r="B8" t="s">
         <v>178</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="16">
+        <v>2023</v>
+      </c>
+      <c r="E8">
         <v>1</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>144</v>
       </c>
-      <c r="E8" t="s">
+      <c r="G8" t="s">
         <v>162</v>
       </c>
-      <c r="F8" t="s">
+      <c r="H8" t="s">
         <v>128</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="I8" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="H8" t="s">
+      <c r="J8" t="s">
         <v>147</v>
       </c>
-      <c r="I8" t="s">
+      <c r="K8" t="s">
         <v>180</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>146</v>
       </c>
-      <c r="K8" t="s">
+      <c r="M8" t="s">
         <v>181</v>
       </c>
-      <c r="M8">
+      <c r="O8">
         <v>6</v>
       </c>
-      <c r="N8" s="2">
+      <c r="P8" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q8" s="2">
         <v>26</v>
       </c>
-      <c r="O8" s="3">
+      <c r="R8" s="3">
         <v>146</v>
       </c>
-      <c r="R8" s="2">
+      <c r="U8" s="2">
         <v>27</v>
       </c>
-      <c r="S8" s="2">
+      <c r="V8" s="2">
         <v>146</v>
       </c>
-      <c r="Z8" t="s">
-        <v>155</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB8" s="2" t="s">
+      <c r="AC8" t="s">
+        <v>155</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>155</v>
+      </c>
+      <c r="AE8" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="AC8" t="s">
-        <v>155</v>
-      </c>
-      <c r="AD8" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="AE8" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="AF8" t="s">
+        <v>155</v>
+      </c>
+      <c r="AG8" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AH8" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AI8" t="s">
         <v>129</v>
       </c>
-      <c r="AG8">
+      <c r="AJ8">
         <v>145</v>
       </c>
-      <c r="AH8" s="2">
+      <c r="AK8" s="16">
+        <v>145</v>
+      </c>
+      <c r="AL8" s="2">
         <v>102</v>
       </c>
-      <c r="AI8">
+      <c r="AM8">
         <v>-19.3</v>
       </c>
-      <c r="AJ8" s="2">
+      <c r="AN8" s="2">
         <v>18.059999999999999</v>
       </c>
-      <c r="AK8" t="s">
+      <c r="AO8" t="s">
         <v>130</v>
       </c>
-      <c r="AL8" t="s">
+      <c r="AP8" t="s">
         <v>131</v>
       </c>
-      <c r="AM8" t="s">
-        <v>132</v>
-      </c>
-      <c r="DW8" t="s">
+      <c r="AQ8" t="s">
+        <v>132</v>
+      </c>
+      <c r="EB8" t="s">
         <v>162</v>
       </c>
-      <c r="DX8" t="s">
+      <c r="EC8" t="s">
         <v>161</v>
       </c>
-      <c r="DY8" t="s">
+      <c r="ED8" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="9" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>185</v>
       </c>
       <c r="B9" t="s">
         <v>186</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="16">
+        <v>2023</v>
+      </c>
+      <c r="E9">
         <v>1</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>144</v>
       </c>
-      <c r="E9" t="s">
+      <c r="G9" t="s">
         <v>127</v>
       </c>
-      <c r="F9" t="s">
+      <c r="H9" t="s">
         <v>183</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="I9" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="H9" t="s">
+      <c r="J9" t="s">
         <v>147</v>
       </c>
-      <c r="I9" t="s">
+      <c r="K9" t="s">
         <v>187</v>
       </c>
-      <c r="J9" s="2">
-        <v>155</v>
-      </c>
-      <c r="K9" t="s">
+      <c r="L9" s="2">
+        <v>155</v>
+      </c>
+      <c r="M9" t="s">
         <v>181</v>
       </c>
-      <c r="M9">
+      <c r="O9">
         <v>6</v>
       </c>
-      <c r="N9" s="2">
+      <c r="P9" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q9" s="2">
         <v>23</v>
       </c>
-      <c r="O9" s="2">
-        <v>155</v>
-      </c>
       <c r="R9" s="2">
+        <v>155</v>
+      </c>
+      <c r="U9" s="2">
         <v>34</v>
       </c>
-      <c r="S9" s="2">
-        <v>155</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>155</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB9" s="2" t="s">
+      <c r="V9" s="2">
+        <v>155</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>155</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>155</v>
+      </c>
+      <c r="AE9" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="AC9" t="s">
-        <v>155</v>
-      </c>
-      <c r="AD9" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="AE9" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="AF9" t="s">
+        <v>155</v>
+      </c>
+      <c r="AG9" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AH9" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AI9" t="s">
         <v>129</v>
       </c>
-      <c r="AG9" s="2">
+      <c r="AJ9" s="2">
         <v>153</v>
       </c>
-      <c r="AH9" s="2">
+      <c r="AK9" s="16">
+        <v>153</v>
+      </c>
+      <c r="AL9" s="2">
         <v>101</v>
       </c>
-      <c r="AI9">
+      <c r="AM9">
         <v>-16.399999999999999</v>
       </c>
-      <c r="AJ9" s="2">
+      <c r="AN9" s="2">
         <v>18.55</v>
       </c>
-      <c r="AK9" t="s">
+      <c r="AO9" t="s">
         <v>130</v>
       </c>
-      <c r="AL9" t="s">
+      <c r="AP9" t="s">
         <v>131</v>
       </c>
-      <c r="AM9" t="s">
-        <v>132</v>
-      </c>
-      <c r="DW9" t="s">
+      <c r="AQ9" t="s">
+        <v>132</v>
+      </c>
+      <c r="EB9" t="s">
         <v>138</v>
       </c>
-      <c r="DX9" t="s">
+      <c r="EC9" t="s">
         <v>161</v>
       </c>
-      <c r="DY9" t="s">
+      <c r="ED9" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="10" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>188</v>
       </c>
       <c r="B10" t="s">
         <v>186</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="16">
+        <v>2023</v>
+      </c>
+      <c r="E10">
         <v>1</v>
       </c>
-      <c r="D10" t="s">
+      <c r="F10" t="s">
         <v>144</v>
       </c>
-      <c r="E10" t="s">
+      <c r="G10" t="s">
         <v>127</v>
       </c>
-      <c r="F10" t="s">
+      <c r="H10" t="s">
         <v>189</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="I10" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="H10" t="s">
+      <c r="J10" t="s">
         <v>147</v>
       </c>
-      <c r="I10" t="s">
+      <c r="K10" t="s">
         <v>187</v>
       </c>
-      <c r="J10" s="2">
+      <c r="L10" s="2">
         <v>154</v>
       </c>
-      <c r="K10" t="s">
+      <c r="M10" t="s">
         <v>181</v>
       </c>
-      <c r="M10">
+      <c r="O10">
         <v>6</v>
       </c>
-      <c r="N10" s="2">
+      <c r="P10" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q10" s="2">
         <v>27</v>
       </c>
-      <c r="O10" s="2">
+      <c r="R10" s="2">
         <v>154</v>
       </c>
-      <c r="R10" s="2">
+      <c r="U10" s="2">
         <v>38</v>
       </c>
-      <c r="S10" s="2">
+      <c r="V10" s="2">
         <v>154</v>
       </c>
-      <c r="Z10" t="s">
-        <v>155</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB10" s="2" t="s">
+      <c r="AC10" t="s">
+        <v>155</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>155</v>
+      </c>
+      <c r="AE10" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="AC10" t="s">
-        <v>155</v>
-      </c>
-      <c r="AD10" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="AE10" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="AF10" t="s">
+        <v>155</v>
+      </c>
+      <c r="AG10" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AH10" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AI10" t="s">
         <v>129</v>
       </c>
-      <c r="AG10" s="2">
+      <c r="AJ10" s="2">
         <v>152</v>
       </c>
-      <c r="AH10" s="2">
+      <c r="AK10" s="16">
+        <v>152</v>
+      </c>
+      <c r="AL10" s="2">
         <v>100</v>
       </c>
-      <c r="AI10">
+      <c r="AM10">
         <v>-18.100000000000001</v>
       </c>
-      <c r="AJ10" s="2">
+      <c r="AN10" s="2">
         <v>18.489999999999998</v>
       </c>
-      <c r="AK10" t="s">
+      <c r="AO10" t="s">
         <v>130</v>
       </c>
-      <c r="AL10" t="s">
+      <c r="AP10" t="s">
         <v>131</v>
       </c>
-      <c r="AM10" t="s">
-        <v>132</v>
-      </c>
-      <c r="DW10" t="s">
+      <c r="AQ10" t="s">
+        <v>132</v>
+      </c>
+      <c r="EB10" t="s">
         <v>138</v>
       </c>
-      <c r="DX10" t="s">
+      <c r="EC10" t="s">
         <v>161</v>
       </c>
-      <c r="DY10" t="s">
+      <c r="ED10" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="11" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>162</v>
       </c>
       <c r="B11" t="s">
         <v>186</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="16">
+        <v>2023</v>
+      </c>
+      <c r="E11">
         <v>1</v>
       </c>
-      <c r="D11" t="s">
+      <c r="F11" t="s">
         <v>144</v>
       </c>
-      <c r="E11" t="s">
+      <c r="G11" t="s">
         <v>162</v>
       </c>
-      <c r="F11" t="s">
+      <c r="H11" t="s">
         <v>128</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="I11" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="H11" t="s">
+      <c r="J11" t="s">
         <v>147</v>
       </c>
-      <c r="I11" t="s">
+      <c r="K11" t="s">
         <v>187</v>
       </c>
-      <c r="J11" s="2">
-        <v>155</v>
-      </c>
-      <c r="K11" t="s">
+      <c r="L11" s="2">
+        <v>155</v>
+      </c>
+      <c r="M11" t="s">
         <v>181</v>
       </c>
-      <c r="M11">
+      <c r="O11">
         <v>6</v>
       </c>
-      <c r="N11" s="2">
+      <c r="P11" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q11" s="2">
         <v>21</v>
       </c>
-      <c r="O11" s="2">
-        <v>155</v>
-      </c>
       <c r="R11" s="2">
+        <v>155</v>
+      </c>
+      <c r="U11" s="2">
         <v>27</v>
       </c>
-      <c r="S11" s="2">
-        <v>155</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>155</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB11" s="2" t="s">
+      <c r="V11" s="2">
+        <v>155</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>155</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>155</v>
+      </c>
+      <c r="AE11" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="AC11" t="s">
-        <v>155</v>
-      </c>
-      <c r="AD11" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="AE11" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="AF11" t="s">
+        <v>155</v>
+      </c>
+      <c r="AG11" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AH11" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AI11" t="s">
         <v>129</v>
       </c>
-      <c r="AG11" s="2">
-        <v>155</v>
-      </c>
-      <c r="AH11" s="2">
+      <c r="AJ11" s="2">
+        <v>155</v>
+      </c>
+      <c r="AK11" s="16">
+        <v>155</v>
+      </c>
+      <c r="AL11" s="2">
         <v>100</v>
       </c>
-      <c r="AI11">
+      <c r="AM11">
         <v>-14.3</v>
       </c>
-      <c r="AJ11" s="2">
+      <c r="AN11" s="2">
         <v>18.670000000000002</v>
       </c>
-      <c r="AK11" t="s">
+      <c r="AO11" t="s">
         <v>130</v>
       </c>
-      <c r="AL11" t="s">
+      <c r="AP11" t="s">
         <v>131</v>
       </c>
-      <c r="AM11" t="s">
-        <v>132</v>
-      </c>
-      <c r="DW11" t="s">
+      <c r="AQ11" t="s">
+        <v>132</v>
+      </c>
+      <c r="EB11" t="s">
         <v>162</v>
       </c>
-      <c r="DX11" t="s">
+      <c r="EC11" t="s">
         <v>161</v>
       </c>
-      <c r="DY11" t="s">
+      <c r="ED11" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="12" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>191</v>
       </c>
       <c r="B12" t="s">
         <v>192</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="16">
+        <v>2023</v>
+      </c>
+      <c r="E12">
         <v>1</v>
       </c>
-      <c r="D12" t="s">
+      <c r="F12" t="s">
         <v>144</v>
       </c>
-      <c r="E12" t="s">
+      <c r="G12" t="s">
         <v>162</v>
       </c>
-      <c r="F12" t="s">
+      <c r="H12" t="s">
         <v>128</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="I12" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="H12" t="s">
+      <c r="J12" t="s">
         <v>147</v>
       </c>
-      <c r="I12" t="s">
+      <c r="K12" t="s">
         <v>193</v>
       </c>
-      <c r="J12">
+      <c r="L12">
         <v>73</v>
       </c>
-      <c r="K12" t="s">
+      <c r="M12" t="s">
         <v>194</v>
       </c>
-      <c r="L12">
+      <c r="N12">
         <v>19</v>
       </c>
-      <c r="M12">
+      <c r="O12">
         <v>4</v>
       </c>
-      <c r="N12" t="s">
+      <c r="P12" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q12" t="s">
         <v>150</v>
       </c>
-      <c r="O12" t="s">
+      <c r="R12" t="s">
         <v>195</v>
       </c>
-      <c r="R12" t="s">
+      <c r="U12" t="s">
         <v>196</v>
       </c>
-      <c r="S12" t="s">
+      <c r="V12" t="s">
         <v>197</v>
       </c>
-      <c r="T12" t="s">
+      <c r="W12" t="s">
         <v>150</v>
       </c>
-      <c r="U12" t="s">
+      <c r="X12" t="s">
         <v>197</v>
       </c>
-      <c r="V12" t="s">
+      <c r="Y12" t="s">
         <v>128</v>
       </c>
-      <c r="W12" t="s">
+      <c r="Z12" t="s">
         <v>195</v>
       </c>
-      <c r="X12" t="s">
+      <c r="AA12" t="s">
         <v>165</v>
       </c>
-      <c r="Y12" t="s">
+      <c r="AB12" t="s">
         <v>195</v>
       </c>
-      <c r="Z12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB12" t="s">
+      <c r="AC12" t="s">
+        <v>155</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>155</v>
+      </c>
+      <c r="AE12" t="s">
         <v>157</v>
       </c>
-      <c r="AC12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AE12" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="AF12" t="s">
+        <v>155</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>155</v>
+      </c>
+      <c r="AH12" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AI12" t="s">
         <v>129</v>
       </c>
-      <c r="AG12">
+      <c r="AJ12">
         <v>54</v>
       </c>
-      <c r="AH12">
+      <c r="AK12" s="16">
+        <v>72</v>
+      </c>
+      <c r="AL12">
         <v>99.38</v>
       </c>
-      <c r="AI12">
+      <c r="AM12">
         <v>88.69</v>
       </c>
-      <c r="AJ12">
+      <c r="AN12">
         <v>20.18</v>
       </c>
-      <c r="AK12" t="s">
+      <c r="AO12" t="s">
         <v>198</v>
       </c>
-      <c r="AL12" t="s">
-        <v>132</v>
-      </c>
-      <c r="AM12" t="s">
-        <v>132</v>
-      </c>
-      <c r="AN12" t="s">
+      <c r="AP12" t="s">
+        <v>132</v>
+      </c>
+      <c r="AQ12" t="s">
+        <v>132</v>
+      </c>
+      <c r="AR12" t="s">
         <v>133</v>
       </c>
-      <c r="AO12">
+      <c r="AS12">
         <v>54</v>
       </c>
-      <c r="AP12">
+      <c r="AT12">
         <v>26.86</v>
       </c>
-      <c r="AQ12">
+      <c r="AU12">
         <v>23.61</v>
       </c>
-      <c r="AR12">
+      <c r="AV12">
         <v>6.64</v>
       </c>
-      <c r="AS12" t="s">
+      <c r="AW12" t="s">
         <v>198</v>
       </c>
-      <c r="AT12" t="s">
-        <v>132</v>
-      </c>
-      <c r="AU12" t="s">
-        <v>132</v>
-      </c>
-      <c r="AV12" t="s">
+      <c r="AX12" t="s">
+        <v>132</v>
+      </c>
+      <c r="AY12" t="s">
+        <v>132</v>
+      </c>
+      <c r="AZ12" t="s">
         <v>134</v>
       </c>
-      <c r="AW12">
+      <c r="BA12">
         <v>54</v>
       </c>
-      <c r="AX12">
+      <c r="BB12">
         <v>24.1</v>
       </c>
-      <c r="AY12">
+      <c r="BC12">
         <v>22.65</v>
       </c>
-      <c r="AZ12">
+      <c r="BD12">
         <v>5.81</v>
       </c>
-      <c r="BA12" t="s">
+      <c r="BE12" t="s">
         <v>198</v>
       </c>
-      <c r="BB12" t="s">
-        <v>132</v>
-      </c>
-      <c r="BC12" t="s">
-        <v>132</v>
-      </c>
-      <c r="BT12" t="s">
+      <c r="BF12" t="s">
+        <v>132</v>
+      </c>
+      <c r="BG12" t="s">
+        <v>132</v>
+      </c>
+      <c r="BX12" t="s">
         <v>199</v>
       </c>
-      <c r="BU12">
+      <c r="BY12">
         <v>54</v>
       </c>
-      <c r="BV12">
+      <c r="BZ12" s="16">
+        <v>72</v>
+      </c>
+      <c r="CA12">
         <v>11.58</v>
       </c>
-      <c r="BW12">
+      <c r="CB12">
         <v>9.56</v>
       </c>
-      <c r="BX12">
+      <c r="CC12">
         <v>4.03</v>
       </c>
-      <c r="BY12" t="s">
+      <c r="CD12" t="s">
         <v>198</v>
       </c>
-      <c r="BZ12" t="s">
-        <v>132</v>
-      </c>
-      <c r="CA12" t="s">
-        <v>132</v>
-      </c>
-      <c r="CS12">
+      <c r="CE12" t="s">
+        <v>132</v>
+      </c>
+      <c r="CF12" t="s">
+        <v>132</v>
+      </c>
+      <c r="CX12">
         <v>23</v>
       </c>
-      <c r="CT12">
+      <c r="CY12">
         <v>72</v>
       </c>
-      <c r="CW12">
+      <c r="DB12">
         <v>6</v>
       </c>
-      <c r="CX12">
+      <c r="DC12">
         <v>72</v>
       </c>
-      <c r="DA12">
+      <c r="DF12">
         <v>4</v>
       </c>
-      <c r="DB12">
+      <c r="DG12">
         <v>72</v>
       </c>
-      <c r="DC12">
+      <c r="DH12">
         <v>4</v>
       </c>
-      <c r="DD12">
+      <c r="DI12">
         <v>72</v>
       </c>
-      <c r="DK12">
+      <c r="DP12">
         <v>2</v>
       </c>
-      <c r="DL12">
+      <c r="DQ12">
         <v>72</v>
       </c>
-      <c r="DO12">
+      <c r="DT12">
         <v>1</v>
       </c>
-      <c r="DP12">
+      <c r="DU12">
         <v>72</v>
       </c>
-      <c r="DU12">
+      <c r="DZ12">
         <v>1</v>
       </c>
-      <c r="DV12">
+      <c r="EA12">
         <v>72</v>
       </c>
-      <c r="DW12" t="s">
+      <c r="EB12" t="s">
         <v>162</v>
       </c>
-      <c r="DX12" t="s">
+      <c r="EC12" t="s">
         <v>161</v>
       </c>
-      <c r="DY12" t="s">
+      <c r="ED12" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="13" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>200</v>
       </c>
       <c r="B13" t="s">
         <v>192</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="16">
+        <v>2023</v>
+      </c>
+      <c r="E13">
         <v>1</v>
       </c>
-      <c r="D13" t="s">
+      <c r="F13" t="s">
         <v>144</v>
       </c>
-      <c r="E13" t="s">
+      <c r="G13" t="s">
         <v>201</v>
       </c>
-      <c r="F13" t="s">
+      <c r="H13" t="s">
         <v>202</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="I13" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="H13" t="s">
+      <c r="J13" t="s">
         <v>147</v>
       </c>
-      <c r="I13" t="s">
+      <c r="K13" t="s">
         <v>193</v>
       </c>
-      <c r="J13">
+      <c r="L13">
         <v>71</v>
       </c>
-      <c r="K13" t="s">
+      <c r="M13" t="s">
         <v>194</v>
       </c>
-      <c r="L13">
+      <c r="N13">
         <v>19</v>
       </c>
-      <c r="M13">
+      <c r="O13">
         <v>4</v>
       </c>
-      <c r="N13" t="s">
+      <c r="P13" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q13" t="s">
         <v>153</v>
       </c>
-      <c r="O13" t="s">
+      <c r="R13" t="s">
         <v>203</v>
       </c>
-      <c r="R13" t="s">
+      <c r="U13" t="s">
         <v>151</v>
       </c>
-      <c r="S13" t="s">
+      <c r="V13" t="s">
         <v>204</v>
       </c>
-      <c r="T13" t="s">
+      <c r="W13" t="s">
         <v>176</v>
       </c>
-      <c r="U13" t="s">
+      <c r="X13" t="s">
         <v>204</v>
       </c>
-      <c r="V13" s="5">
-        <v>0</v>
-      </c>
-      <c r="W13" t="s">
+      <c r="Y13" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="s">
         <v>203</v>
       </c>
-      <c r="X13" s="5">
+      <c r="AA13" s="5">
         <v>2</v>
       </c>
-      <c r="Y13" t="s">
+      <c r="AB13" t="s">
         <v>203</v>
       </c>
-      <c r="Z13" t="s">
-        <v>155</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB13" t="s">
+      <c r="AC13" t="s">
+        <v>155</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>155</v>
+      </c>
+      <c r="AE13" t="s">
         <v>157</v>
       </c>
-      <c r="AC13" t="s">
-        <v>155</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>155</v>
-      </c>
-      <c r="AE13" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="AF13" t="s">
+        <v>155</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>155</v>
+      </c>
+      <c r="AH13" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AI13" t="s">
         <v>129</v>
       </c>
-      <c r="AG13">
+      <c r="AJ13">
         <v>49</v>
       </c>
-      <c r="AH13">
+      <c r="AK13" s="16">
+        <v>65</v>
+      </c>
+      <c r="AL13">
         <v>98.54</v>
       </c>
-      <c r="AI13">
+      <c r="AM13">
         <v>88.94</v>
       </c>
-      <c r="AJ13">
+      <c r="AN13">
         <v>17.03</v>
       </c>
-      <c r="AK13" t="s">
+      <c r="AO13" t="s">
         <v>198</v>
       </c>
-      <c r="AL13" t="s">
-        <v>132</v>
-      </c>
-      <c r="AM13" t="s">
-        <v>132</v>
-      </c>
-      <c r="AN13" t="s">
+      <c r="AP13" t="s">
+        <v>132</v>
+      </c>
+      <c r="AQ13" t="s">
+        <v>132</v>
+      </c>
+      <c r="AR13" t="s">
         <v>133</v>
       </c>
-      <c r="AO13">
+      <c r="AS13">
         <v>49</v>
       </c>
-      <c r="AP13">
+      <c r="AT13">
         <v>26.2</v>
       </c>
-      <c r="AQ13">
+      <c r="AU13">
         <v>23.41</v>
       </c>
-      <c r="AR13">
+      <c r="AV13">
         <v>6.14</v>
       </c>
-      <c r="AS13" t="s">
+      <c r="AW13" t="s">
         <v>198</v>
       </c>
-      <c r="AT13" t="s">
-        <v>132</v>
-      </c>
-      <c r="AU13" t="s">
-        <v>132</v>
-      </c>
-      <c r="AV13" t="s">
+      <c r="AX13" t="s">
+        <v>132</v>
+      </c>
+      <c r="AY13" t="s">
+        <v>132</v>
+      </c>
+      <c r="AZ13" t="s">
         <v>134</v>
       </c>
-      <c r="AW13">
+      <c r="BA13">
         <v>49</v>
       </c>
-      <c r="AX13">
+      <c r="BB13">
         <v>23.65</v>
       </c>
-      <c r="AY13">
+      <c r="BC13">
         <v>21.82</v>
       </c>
-      <c r="AZ13">
+      <c r="BD13">
         <v>5.85</v>
       </c>
-      <c r="BA13" t="s">
+      <c r="BE13" t="s">
         <v>198</v>
       </c>
-      <c r="BB13" t="s">
-        <v>132</v>
-      </c>
-      <c r="BC13" t="s">
-        <v>132</v>
-      </c>
-      <c r="BT13" t="s">
+      <c r="BF13" t="s">
+        <v>132</v>
+      </c>
+      <c r="BG13" t="s">
+        <v>132</v>
+      </c>
+      <c r="BX13" t="s">
         <v>199</v>
       </c>
-      <c r="BU13">
+      <c r="BY13">
         <v>49</v>
       </c>
-      <c r="BV13">
+      <c r="BZ13" s="16">
+        <v>65</v>
+      </c>
+      <c r="CA13">
         <v>12.91</v>
       </c>
-      <c r="BW13">
+      <c r="CB13">
         <v>9.8800000000000008</v>
       </c>
-      <c r="BX13">
+      <c r="CC13">
         <v>4.1500000000000004</v>
       </c>
-      <c r="BY13" t="s">
+      <c r="CD13" t="s">
         <v>198</v>
       </c>
-      <c r="BZ13" t="s">
-        <v>132</v>
-      </c>
-      <c r="CA13" t="s">
-        <v>132</v>
-      </c>
-      <c r="CS13">
+      <c r="CE13" t="s">
+        <v>132</v>
+      </c>
+      <c r="CF13" t="s">
+        <v>132</v>
+      </c>
+      <c r="CX13">
         <v>14</v>
       </c>
-      <c r="CT13">
+      <c r="CY13">
         <v>65</v>
       </c>
-      <c r="CW13">
+      <c r="DB13">
         <v>3</v>
       </c>
-      <c r="CX13">
+      <c r="DC13">
         <v>65</v>
       </c>
-      <c r="DA13">
+      <c r="DF13">
         <v>4</v>
       </c>
-      <c r="DB13">
+      <c r="DG13">
         <v>65</v>
       </c>
-      <c r="DC13">
-        <v>0</v>
-      </c>
-      <c r="DD13">
+      <c r="DH13">
+        <v>0</v>
+      </c>
+      <c r="DI13">
         <v>65</v>
       </c>
-      <c r="DK13">
-        <v>0</v>
-      </c>
-      <c r="DL13">
+      <c r="DP13">
+        <v>0</v>
+      </c>
+      <c r="DQ13">
         <v>65</v>
       </c>
-      <c r="DO13">
+      <c r="DT13">
         <v>3</v>
       </c>
-      <c r="DP13">
+      <c r="DU13">
         <v>65</v>
       </c>
-      <c r="DU13">
+      <c r="DZ13">
         <v>2</v>
       </c>
-      <c r="DV13">
+      <c r="EA13">
         <v>65</v>
       </c>
-      <c r="DW13" t="s">
+      <c r="EB13" t="s">
         <v>138</v>
       </c>
-      <c r="DX13" t="s">
+      <c r="EC13" t="s">
         <v>161</v>
       </c>
-      <c r="DY13" t="s">
+      <c r="ED13" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="14" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>205</v>
       </c>
       <c r="B14" t="s">
         <v>192</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="16">
+        <v>2023</v>
+      </c>
+      <c r="E14">
         <v>1</v>
       </c>
-      <c r="D14" t="s">
+      <c r="F14" t="s">
         <v>144</v>
       </c>
-      <c r="E14" t="s">
+      <c r="G14" t="s">
         <v>201</v>
       </c>
-      <c r="F14" t="s">
+      <c r="H14" t="s">
         <v>206</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="I14" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="H14" t="s">
+      <c r="J14" t="s">
         <v>147</v>
       </c>
-      <c r="I14" t="s">
+      <c r="K14" t="s">
         <v>193</v>
       </c>
-      <c r="J14">
+      <c r="L14">
         <v>69</v>
       </c>
-      <c r="K14" t="s">
+      <c r="M14" t="s">
         <v>194</v>
       </c>
-      <c r="L14">
+      <c r="N14">
         <v>15</v>
       </c>
-      <c r="M14">
+      <c r="O14">
         <v>4</v>
       </c>
-      <c r="N14" t="s">
+      <c r="P14" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q14" t="s">
         <v>150</v>
       </c>
-      <c r="O14" t="s">
+      <c r="R14" t="s">
         <v>207</v>
       </c>
-      <c r="R14" t="s">
+      <c r="U14" t="s">
         <v>151</v>
       </c>
-      <c r="S14" t="s">
+      <c r="V14" t="s">
         <v>208</v>
       </c>
-      <c r="T14" t="s">
+      <c r="W14" t="s">
         <v>153</v>
       </c>
-      <c r="U14" t="s">
+      <c r="X14" t="s">
         <v>208</v>
       </c>
-      <c r="V14" t="s">
+      <c r="Y14" t="s">
         <v>128</v>
       </c>
-      <c r="W14" t="s">
+      <c r="Z14" t="s">
         <v>207</v>
       </c>
-      <c r="X14" t="s">
+      <c r="AA14" t="s">
         <v>165</v>
       </c>
-      <c r="Y14" t="s">
+      <c r="AB14" t="s">
         <v>207</v>
       </c>
-      <c r="Z14" t="s">
-        <v>155</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB14" t="s">
+      <c r="AC14" t="s">
+        <v>155</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>155</v>
+      </c>
+      <c r="AE14" t="s">
         <v>157</v>
       </c>
-      <c r="AC14" t="s">
-        <v>155</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>155</v>
-      </c>
-      <c r="AE14" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="AF14" t="s">
+        <v>155</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>155</v>
+      </c>
+      <c r="AH14" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AI14" t="s">
         <v>129</v>
       </c>
-      <c r="AG14">
+      <c r="AJ14">
         <v>51</v>
       </c>
-      <c r="AH14">
+      <c r="AK14" s="16">
+        <v>68</v>
+      </c>
+      <c r="AL14">
         <v>100.53</v>
       </c>
-      <c r="AI14">
+      <c r="AM14">
         <v>85.18</v>
       </c>
-      <c r="AJ14">
+      <c r="AN14">
         <v>17.670000000000002</v>
       </c>
-      <c r="AK14" t="s">
+      <c r="AO14" t="s">
         <v>198</v>
       </c>
-      <c r="AL14" t="s">
-        <v>132</v>
-      </c>
-      <c r="AM14" t="s">
-        <v>132</v>
-      </c>
-      <c r="AN14" t="s">
+      <c r="AP14" t="s">
+        <v>132</v>
+      </c>
+      <c r="AQ14" t="s">
+        <v>132</v>
+      </c>
+      <c r="AR14" t="s">
         <v>133</v>
       </c>
-      <c r="AO14">
+      <c r="AS14">
         <v>51</v>
       </c>
-      <c r="AP14">
+      <c r="AT14">
         <v>27.26</v>
       </c>
-      <c r="AQ14">
+      <c r="AU14">
         <v>22.22</v>
       </c>
-      <c r="AR14">
+      <c r="AV14">
         <v>6.5</v>
       </c>
-      <c r="AS14" t="s">
+      <c r="AW14" t="s">
         <v>198</v>
       </c>
-      <c r="AT14" t="s">
-        <v>132</v>
-      </c>
-      <c r="AU14" t="s">
-        <v>132</v>
-      </c>
-      <c r="AV14" t="s">
+      <c r="AX14" t="s">
+        <v>132</v>
+      </c>
+      <c r="AY14" t="s">
+        <v>132</v>
+      </c>
+      <c r="AZ14" t="s">
         <v>134</v>
       </c>
-      <c r="AW14">
+      <c r="BA14">
         <v>51</v>
       </c>
-      <c r="AX14">
+      <c r="BB14">
         <v>24.59</v>
       </c>
-      <c r="AY14">
+      <c r="BC14">
         <v>22.53</v>
       </c>
-      <c r="AZ14">
+      <c r="BD14">
         <v>5.41</v>
       </c>
-      <c r="BA14" t="s">
+      <c r="BE14" t="s">
         <v>198</v>
       </c>
-      <c r="BB14" t="s">
-        <v>132</v>
-      </c>
-      <c r="BC14" t="s">
-        <v>132</v>
-      </c>
-      <c r="BT14" t="s">
+      <c r="BF14" t="s">
+        <v>132</v>
+      </c>
+      <c r="BG14" t="s">
+        <v>132</v>
+      </c>
+      <c r="BX14" t="s">
         <v>199</v>
       </c>
-      <c r="BU14">
+      <c r="BY14">
         <v>51</v>
       </c>
-      <c r="BV14">
+      <c r="BZ14" s="16">
+        <v>68</v>
+      </c>
+      <c r="CA14">
         <v>11.54</v>
       </c>
-      <c r="BW14">
+      <c r="CB14">
         <v>9.06</v>
       </c>
-      <c r="BX14">
+      <c r="CC14">
         <v>4.08</v>
       </c>
-      <c r="BY14" t="s">
+      <c r="CD14" t="s">
         <v>198</v>
       </c>
-      <c r="BZ14" t="s">
-        <v>132</v>
-      </c>
-      <c r="CA14" t="s">
-        <v>132</v>
-      </c>
-      <c r="CS14">
+      <c r="CE14" t="s">
+        <v>132</v>
+      </c>
+      <c r="CF14" t="s">
+        <v>132</v>
+      </c>
+      <c r="CX14">
         <v>23</v>
       </c>
-      <c r="CT14">
+      <c r="CY14">
         <v>68</v>
       </c>
-      <c r="CW14">
+      <c r="DB14">
         <v>2</v>
       </c>
-      <c r="CX14">
+      <c r="DC14">
         <v>68</v>
       </c>
-      <c r="DA14">
+      <c r="DF14">
         <v>5</v>
       </c>
-      <c r="DB14">
+      <c r="DG14">
         <v>68</v>
       </c>
-      <c r="DC14">
+      <c r="DH14">
         <v>2</v>
       </c>
-      <c r="DD14">
+      <c r="DI14">
         <v>68</v>
       </c>
-      <c r="DK14">
+      <c r="DP14">
         <v>8</v>
       </c>
-      <c r="DL14">
+      <c r="DQ14">
         <v>68</v>
       </c>
-      <c r="DO14">
+      <c r="DT14">
         <v>5</v>
       </c>
-      <c r="DP14">
+      <c r="DU14">
         <v>68</v>
       </c>
-      <c r="DU14">
-        <v>0</v>
-      </c>
-      <c r="DV14">
+      <c r="DZ14">
+        <v>0</v>
+      </c>
+      <c r="EA14">
         <v>68</v>
       </c>
-      <c r="DW14" t="s">
+      <c r="EB14" t="s">
         <v>138</v>
       </c>
-      <c r="DX14" t="s">
+      <c r="EC14" t="s">
         <v>161</v>
       </c>
-      <c r="DY14" t="s">
+      <c r="ED14" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="15" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>209</v>
       </c>
       <c r="B15" t="s">
         <v>192</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="16">
+        <v>2023</v>
+      </c>
+      <c r="E15">
         <v>1</v>
       </c>
-      <c r="D15" t="s">
+      <c r="F15" t="s">
         <v>144</v>
       </c>
-      <c r="E15" t="s">
+      <c r="G15" t="s">
         <v>210</v>
       </c>
-      <c r="F15" t="s">
+      <c r="H15" t="s">
         <v>176</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="I15" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="H15" t="s">
+      <c r="J15" t="s">
         <v>147</v>
       </c>
-      <c r="I15" t="s">
+      <c r="K15" t="s">
         <v>193</v>
       </c>
-      <c r="J15">
+      <c r="L15">
         <v>74</v>
       </c>
-      <c r="K15" t="s">
+      <c r="M15" t="s">
         <v>194</v>
       </c>
-      <c r="L15">
+      <c r="N15">
         <v>18</v>
       </c>
-      <c r="M15">
+      <c r="O15">
         <v>4</v>
       </c>
-      <c r="N15" t="s">
+      <c r="P15" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q15" t="s">
         <v>152</v>
       </c>
-      <c r="O15" t="s">
+      <c r="R15" t="s">
         <v>204</v>
       </c>
-      <c r="R15" t="s">
+      <c r="U15" t="s">
         <v>164</v>
       </c>
-      <c r="S15" t="s">
+      <c r="V15" t="s">
         <v>211</v>
       </c>
-      <c r="T15" t="s">
+      <c r="W15" t="s">
         <v>165</v>
       </c>
-      <c r="U15" t="s">
+      <c r="X15" t="s">
         <v>211</v>
       </c>
-      <c r="V15" t="s">
+      <c r="Y15" t="s">
         <v>128</v>
       </c>
-      <c r="W15" t="s">
+      <c r="Z15" t="s">
         <v>204</v>
       </c>
-      <c r="X15" t="s">
+      <c r="AA15" t="s">
         <v>128</v>
       </c>
-      <c r="Y15" t="s">
+      <c r="AB15" t="s">
         <v>204</v>
       </c>
-      <c r="Z15" t="s">
-        <v>155</v>
-      </c>
-      <c r="AA15" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB15" t="s">
+      <c r="AC15" t="s">
+        <v>155</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>155</v>
+      </c>
+      <c r="AE15" t="s">
         <v>157</v>
       </c>
-      <c r="AC15" t="s">
-        <v>155</v>
-      </c>
-      <c r="AD15" t="s">
-        <v>155</v>
-      </c>
-      <c r="AE15" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="AF15" t="s">
+        <v>155</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>155</v>
+      </c>
+      <c r="AH15" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AI15" t="s">
         <v>129</v>
       </c>
-      <c r="AG15">
+      <c r="AJ15">
         <v>56</v>
       </c>
-      <c r="AH15">
+      <c r="AK15" s="16">
+        <v>71</v>
+      </c>
+      <c r="AL15">
         <v>100.03</v>
       </c>
-      <c r="AI15">
+      <c r="AM15">
         <v>78.040000000000006</v>
       </c>
-      <c r="AJ15">
+      <c r="AN15">
         <v>15.78</v>
       </c>
-      <c r="AK15" t="s">
+      <c r="AO15" t="s">
         <v>198</v>
       </c>
-      <c r="AL15" t="s">
-        <v>132</v>
-      </c>
-      <c r="AM15" t="s">
-        <v>132</v>
-      </c>
-      <c r="AN15" t="s">
+      <c r="AP15" t="s">
+        <v>132</v>
+      </c>
+      <c r="AQ15" t="s">
+        <v>132</v>
+      </c>
+      <c r="AR15" t="s">
         <v>133</v>
       </c>
-      <c r="AO15">
+      <c r="AS15">
         <v>56</v>
       </c>
-      <c r="AP15">
+      <c r="AT15">
         <v>27.49</v>
       </c>
-      <c r="AQ15">
+      <c r="AU15">
         <v>19.52</v>
       </c>
-      <c r="AR15">
+      <c r="AV15">
         <v>5.1100000000000003</v>
       </c>
-      <c r="AS15" t="s">
+      <c r="AW15" t="s">
         <v>198</v>
       </c>
-      <c r="AT15" t="s">
-        <v>132</v>
-      </c>
-      <c r="AU15" t="s">
-        <v>132</v>
-      </c>
-      <c r="AV15" t="s">
+      <c r="AX15" t="s">
+        <v>132</v>
+      </c>
+      <c r="AY15" t="s">
+        <v>132</v>
+      </c>
+      <c r="AZ15" t="s">
         <v>134</v>
       </c>
-      <c r="AW15">
+      <c r="BA15">
         <v>56</v>
       </c>
-      <c r="AX15">
+      <c r="BB15">
         <v>23.65</v>
       </c>
-      <c r="AY15">
+      <c r="BC15">
         <v>21.45</v>
       </c>
-      <c r="AZ15">
+      <c r="BD15">
         <v>5.13</v>
       </c>
-      <c r="BA15" t="s">
+      <c r="BE15" t="s">
         <v>198</v>
       </c>
-      <c r="BB15" t="s">
-        <v>132</v>
-      </c>
-      <c r="BC15" t="s">
-        <v>132</v>
-      </c>
-      <c r="BT15" t="s">
+      <c r="BF15" t="s">
+        <v>132</v>
+      </c>
+      <c r="BG15" t="s">
+        <v>132</v>
+      </c>
+      <c r="BX15" t="s">
         <v>199</v>
       </c>
-      <c r="BU15">
+      <c r="BY15">
         <v>56</v>
       </c>
-      <c r="BV15">
+      <c r="BZ15" s="16">
+        <v>71</v>
+      </c>
+      <c r="CA15">
         <v>12.58</v>
       </c>
-      <c r="BW15">
+      <c r="CB15">
         <v>8.5</v>
       </c>
-      <c r="BX15">
+      <c r="CC15">
         <v>4.09</v>
       </c>
-      <c r="BY15" t="s">
+      <c r="CD15" t="s">
         <v>198</v>
       </c>
-      <c r="BZ15" t="s">
-        <v>132</v>
-      </c>
-      <c r="CA15" t="s">
-        <v>132</v>
-      </c>
-      <c r="CS15">
+      <c r="CE15" t="s">
+        <v>132</v>
+      </c>
+      <c r="CF15" t="s">
+        <v>132</v>
+      </c>
+      <c r="CX15">
         <v>36</v>
       </c>
-      <c r="CT15">
+      <c r="CY15">
         <v>71</v>
       </c>
-      <c r="CW15">
+      <c r="DB15">
         <v>5</v>
       </c>
-      <c r="CX15">
+      <c r="DC15">
         <v>71</v>
       </c>
-      <c r="DA15">
+      <c r="DF15">
         <v>6</v>
       </c>
-      <c r="DB15">
+      <c r="DG15">
         <v>71</v>
       </c>
-      <c r="DC15">
+      <c r="DH15">
         <v>6</v>
       </c>
-      <c r="DD15">
+      <c r="DI15">
         <v>71</v>
       </c>
-      <c r="DK15">
-        <v>0</v>
-      </c>
-      <c r="DL15">
+      <c r="DP15">
+        <v>0</v>
+      </c>
+      <c r="DQ15">
         <v>71</v>
       </c>
-      <c r="DO15">
+      <c r="DT15">
         <v>5</v>
       </c>
-      <c r="DP15">
+      <c r="DU15">
         <v>71</v>
       </c>
-      <c r="DU15">
+      <c r="DZ15">
         <v>8</v>
       </c>
-      <c r="DV15">
+      <c r="EA15">
         <v>71</v>
       </c>
-      <c r="DW15" t="s">
+      <c r="EB15" t="s">
         <v>212</v>
       </c>
-      <c r="DX15" t="s">
+      <c r="EC15" t="s">
         <v>161</v>
       </c>
-      <c r="DY15" t="s">
+      <c r="ED15" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="16" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>213</v>
       </c>
       <c r="B16" t="s">
         <v>214</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>278</v>
+      </c>
+      <c r="E16">
         <v>1</v>
       </c>
-      <c r="D16" t="s">
+      <c r="F16" t="s">
         <v>144</v>
       </c>
-      <c r="E16" t="s">
+      <c r="G16" t="s">
         <v>162</v>
       </c>
-      <c r="F16" t="s">
+      <c r="H16" t="s">
         <v>128</v>
       </c>
-      <c r="G16" t="s">
+      <c r="I16" t="s">
         <v>215</v>
       </c>
-      <c r="I16" t="s">
+      <c r="K16" t="s">
         <v>216</v>
       </c>
-      <c r="J16">
+      <c r="L16">
         <v>34</v>
       </c>
-      <c r="K16" t="s">
+      <c r="M16" t="s">
         <v>217</v>
       </c>
-      <c r="L16">
+      <c r="N16">
         <v>18</v>
       </c>
-      <c r="M16">
+      <c r="O16">
         <v>0.14000000000000001</v>
       </c>
-      <c r="R16" t="s">
+      <c r="P16" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="U16" t="s">
         <v>154</v>
       </c>
-      <c r="S16" t="s">
+      <c r="V16" t="s">
         <v>218</v>
       </c>
-      <c r="T16" t="s">
+      <c r="W16" t="s">
         <v>128</v>
       </c>
-      <c r="U16" t="s">
+      <c r="X16" t="s">
         <v>218</v>
       </c>
-      <c r="V16" t="s">
+      <c r="Y16" t="s">
         <v>128</v>
       </c>
-      <c r="W16" t="s">
+      <c r="Z16" t="s">
         <v>218</v>
       </c>
-      <c r="X16" t="s">
+      <c r="AA16" t="s">
         <v>128</v>
       </c>
-      <c r="Y16" t="s">
+      <c r="AB16" t="s">
         <v>218</v>
       </c>
-      <c r="CS16">
+      <c r="CX16">
         <v>16</v>
       </c>
-      <c r="CT16">
+      <c r="CY16">
         <v>34</v>
       </c>
-      <c r="CU16">
-        <v>0</v>
-      </c>
-      <c r="CV16">
+      <c r="CZ16">
+        <v>0</v>
+      </c>
+      <c r="DA16">
         <v>34</v>
       </c>
-      <c r="CW16">
-        <v>0</v>
-      </c>
-      <c r="CX16">
+      <c r="DB16">
+        <v>0</v>
+      </c>
+      <c r="DC16">
         <v>34</v>
       </c>
-      <c r="CY16">
+      <c r="DD16">
         <v>2</v>
       </c>
-      <c r="CZ16">
+      <c r="DE16">
         <v>34</v>
       </c>
-      <c r="DA16">
+      <c r="DF16">
         <v>7</v>
       </c>
-      <c r="DB16">
+      <c r="DG16">
         <v>34</v>
       </c>
-      <c r="DC16">
-        <v>0</v>
-      </c>
-      <c r="DD16">
+      <c r="DH16">
+        <v>0</v>
+      </c>
+      <c r="DI16">
         <v>34</v>
       </c>
-      <c r="DE16">
+      <c r="DJ16">
         <v>5</v>
       </c>
-      <c r="DF16">
+      <c r="DK16">
         <v>34</v>
       </c>
-      <c r="DW16" t="s">
+      <c r="EB16" t="s">
         <v>162</v>
       </c>
-      <c r="DX16" t="s">
+      <c r="EC16" t="s">
         <v>219</v>
       </c>
-      <c r="DY16" t="s">
+      <c r="ED16" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="17" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>220</v>
       </c>
       <c r="B17" t="s">
         <v>214</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="E17">
         <v>1</v>
       </c>
-      <c r="D17" t="s">
+      <c r="F17" t="s">
         <v>144</v>
       </c>
-      <c r="E17" t="s">
+      <c r="G17" t="s">
         <v>127</v>
       </c>
-      <c r="F17" t="s">
+      <c r="H17" t="s">
         <v>179</v>
       </c>
-      <c r="G17" t="s">
+      <c r="I17" t="s">
         <v>215</v>
       </c>
-      <c r="I17" t="s">
+      <c r="K17" t="s">
         <v>216</v>
       </c>
-      <c r="J17">
+      <c r="L17">
         <v>35</v>
       </c>
-      <c r="K17" t="s">
+      <c r="M17" t="s">
         <v>221</v>
       </c>
-      <c r="L17">
+      <c r="N17">
         <v>14</v>
       </c>
-      <c r="M17">
+      <c r="O17">
         <v>0.14000000000000001</v>
       </c>
-      <c r="R17" t="s">
+      <c r="P17" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="U17" t="s">
         <v>153</v>
       </c>
-      <c r="S17" t="s">
+      <c r="V17" t="s">
         <v>222</v>
       </c>
-      <c r="T17" t="s">
+      <c r="W17" t="s">
         <v>128</v>
       </c>
-      <c r="U17" t="s">
+      <c r="X17" t="s">
         <v>222</v>
       </c>
-      <c r="V17" t="s">
+      <c r="Y17" t="s">
         <v>128</v>
       </c>
-      <c r="W17" t="s">
+      <c r="Z17" t="s">
         <v>222</v>
       </c>
-      <c r="X17" t="s">
+      <c r="AA17" t="s">
         <v>165</v>
       </c>
-      <c r="Y17" t="s">
+      <c r="AB17" t="s">
         <v>222</v>
       </c>
-      <c r="CS17">
+      <c r="CX17">
         <v>34</v>
       </c>
-      <c r="CT17">
+      <c r="CY17">
         <v>35</v>
       </c>
-      <c r="CU17">
+      <c r="CZ17">
         <v>5</v>
       </c>
-      <c r="CV17">
+      <c r="DA17">
         <v>35</v>
       </c>
-      <c r="CW17">
-        <v>0</v>
-      </c>
-      <c r="CX17">
+      <c r="DB17">
+        <v>0</v>
+      </c>
+      <c r="DC17">
         <v>35</v>
       </c>
-      <c r="CY17">
+      <c r="DD17">
         <v>10</v>
       </c>
-      <c r="CZ17">
+      <c r="DE17">
         <v>35</v>
       </c>
-      <c r="DA17">
+      <c r="DF17">
         <v>4</v>
       </c>
-      <c r="DB17">
+      <c r="DG17">
         <v>35</v>
       </c>
-      <c r="DC17">
+      <c r="DH17">
         <v>12</v>
       </c>
-      <c r="DD17">
+      <c r="DI17">
         <v>35</v>
       </c>
-      <c r="DE17">
+      <c r="DJ17">
         <v>21</v>
       </c>
-      <c r="DF17">
+      <c r="DK17">
         <v>35</v>
       </c>
-      <c r="DW17" t="s">
+      <c r="EB17" t="s">
         <v>138</v>
       </c>
-      <c r="DX17" t="s">
+      <c r="EC17" t="s">
         <v>219</v>
       </c>
-      <c r="DY17" t="s">
+      <c r="ED17" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="18" spans="1:129" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:134" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>223</v>
       </c>
       <c r="B18" t="s">
         <v>214</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="E18">
         <v>1</v>
       </c>
-      <c r="D18" t="s">
+      <c r="F18" t="s">
         <v>144</v>
       </c>
-      <c r="E18" t="s">
+      <c r="G18" t="s">
         <v>224</v>
       </c>
-      <c r="F18" t="s">
+      <c r="H18" t="s">
         <v>225</v>
       </c>
-      <c r="G18" t="s">
+      <c r="I18" t="s">
         <v>215</v>
       </c>
-      <c r="I18" t="s">
+      <c r="K18" t="s">
         <v>216</v>
       </c>
-      <c r="J18">
+      <c r="L18">
         <v>36</v>
       </c>
-      <c r="K18" t="s">
+      <c r="M18" t="s">
         <v>226</v>
       </c>
-      <c r="L18">
+      <c r="N18">
         <v>13</v>
       </c>
-      <c r="M18">
+      <c r="O18">
         <v>0.14000000000000001</v>
       </c>
-      <c r="R18" t="s">
+      <c r="P18" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="U18" t="s">
         <v>154</v>
       </c>
-      <c r="S18" t="s">
+      <c r="V18" t="s">
         <v>227</v>
       </c>
-      <c r="T18" t="s">
+      <c r="W18" t="s">
         <v>128</v>
       </c>
-      <c r="U18" t="s">
+      <c r="X18" t="s">
         <v>227</v>
       </c>
-      <c r="V18" t="s">
+      <c r="Y18" t="s">
         <v>128</v>
       </c>
-      <c r="W18" t="s">
+      <c r="Z18" t="s">
         <v>227</v>
       </c>
-      <c r="X18" t="s">
+      <c r="AA18" t="s">
         <v>128</v>
       </c>
-      <c r="Y18" t="s">
+      <c r="AB18" t="s">
         <v>227</v>
       </c>
-      <c r="CS18">
+      <c r="CX18">
         <v>15</v>
       </c>
-      <c r="CT18">
+      <c r="CY18">
         <v>36</v>
       </c>
-      <c r="CU18">
-        <v>0</v>
-      </c>
-      <c r="CV18">
+      <c r="CZ18">
+        <v>0</v>
+      </c>
+      <c r="DA18">
         <v>36</v>
       </c>
-      <c r="CW18">
+      <c r="DB18">
         <v>3</v>
       </c>
-      <c r="CX18">
+      <c r="DC18">
         <v>36</v>
       </c>
-      <c r="CY18">
+      <c r="DD18">
         <v>1</v>
       </c>
-      <c r="CZ18">
+      <c r="DE18">
         <v>36</v>
       </c>
-      <c r="DA18">
+      <c r="DF18">
         <v>1</v>
       </c>
-      <c r="DB18">
+      <c r="DG18">
         <v>36</v>
       </c>
-      <c r="DC18">
-        <v>0</v>
-      </c>
-      <c r="DD18">
+      <c r="DH18">
+        <v>0</v>
+      </c>
+      <c r="DI18">
         <v>36</v>
       </c>
-      <c r="DE18">
+      <c r="DJ18">
         <v>5</v>
       </c>
-      <c r="DF18">
+      <c r="DK18">
         <v>36</v>
       </c>
-      <c r="DW18" t="s">
+      <c r="EB18" t="s">
         <v>212</v>
       </c>
-      <c r="DX18" t="s">
+      <c r="EC18" t="s">
         <v>219</v>
       </c>
-      <c r="DY18" t="s">
+      <c r="ED18" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="19" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>162</v>
       </c>
       <c r="B19" t="s">
         <v>228</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="E19">
         <v>1</v>
       </c>
-      <c r="D19" t="s">
+      <c r="F19" t="s">
         <v>229</v>
       </c>
-      <c r="E19" t="s">
+      <c r="G19" t="s">
         <v>162</v>
       </c>
-      <c r="F19" t="s">
+      <c r="H19" t="s">
         <v>128</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="I19" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="H19" t="s">
+      <c r="J19" t="s">
         <v>230</v>
       </c>
-      <c r="I19" t="s">
+      <c r="K19" t="s">
         <v>207</v>
       </c>
-      <c r="J19">
+      <c r="L19">
         <v>68</v>
       </c>
-      <c r="K19" t="s">
+      <c r="M19" t="s">
         <v>231</v>
       </c>
-      <c r="L19">
+      <c r="N19">
         <v>15</v>
       </c>
-      <c r="M19">
+      <c r="O19">
         <v>0.14000000000000001</v>
       </c>
-      <c r="T19" t="s">
+      <c r="P19" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="W19" t="s">
         <v>165</v>
       </c>
-      <c r="U19" t="s">
+      <c r="X19" t="s">
         <v>232</v>
       </c>
-      <c r="V19" t="s">
+      <c r="Y19" t="s">
         <v>128</v>
       </c>
-      <c r="W19" t="s">
+      <c r="Z19" t="s">
         <v>232</v>
       </c>
-      <c r="X19" t="s">
+      <c r="AA19" t="s">
         <v>128</v>
       </c>
-      <c r="Y19" t="s">
+      <c r="AB19" t="s">
         <v>232</v>
       </c>
-      <c r="CS19">
+      <c r="CX19">
         <v>2</v>
       </c>
-      <c r="CT19">
+      <c r="CY19">
         <v>63</v>
       </c>
-      <c r="CY19">
+      <c r="DD19">
         <v>1</v>
       </c>
-      <c r="CZ19">
+      <c r="DE19">
         <v>63</v>
       </c>
-      <c r="DC19">
+      <c r="DH19">
         <v>1</v>
       </c>
-      <c r="DD19">
+      <c r="DI19">
         <v>63</v>
       </c>
-      <c r="DE19" s="8">
-        <v>0</v>
-      </c>
-      <c r="DF19">
+      <c r="DJ19" s="8">
+        <v>0</v>
+      </c>
+      <c r="DK19">
         <v>63</v>
       </c>
-      <c r="DI19">
+      <c r="DN19">
         <v>1</v>
       </c>
-      <c r="DJ19">
+      <c r="DO19">
         <v>59</v>
       </c>
-      <c r="DW19" t="s">
+      <c r="EB19" t="s">
         <v>162</v>
       </c>
-      <c r="DX19" t="s">
+      <c r="EC19" t="s">
         <v>219</v>
       </c>
-      <c r="DY19" t="s">
+      <c r="ED19" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="20" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>233</v>
       </c>
       <c r="B20" t="s">
         <v>228</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="E20">
         <v>1</v>
       </c>
-      <c r="D20" t="s">
+      <c r="F20" t="s">
         <v>229</v>
       </c>
-      <c r="E20" t="s">
+      <c r="G20" t="s">
         <v>127</v>
       </c>
-      <c r="F20" t="s">
+      <c r="H20" t="s">
         <v>206</v>
       </c>
-      <c r="G20" s="10" t="s">
+      <c r="I20" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="H20" t="s">
+      <c r="J20" t="s">
         <v>230</v>
       </c>
-      <c r="I20" t="s">
+      <c r="K20" t="s">
         <v>207</v>
       </c>
-      <c r="J20">
+      <c r="L20">
         <v>68</v>
       </c>
-      <c r="K20" t="s">
+      <c r="M20" t="s">
         <v>231</v>
       </c>
-      <c r="L20">
+      <c r="N20">
         <v>15</v>
       </c>
-      <c r="M20">
+      <c r="O20">
         <v>0.14000000000000001</v>
       </c>
-      <c r="R20" t="s">
+      <c r="P20" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="U20" t="s">
         <v>128</v>
       </c>
-      <c r="S20" t="s">
+      <c r="V20" t="s">
         <v>232</v>
       </c>
-      <c r="T20" t="s">
+      <c r="W20" t="s">
         <v>128</v>
       </c>
-      <c r="U20" t="s">
+      <c r="X20" t="s">
         <v>232</v>
       </c>
-      <c r="V20" t="s">
+      <c r="Y20" t="s">
         <v>128</v>
       </c>
-      <c r="W20" t="s">
+      <c r="Z20" t="s">
         <v>232</v>
       </c>
-      <c r="X20" t="s">
+      <c r="AA20" t="s">
         <v>165</v>
       </c>
-      <c r="Y20" t="s">
+      <c r="AB20" t="s">
         <v>232</v>
       </c>
-      <c r="CS20">
+      <c r="CX20">
         <v>32</v>
       </c>
-      <c r="CT20">
+      <c r="CY20">
         <v>63</v>
       </c>
-      <c r="CY20">
+      <c r="DD20">
         <v>7</v>
       </c>
-      <c r="CZ20">
+      <c r="DE20">
         <v>63</v>
       </c>
-      <c r="DC20">
+      <c r="DH20">
         <v>16</v>
       </c>
-      <c r="DD20">
+      <c r="DI20">
         <v>63</v>
       </c>
-      <c r="DE20">
+      <c r="DJ20">
         <v>16</v>
       </c>
-      <c r="DF20">
+      <c r="DK20">
         <v>63</v>
       </c>
-      <c r="DI20">
+      <c r="DN20">
         <v>5</v>
       </c>
-      <c r="DJ20">
+      <c r="DO20">
         <v>62</v>
       </c>
-      <c r="DW20" t="s">
+      <c r="EB20" t="s">
         <v>138</v>
       </c>
-      <c r="DX20" t="s">
+      <c r="EC20" t="s">
         <v>219</v>
       </c>
-      <c r="DY20" t="s">
+      <c r="ED20" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="21" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>234</v>
       </c>
       <c r="B21" t="s">
         <v>235</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="16">
+        <v>2021</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>274</v>
+      </c>
+      <c r="E21">
         <v>1</v>
       </c>
-      <c r="D21" t="s">
+      <c r="F21" t="s">
         <v>229</v>
       </c>
-      <c r="E21" t="s">
+      <c r="G21" t="s">
         <v>127</v>
       </c>
-      <c r="F21" t="s">
+      <c r="H21" t="s">
         <v>152</v>
       </c>
-      <c r="G21" t="s">
+      <c r="I21" t="s">
         <v>215</v>
       </c>
-      <c r="I21" t="s">
+      <c r="K21" t="s">
         <v>190</v>
       </c>
-      <c r="J21">
+      <c r="L21">
         <v>12</v>
       </c>
-      <c r="K21" t="s">
+      <c r="M21" t="s">
         <v>236</v>
       </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
         <v>0.14000000000000001</v>
       </c>
-      <c r="R21" t="s">
+      <c r="P21" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="U21" t="s">
         <v>128</v>
       </c>
-      <c r="S21" t="s">
+      <c r="V21" t="s">
         <v>140</v>
       </c>
-      <c r="T21" t="s">
+      <c r="W21" t="s">
         <v>128</v>
       </c>
-      <c r="U21" t="s">
+      <c r="X21" t="s">
         <v>140</v>
       </c>
-      <c r="V21" t="s">
+      <c r="Y21" t="s">
         <v>128</v>
       </c>
-      <c r="W21" t="s">
+      <c r="Z21" t="s">
         <v>140</v>
       </c>
-      <c r="X21" t="s">
+      <c r="AA21" t="s">
         <v>128</v>
       </c>
-      <c r="Y21" t="s">
+      <c r="AB21" t="s">
         <v>140</v>
       </c>
-      <c r="CS21">
+      <c r="CX21">
         <v>1</v>
       </c>
-      <c r="CT21">
+      <c r="CY21">
         <v>12</v>
       </c>
-      <c r="DC21">
+      <c r="DH21">
         <v>1</v>
       </c>
-      <c r="DD21">
+      <c r="DI21">
         <v>12</v>
       </c>
-      <c r="DE21">
-        <v>0</v>
-      </c>
-      <c r="DF21">
+      <c r="DJ21">
+        <v>0</v>
+      </c>
+      <c r="DK21">
         <v>12</v>
       </c>
-      <c r="DG21">
-        <v>0</v>
-      </c>
-      <c r="DH21">
+      <c r="DL21">
+        <v>0</v>
+      </c>
+      <c r="DM21">
         <v>12</v>
       </c>
-      <c r="DI21">
-        <v>0</v>
-      </c>
-      <c r="DJ21">
+      <c r="DN21">
+        <v>0</v>
+      </c>
+      <c r="DO21">
         <v>12</v>
       </c>
-      <c r="DW21" t="s">
+      <c r="EB21" t="s">
         <v>138</v>
       </c>
-      <c r="DX21" t="s">
+      <c r="EC21" t="s">
         <v>219</v>
       </c>
-      <c r="DY21" t="s">
+      <c r="ED21" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="22" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>237</v>
       </c>
       <c r="B22" t="s">
         <v>235</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="16">
+        <v>2021</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>274</v>
+      </c>
+      <c r="E22">
         <v>1</v>
       </c>
-      <c r="D22" t="s">
+      <c r="F22" t="s">
         <v>229</v>
       </c>
-      <c r="E22" t="s">
+      <c r="G22" t="s">
         <v>127</v>
       </c>
-      <c r="F22" t="s">
+      <c r="H22" t="s">
         <v>179</v>
       </c>
-      <c r="G22" t="s">
+      <c r="I22" t="s">
         <v>215</v>
       </c>
-      <c r="I22" t="s">
+      <c r="K22" t="s">
         <v>190</v>
       </c>
-      <c r="J22">
+      <c r="L22">
         <v>12</v>
       </c>
-      <c r="K22" t="s">
+      <c r="M22" t="s">
         <v>236</v>
       </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
         <v>0.14000000000000001</v>
       </c>
-      <c r="R22" t="s">
+      <c r="P22" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="U22" t="s">
         <v>128</v>
       </c>
-      <c r="S22" t="s">
+      <c r="V22" t="s">
         <v>140</v>
       </c>
-      <c r="T22" t="s">
+      <c r="W22" t="s">
         <v>128</v>
       </c>
-      <c r="U22" t="s">
+      <c r="X22" t="s">
         <v>140</v>
       </c>
-      <c r="V22" t="s">
+      <c r="Y22" t="s">
         <v>128</v>
       </c>
-      <c r="W22" t="s">
+      <c r="Z22" t="s">
         <v>140</v>
       </c>
-      <c r="X22" t="s">
+      <c r="AA22" t="s">
         <v>128</v>
       </c>
-      <c r="Y22" t="s">
+      <c r="AB22" t="s">
         <v>140</v>
       </c>
-      <c r="CS22">
+      <c r="CX22">
         <v>1</v>
       </c>
-      <c r="CT22">
+      <c r="CY22">
         <v>12</v>
       </c>
-      <c r="DC22">
-        <v>0</v>
-      </c>
-      <c r="DD22">
+      <c r="DH22">
+        <v>0</v>
+      </c>
+      <c r="DI22">
         <v>12</v>
       </c>
-      <c r="DE22">
+      <c r="DJ22">
         <v>1</v>
       </c>
-      <c r="DF22">
+      <c r="DK22">
         <v>12</v>
       </c>
-      <c r="DG22">
-        <v>0</v>
-      </c>
-      <c r="DH22">
+      <c r="DL22">
+        <v>0</v>
+      </c>
+      <c r="DM22">
         <v>12</v>
       </c>
-      <c r="DI22">
-        <v>0</v>
-      </c>
-      <c r="DJ22">
+      <c r="DN22">
+        <v>0</v>
+      </c>
+      <c r="DO22">
         <v>12</v>
       </c>
-      <c r="DW22" t="s">
+      <c r="EB22" t="s">
         <v>138</v>
       </c>
-      <c r="DX22" t="s">
+      <c r="EC22" t="s">
         <v>219</v>
       </c>
-      <c r="DY22" t="s">
+      <c r="ED22" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="23" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>162</v>
       </c>
       <c r="B23" t="s">
         <v>235</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="16">
+        <v>2021</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>274</v>
+      </c>
+      <c r="E23">
         <v>1</v>
       </c>
-      <c r="D23" t="s">
+      <c r="F23" t="s">
         <v>229</v>
       </c>
-      <c r="E23" t="s">
+      <c r="G23" t="s">
         <v>162</v>
       </c>
-      <c r="F23" t="s">
+      <c r="H23" t="s">
         <v>128</v>
       </c>
-      <c r="G23" t="s">
+      <c r="I23" t="s">
         <v>215</v>
       </c>
-      <c r="I23" t="s">
+      <c r="K23" t="s">
         <v>190</v>
       </c>
-      <c r="J23">
+      <c r="L23">
         <v>24</v>
       </c>
-      <c r="K23" t="s">
+      <c r="M23" t="s">
         <v>236</v>
       </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
         <v>0.14000000000000001</v>
       </c>
-      <c r="R23" t="s">
+      <c r="P23" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="U23" t="s">
         <v>128</v>
       </c>
-      <c r="S23" t="s">
+      <c r="V23" t="s">
         <v>190</v>
       </c>
-      <c r="T23" t="s">
+      <c r="W23" t="s">
         <v>128</v>
       </c>
-      <c r="U23" t="s">
+      <c r="X23" t="s">
         <v>190</v>
       </c>
-      <c r="V23" t="s">
+      <c r="Y23" t="s">
         <v>128</v>
       </c>
-      <c r="W23" t="s">
+      <c r="Z23" t="s">
         <v>190</v>
       </c>
-      <c r="X23" t="s">
+      <c r="AA23" t="s">
         <v>128</v>
       </c>
-      <c r="Y23" t="s">
+      <c r="AB23" t="s">
         <v>190</v>
       </c>
-      <c r="CS23">
+      <c r="CX23">
         <v>1</v>
       </c>
-      <c r="CT23">
+      <c r="CY23">
         <v>24</v>
       </c>
-      <c r="DC23">
-        <v>0</v>
-      </c>
-      <c r="DD23">
+      <c r="DH23">
+        <v>0</v>
+      </c>
+      <c r="DI23">
         <v>24</v>
       </c>
-      <c r="DE23">
-        <v>0</v>
-      </c>
-      <c r="DF23">
+      <c r="DJ23">
+        <v>0</v>
+      </c>
+      <c r="DK23">
         <v>24</v>
       </c>
-      <c r="DG23">
-        <v>0</v>
-      </c>
-      <c r="DH23">
+      <c r="DL23">
+        <v>0</v>
+      </c>
+      <c r="DM23">
         <v>24</v>
       </c>
-      <c r="DI23">
-        <v>0</v>
-      </c>
-      <c r="DJ23">
+      <c r="DN23">
+        <v>0</v>
+      </c>
+      <c r="DO23">
         <v>24</v>
       </c>
-      <c r="DW23" t="s">
+      <c r="EB23" t="s">
         <v>162</v>
       </c>
-      <c r="DX23" t="s">
+      <c r="EC23" t="s">
         <v>219</v>
       </c>
-      <c r="DY23" t="s">
+      <c r="ED23" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="24" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>237</v>
       </c>
       <c r="B24" t="s">
         <v>238</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>273</v>
+      </c>
+      <c r="E24">
         <v>1</v>
       </c>
-      <c r="D24" t="s">
+      <c r="F24" t="s">
         <v>229</v>
       </c>
-      <c r="E24" t="s">
+      <c r="G24" t="s">
         <v>127</v>
       </c>
-      <c r="F24" t="s">
+      <c r="H24" t="s">
         <v>179</v>
       </c>
-      <c r="G24" t="s">
+      <c r="I24" t="s">
         <v>239</v>
       </c>
-      <c r="I24" t="s">
+      <c r="K24" t="s">
         <v>151</v>
       </c>
-      <c r="J24">
+      <c r="L24">
         <v>16</v>
       </c>
-      <c r="K24" t="s">
+      <c r="M24" t="s">
         <v>240</v>
       </c>
-      <c r="L24">
+      <c r="N24">
         <v>12</v>
       </c>
-      <c r="M24">
+      <c r="O24">
         <v>2</v>
       </c>
-      <c r="V24" t="s">
+      <c r="P24" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="Y24" t="s">
         <v>128</v>
       </c>
-      <c r="W24" t="s">
+      <c r="Z24" t="s">
         <v>151</v>
       </c>
-      <c r="X24" t="s">
+      <c r="AA24" t="s">
         <v>128</v>
       </c>
-      <c r="Y24" t="s">
+      <c r="AB24" t="s">
         <v>151</v>
       </c>
-      <c r="CS24" s="6">
+      <c r="CX24" s="6">
         <v>6</v>
       </c>
-      <c r="CT24" s="6">
+      <c r="CY24" s="6">
         <v>15</v>
       </c>
-      <c r="DW24" t="s">
+      <c r="EB24" t="s">
         <v>138</v>
       </c>
-      <c r="DX24" t="s">
+      <c r="EC24" t="s">
         <v>219</v>
       </c>
-      <c r="DY24" t="s">
+      <c r="ED24" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="25" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>241</v>
       </c>
       <c r="B25" t="s">
         <v>238</v>
       </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="C25" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>273</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25" t="s">
         <v>229</v>
       </c>
-      <c r="E25" t="s">
+      <c r="G25" t="s">
         <v>127</v>
       </c>
-      <c r="F25" t="s">
+      <c r="H25" t="s">
         <v>141</v>
       </c>
-      <c r="G25" t="s">
+      <c r="I25" t="s">
         <v>239</v>
       </c>
-      <c r="I25" t="s">
+      <c r="K25" t="s">
         <v>151</v>
       </c>
-      <c r="J25">
+      <c r="L25">
         <v>16</v>
       </c>
-      <c r="K25" t="s">
+      <c r="M25" t="s">
         <v>240</v>
       </c>
-      <c r="L25">
+      <c r="N25">
         <v>12</v>
       </c>
-      <c r="M25">
+      <c r="O25">
         <v>2</v>
       </c>
-      <c r="V25" t="s">
+      <c r="P25" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="Y25" t="s">
         <v>128</v>
       </c>
-      <c r="W25" t="s">
+      <c r="Z25" t="s">
         <v>151</v>
       </c>
-      <c r="X25" t="s">
+      <c r="AA25" t="s">
         <v>128</v>
       </c>
-      <c r="Y25" t="s">
+      <c r="AB25" t="s">
         <v>151</v>
       </c>
-      <c r="CS25" s="6">
+      <c r="CX25" s="6">
         <v>1</v>
       </c>
-      <c r="CT25" s="6">
+      <c r="CY25" s="6">
         <v>13</v>
       </c>
-      <c r="DW25" t="s">
+      <c r="EB25" t="s">
         <v>138</v>
       </c>
-      <c r="DX25" t="s">
+      <c r="EC25" t="s">
         <v>219</v>
       </c>
-      <c r="DY25" t="s">
+      <c r="ED25" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="26" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>162</v>
       </c>
       <c r="B26" t="s">
         <v>238</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>273</v>
+      </c>
+      <c r="E26">
         <v>1</v>
       </c>
-      <c r="D26" t="s">
+      <c r="F26" t="s">
         <v>229</v>
       </c>
-      <c r="E26" t="s">
+      <c r="G26" t="s">
         <v>162</v>
       </c>
-      <c r="F26" t="s">
+      <c r="H26" t="s">
         <v>128</v>
       </c>
-      <c r="G26" t="s">
+      <c r="I26" t="s">
         <v>239</v>
       </c>
-      <c r="I26" t="s">
+      <c r="K26" t="s">
         <v>151</v>
       </c>
-      <c r="J26">
+      <c r="L26">
         <v>16</v>
       </c>
-      <c r="K26" t="s">
+      <c r="M26" t="s">
         <v>240</v>
       </c>
-      <c r="L26">
+      <c r="N26">
         <v>12</v>
       </c>
-      <c r="M26">
+      <c r="O26">
         <v>2</v>
       </c>
-      <c r="V26" t="s">
+      <c r="P26" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="Y26" t="s">
         <v>128</v>
       </c>
-      <c r="W26" t="s">
+      <c r="Z26" t="s">
         <v>151</v>
       </c>
-      <c r="X26" t="s">
+      <c r="AA26" t="s">
         <v>128</v>
       </c>
-      <c r="Y26" t="s">
+      <c r="AB26" t="s">
         <v>151</v>
       </c>
-      <c r="CS26" s="6">
+      <c r="CX26" s="6">
         <v>2</v>
       </c>
-      <c r="CT26" s="6">
+      <c r="CY26" s="6">
         <v>14</v>
       </c>
-      <c r="DW26" t="s">
+      <c r="EB26" t="s">
         <v>162</v>
       </c>
-      <c r="DX26" t="s">
+      <c r="EC26" t="s">
         <v>219</v>
       </c>
-      <c r="DY26" t="s">
+      <c r="ED26" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="27" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A27" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B27" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="C27" s="10">
+      <c r="C27" s="16">
+        <v>2024</v>
+      </c>
+      <c r="E27" s="10">
         <v>1</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="F27" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="G27" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="H27" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="G27" s="10" t="s">
+      <c r="I27" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="H27" s="10" t="s">
+      <c r="J27" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I27" s="11">
+      <c r="K27" s="11">
         <v>303</v>
       </c>
-      <c r="J27" s="10">
+      <c r="L27" s="10">
         <v>201</v>
       </c>
-      <c r="K27" s="10" t="s">
+      <c r="M27" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="M27" s="10">
+      <c r="O27" s="10">
         <v>52</v>
       </c>
-      <c r="P27" s="10">
+      <c r="P27" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="S27" s="10">
         <v>29</v>
       </c>
-      <c r="Q27" s="10">
+      <c r="T27" s="10">
         <v>201</v>
       </c>
-      <c r="R27" s="10">
+      <c r="U27" s="10">
         <v>96</v>
       </c>
-      <c r="S27" s="10">
+      <c r="V27" s="10">
         <v>201</v>
       </c>
-      <c r="T27" s="11">
+      <c r="W27" s="11">
         <v>44</v>
       </c>
-      <c r="U27" s="11">
+      <c r="X27" s="11">
         <v>201</v>
-      </c>
-      <c r="Z27" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="AA27" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB27" s="11" t="s">
-        <v>156</v>
       </c>
       <c r="AC27" s="11" t="s">
         <v>155</v>
@@ -5408,133 +5734,139 @@
       <c r="AE27" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="CB27" s="10" t="s">
+      <c r="AF27" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="AG27" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="AH27" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="CG27" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="CC27" s="10">
+      <c r="CH27" s="10">
         <v>201</v>
       </c>
-      <c r="CE27" s="10">
+      <c r="CJ27" s="10">
         <v>-1.2</v>
       </c>
-      <c r="CF27" s="11">
+      <c r="CK27" s="11">
         <v>6.4</v>
       </c>
-      <c r="CG27" s="10" t="s">
+      <c r="CL27" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="CH27" s="10" t="s">
+      <c r="CM27" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="CI27" s="10" t="s">
+      <c r="CN27" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="CJ27" s="10" t="s">
+      <c r="CO27" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="CU27" s="11">
+      <c r="CZ27" s="11">
         <v>7</v>
       </c>
-      <c r="CV27" s="11">
+      <c r="DA27" s="11">
         <v>201</v>
       </c>
-      <c r="CW27" s="11">
+      <c r="DB27" s="11">
         <v>28</v>
       </c>
-      <c r="CX27" s="11">
+      <c r="DC27" s="11">
         <v>201</v>
       </c>
-      <c r="DE27" s="11">
+      <c r="DJ27" s="11">
         <v>12</v>
       </c>
-      <c r="DF27" s="11">
+      <c r="DK27" s="11">
         <v>201</v>
       </c>
-      <c r="DO27" s="10">
+      <c r="DT27" s="10">
         <v>30</v>
       </c>
-      <c r="DP27" s="10">
+      <c r="DU27" s="10">
         <v>201</v>
       </c>
-      <c r="DU27" s="10">
+      <c r="DZ27" s="10">
         <v>8</v>
       </c>
-      <c r="DV27" s="10">
+      <c r="EA27" s="10">
         <v>201</v>
       </c>
-      <c r="DW27" t="s">
+      <c r="EB27" t="s">
         <v>138</v>
       </c>
-      <c r="DX27" t="s">
+      <c r="EC27" t="s">
         <v>266</v>
       </c>
-      <c r="DY27" t="s">
+      <c r="ED27" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="28" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A28" s="10" t="s">
         <v>245</v>
       </c>
       <c r="B28" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="C28" s="10">
+      <c r="C28" s="16">
+        <v>2024</v>
+      </c>
+      <c r="E28" s="10">
         <v>1</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="F28" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="G28" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="F28" s="10" t="s">
+      <c r="H28" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="G28" s="10" t="s">
+      <c r="I28" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="H28" s="10" t="s">
+      <c r="J28" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I28" s="11">
+      <c r="K28" s="11">
         <v>303</v>
       </c>
-      <c r="J28" s="10">
+      <c r="L28" s="10">
         <v>102</v>
       </c>
-      <c r="K28" s="10" t="s">
+      <c r="M28" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="M28" s="10">
+      <c r="O28" s="10">
         <v>52</v>
       </c>
-      <c r="P28" s="10">
+      <c r="P28" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="S28" s="10">
         <v>6</v>
       </c>
-      <c r="Q28" s="10">
+      <c r="T28" s="10">
         <v>102</v>
       </c>
-      <c r="R28" s="10">
+      <c r="U28" s="10">
         <v>45</v>
       </c>
-      <c r="S28" s="10">
+      <c r="V28" s="10">
         <v>102</v>
       </c>
-      <c r="T28" s="11">
+      <c r="W28" s="11">
         <v>21</v>
       </c>
-      <c r="U28" s="11">
+      <c r="X28" s="11">
         <v>102</v>
-      </c>
-      <c r="Z28" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="AA28" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB28" s="11" t="s">
-        <v>156</v>
       </c>
       <c r="AC28" s="11" t="s">
         <v>155</v>
@@ -5545,154 +5877,160 @@
       <c r="AE28" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="CB28" s="10" t="s">
+      <c r="AF28" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="AG28" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="AH28" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="CG28" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="CC28" s="10">
+      <c r="CH28" s="10">
         <v>102</v>
       </c>
-      <c r="CE28" s="10">
+      <c r="CJ28" s="10">
         <v>1.4</v>
       </c>
-      <c r="CF28" s="11">
+      <c r="CK28" s="11">
         <v>6.4</v>
       </c>
-      <c r="CG28" s="10" t="s">
+      <c r="CL28" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="CH28" s="10" t="s">
+      <c r="CM28" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="CI28" s="10" t="s">
+      <c r="CN28" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="CJ28" s="10" t="s">
+      <c r="CO28" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="CU28" s="11">
+      <c r="CZ28" s="11">
         <v>12</v>
       </c>
-      <c r="CV28" s="11">
+      <c r="DA28" s="11">
         <v>102</v>
       </c>
-      <c r="CW28" s="11">
+      <c r="DB28" s="11">
         <v>10</v>
       </c>
-      <c r="CX28" s="11">
+      <c r="DC28" s="11">
         <v>102</v>
       </c>
-      <c r="DE28" s="11">
+      <c r="DJ28" s="11">
         <v>21</v>
       </c>
-      <c r="DF28" s="11">
+      <c r="DK28" s="11">
         <v>102</v>
       </c>
-      <c r="DO28" s="10">
+      <c r="DT28" s="10">
         <v>11</v>
       </c>
-      <c r="DP28" s="10">
+      <c r="DU28" s="10">
         <v>102</v>
       </c>
-      <c r="DU28" s="10">
+      <c r="DZ28" s="10">
         <v>11</v>
       </c>
-      <c r="DV28" s="10">
+      <c r="EA28" s="10">
         <v>102</v>
       </c>
-      <c r="DW28" t="s">
+      <c r="EB28" t="s">
         <v>212</v>
       </c>
-      <c r="DX28" t="s">
+      <c r="EC28" t="s">
         <v>266</v>
       </c>
-      <c r="DY28" t="s">
+      <c r="ED28" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="29" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>258</v>
       </c>
       <c r="B29" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="16">
+        <v>2024</v>
+      </c>
+      <c r="E29">
         <v>1</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="F29" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E29" t="s">
+      <c r="G29" t="s">
         <v>201</v>
       </c>
-      <c r="F29">
+      <c r="H29">
         <v>150</v>
       </c>
-      <c r="G29" s="10" t="s">
+      <c r="I29" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="H29" s="9" t="s">
+      <c r="J29" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="I29" s="9">
+      <c r="K29" s="9">
         <v>27</v>
       </c>
-      <c r="J29" s="10">
+      <c r="L29" s="10">
         <v>12</v>
       </c>
-      <c r="K29" s="10">
+      <c r="M29" s="10">
         <v>43.6</v>
       </c>
-      <c r="L29" s="10">
+      <c r="N29" s="10">
         <v>3</v>
       </c>
-      <c r="M29" s="10">
+      <c r="O29" s="10">
         <v>12</v>
       </c>
-      <c r="N29" s="11">
-        <v>0</v>
-      </c>
-      <c r="O29" s="11">
+      <c r="P29" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q29" s="11">
+        <v>0</v>
+      </c>
+      <c r="R29" s="11">
         <v>6</v>
       </c>
-      <c r="P29" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="11">
+      <c r="S29" s="11">
+        <v>0</v>
+      </c>
+      <c r="T29" s="11">
         <v>12</v>
       </c>
-      <c r="R29" s="11">
+      <c r="U29" s="11">
         <v>5</v>
       </c>
-      <c r="S29" s="11">
+      <c r="V29" s="11">
         <v>12</v>
       </c>
-      <c r="T29" s="11">
+      <c r="W29" s="11">
         <v>1</v>
       </c>
-      <c r="U29" s="11">
+      <c r="X29" s="11">
         <v>12</v>
       </c>
-      <c r="V29" s="11">
-        <v>0</v>
-      </c>
-      <c r="W29" s="11">
+      <c r="Y29" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="11">
         <v>12</v>
       </c>
-      <c r="X29" s="11">
+      <c r="AA29" s="11">
         <v>1</v>
       </c>
-      <c r="Y29" s="11">
+      <c r="AB29" s="11">
         <v>12</v>
-      </c>
-      <c r="Z29" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AA29" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB29" s="12" t="s">
-        <v>156</v>
       </c>
       <c r="AC29" s="12" t="s">
         <v>155</v>
@@ -5703,214 +6041,223 @@
       <c r="AE29" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="AF29" s="11" t="s">
+      <c r="AF29" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="AG29" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="AH29" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="AI29" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="AG29" s="11">
+      <c r="AJ29" s="11">
         <v>6</v>
       </c>
-      <c r="AH29" s="11">
+      <c r="AK29" s="16">
+        <v>15</v>
+      </c>
+      <c r="AL29" s="11">
         <v>67.92</v>
       </c>
-      <c r="AI29" s="11">
+      <c r="AM29" s="11">
         <v>59.17</v>
       </c>
-      <c r="AJ29" s="11">
+      <c r="AN29" s="11">
         <v>6.27</v>
       </c>
-      <c r="AK29" s="11" t="s">
+      <c r="AO29" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="AL29" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="AM29" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="AN29" s="11" t="s">
+      <c r="AP29" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AQ29" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AR29" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="AO29" s="11">
+      <c r="AS29" s="11">
         <v>6</v>
       </c>
-      <c r="AP29" s="11">
+      <c r="AT29" s="11">
         <v>19.75</v>
       </c>
-      <c r="AQ29" s="11">
+      <c r="AU29" s="11">
         <v>19.670000000000002</v>
       </c>
-      <c r="AR29" s="11">
+      <c r="AV29" s="11">
         <v>3.61</v>
       </c>
-      <c r="AS29" s="11" t="s">
+      <c r="AW29" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="AT29" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="AU29" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="AV29" s="11" t="s">
+      <c r="AX29" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AY29" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AZ29" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="AW29" s="11">
+      <c r="BA29" s="11">
         <v>6</v>
       </c>
-      <c r="AX29" s="11">
+      <c r="BB29" s="11">
         <v>35.17</v>
       </c>
-      <c r="AY29" s="11">
+      <c r="BC29" s="11">
         <v>28.17</v>
       </c>
-      <c r="AZ29" s="11">
+      <c r="BD29" s="11">
         <v>20.440000000000001</v>
       </c>
-      <c r="BA29" s="11" t="s">
+      <c r="BE29" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="BB29" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="BC29" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="CS29" s="11">
+      <c r="BF29" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="BG29" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="CX29" s="11">
         <v>4</v>
       </c>
-      <c r="CT29" s="11">
+      <c r="CY29" s="11">
         <v>12</v>
       </c>
-      <c r="CU29" s="11">
+      <c r="CZ29" s="11">
         <v>1</v>
       </c>
-      <c r="CV29" s="11">
+      <c r="DA29" s="11">
         <v>12</v>
       </c>
-      <c r="CY29" s="11">
-        <v>0</v>
-      </c>
-      <c r="CZ29" s="11">
+      <c r="DD29" s="11">
+        <v>0</v>
+      </c>
+      <c r="DE29" s="11">
         <v>12</v>
       </c>
-      <c r="DA29" s="11">
-        <v>0</v>
-      </c>
-      <c r="DB29" s="11">
+      <c r="DF29" s="11">
+        <v>0</v>
+      </c>
+      <c r="DG29" s="11">
         <v>12</v>
       </c>
-      <c r="DC29" s="11">
+      <c r="DH29" s="11">
         <v>2</v>
       </c>
-      <c r="DD29" s="11">
+      <c r="DI29" s="11">
         <v>12</v>
       </c>
-      <c r="DE29" s="11">
-        <v>0</v>
-      </c>
-      <c r="DF29" s="11">
+      <c r="DJ29" s="11">
+        <v>0</v>
+      </c>
+      <c r="DK29" s="11">
         <v>12</v>
       </c>
-      <c r="DO29" s="11">
+      <c r="DT29" s="11">
         <v>2</v>
       </c>
-      <c r="DP29" s="11">
+      <c r="DU29" s="11">
         <v>12</v>
       </c>
-      <c r="DW29" t="s">
+      <c r="EB29" t="s">
         <v>138</v>
       </c>
-      <c r="DX29" t="s">
+      <c r="EC29" t="s">
         <v>161</v>
       </c>
-      <c r="DY29" t="s">
+      <c r="ED29" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="30" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>251</v>
       </c>
       <c r="B30" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="16">
+        <v>2024</v>
+      </c>
+      <c r="E30">
         <v>1</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="F30" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E30" t="s">
+      <c r="G30" t="s">
         <v>162</v>
       </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
-      <c r="G30" s="10" t="s">
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="H30" s="9" t="s">
+      <c r="J30" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="I30" s="9">
+      <c r="K30" s="9">
         <v>27</v>
       </c>
-      <c r="J30" s="10">
+      <c r="L30" s="10">
         <v>15</v>
       </c>
-      <c r="K30" s="10">
+      <c r="M30" s="10">
         <v>42.7</v>
       </c>
-      <c r="L30" s="10">
+      <c r="N30" s="10">
         <v>3</v>
       </c>
-      <c r="M30" s="10">
+      <c r="O30" s="10">
         <v>12</v>
       </c>
-      <c r="N30" s="11">
+      <c r="P30" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q30" s="11">
         <v>1</v>
       </c>
-      <c r="O30" s="11">
+      <c r="R30" s="11">
         <v>10</v>
       </c>
-      <c r="P30" s="11">
+      <c r="S30" s="11">
         <v>1</v>
       </c>
-      <c r="Q30" s="11">
+      <c r="T30" s="11">
         <v>15</v>
       </c>
-      <c r="R30" s="11">
+      <c r="U30" s="11">
         <v>5</v>
       </c>
-      <c r="S30" s="11">
+      <c r="V30" s="11">
         <v>15</v>
       </c>
-      <c r="T30" s="11">
+      <c r="W30" s="11">
         <v>2</v>
       </c>
-      <c r="U30" s="11">
+      <c r="X30" s="11">
         <v>15</v>
       </c>
-      <c r="V30" s="11">
-        <v>0</v>
-      </c>
-      <c r="W30" s="11">
+      <c r="Y30" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="11">
         <v>15</v>
       </c>
-      <c r="X30" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y30" s="11">
+      <c r="AA30" s="11">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="11">
         <v>15</v>
-      </c>
-      <c r="Z30" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AA30" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB30" s="12" t="s">
-        <v>156</v>
       </c>
       <c r="AC30" s="12" t="s">
         <v>155</v>
@@ -5921,214 +6268,223 @@
       <c r="AE30" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="AF30" s="11" t="s">
+      <c r="AF30" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="AG30" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="AH30" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="AI30" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="AG30" s="11">
+      <c r="AJ30" s="11">
         <v>10</v>
       </c>
-      <c r="AH30" s="11">
+      <c r="AK30" s="16">
+        <v>12</v>
+      </c>
+      <c r="AL30" s="11">
         <v>67.430000000000007</v>
       </c>
-      <c r="AI30" s="11">
+      <c r="AM30" s="11">
         <v>64.7</v>
       </c>
-      <c r="AJ30" s="11">
+      <c r="AN30" s="11">
         <v>13.92</v>
       </c>
-      <c r="AK30" s="11" t="s">
+      <c r="AO30" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="AL30" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="AM30" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="AN30" s="11" t="s">
+      <c r="AP30" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AQ30" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AR30" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="AO30" s="11">
+      <c r="AS30" s="11">
         <v>10</v>
       </c>
-      <c r="AP30" s="11">
+      <c r="AT30" s="11">
         <v>17.93</v>
       </c>
-      <c r="AQ30" s="11">
+      <c r="AU30" s="11">
         <v>17.7</v>
       </c>
-      <c r="AR30" s="11">
+      <c r="AV30" s="11">
         <v>5.25</v>
       </c>
-      <c r="AS30" s="11" t="s">
+      <c r="AW30" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="AT30" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="AU30" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="AV30" s="11" t="s">
+      <c r="AX30" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AY30" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AZ30" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="AW30" s="11">
+      <c r="BA30" s="11">
         <v>10</v>
       </c>
-      <c r="AX30" s="11">
+      <c r="BB30" s="11">
         <v>34.79</v>
       </c>
-      <c r="AY30" s="11">
+      <c r="BC30" s="11">
         <v>30.4</v>
       </c>
-      <c r="AZ30" s="11">
+      <c r="BD30" s="11">
         <v>12.86</v>
       </c>
-      <c r="BA30" s="11" t="s">
+      <c r="BE30" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="BB30" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="BC30" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="CS30" s="11">
+      <c r="BF30" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="BG30" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="CX30" s="11">
         <v>7</v>
       </c>
-      <c r="CT30" s="11">
+      <c r="CY30" s="11">
         <v>15</v>
       </c>
-      <c r="CU30" s="11">
-        <v>0</v>
-      </c>
-      <c r="CV30" s="11">
+      <c r="CZ30" s="11">
+        <v>0</v>
+      </c>
+      <c r="DA30" s="11">
         <v>15</v>
       </c>
-      <c r="CY30" s="11">
-        <v>0</v>
-      </c>
-      <c r="CZ30" s="11">
+      <c r="DD30" s="11">
+        <v>0</v>
+      </c>
+      <c r="DE30" s="11">
         <v>15</v>
       </c>
-      <c r="DA30" s="11">
-        <v>0</v>
-      </c>
-      <c r="DB30" s="11">
+      <c r="DF30" s="11">
+        <v>0</v>
+      </c>
+      <c r="DG30" s="11">
         <v>15</v>
       </c>
-      <c r="DC30" s="11">
-        <v>0</v>
-      </c>
-      <c r="DD30" s="11">
+      <c r="DH30" s="11">
+        <v>0</v>
+      </c>
+      <c r="DI30" s="11">
         <v>15</v>
       </c>
-      <c r="DE30" s="11">
-        <v>0</v>
-      </c>
-      <c r="DF30" s="11">
+      <c r="DJ30" s="11">
+        <v>0</v>
+      </c>
+      <c r="DK30" s="11">
         <v>15</v>
       </c>
-      <c r="DO30" s="11">
+      <c r="DT30" s="11">
         <v>1</v>
       </c>
-      <c r="DP30" s="11">
+      <c r="DU30" s="11">
         <v>15</v>
       </c>
-      <c r="DW30" t="s">
+      <c r="EB30" t="s">
         <v>162</v>
       </c>
-      <c r="DX30" t="s">
+      <c r="EC30" t="s">
         <v>161</v>
       </c>
-      <c r="DY30" t="s">
+      <c r="ED30" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="31" spans="1:129" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:134" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>255</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="16">
+        <v>2024</v>
+      </c>
+      <c r="E31">
         <v>1</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="F31" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E31" t="s">
+      <c r="G31" t="s">
         <v>267</v>
       </c>
-      <c r="F31" s="9">
+      <c r="H31" s="9">
         <v>45</v>
       </c>
-      <c r="G31" s="10" t="s">
+      <c r="I31" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="H31" s="9" t="s">
+      <c r="J31" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="I31" s="9">
+      <c r="K31" s="9">
         <v>104</v>
       </c>
-      <c r="J31" s="9">
+      <c r="L31" s="9">
         <v>5</v>
       </c>
-      <c r="K31" s="9">
+      <c r="M31" s="9">
         <v>41.6</v>
       </c>
-      <c r="L31" s="9">
-        <v>0</v>
-      </c>
-      <c r="M31" s="11">
+      <c r="N31" s="9">
+        <v>0</v>
+      </c>
+      <c r="O31" s="11">
         <v>12</v>
       </c>
-      <c r="N31" s="11">
-        <v>0</v>
-      </c>
-      <c r="O31" s="11">
+      <c r="P31" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q31" s="11">
+        <v>0</v>
+      </c>
+      <c r="R31" s="11">
         <v>4</v>
       </c>
-      <c r="P31" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="11">
+      <c r="S31" s="11">
+        <v>0</v>
+      </c>
+      <c r="T31" s="11">
         <v>5</v>
       </c>
-      <c r="R31" s="11">
-        <v>0</v>
-      </c>
-      <c r="S31" s="11">
+      <c r="U31" s="11">
+        <v>0</v>
+      </c>
+      <c r="V31" s="11">
         <v>5</v>
       </c>
-      <c r="T31" s="11">
-        <v>0</v>
-      </c>
-      <c r="U31" s="11">
+      <c r="W31" s="11">
+        <v>0</v>
+      </c>
+      <c r="X31" s="11">
         <v>5</v>
       </c>
-      <c r="V31" s="11">
-        <v>0</v>
-      </c>
-      <c r="W31" s="11">
+      <c r="Y31" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="11">
         <v>5</v>
       </c>
-      <c r="X31" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y31" s="11">
+      <c r="AA31" s="11">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="11">
         <v>5</v>
-      </c>
-      <c r="Z31" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AA31" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB31" s="12" t="s">
-        <v>156</v>
       </c>
       <c r="AC31" s="12" t="s">
         <v>155</v>
@@ -6139,214 +6495,223 @@
       <c r="AE31" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="AF31" s="11" t="s">
+      <c r="AF31" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="AG31" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="AH31" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="AI31" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="AG31" s="11">
+      <c r="AJ31" s="11">
         <v>4</v>
       </c>
-      <c r="AH31" s="11">
+      <c r="AK31" s="16">
+        <v>5</v>
+      </c>
+      <c r="AL31" s="11">
         <v>62.8</v>
       </c>
-      <c r="AI31" s="11">
+      <c r="AM31" s="11">
         <v>74.8</v>
       </c>
-      <c r="AJ31" s="11">
+      <c r="AN31" s="11">
         <v>7.2</v>
       </c>
-      <c r="AK31" s="11" t="s">
+      <c r="AO31" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="AL31" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="AM31" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="AN31" s="11" t="s">
+      <c r="AP31" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AQ31" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AR31" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="AO31" s="11">
+      <c r="AS31" s="11">
         <v>4</v>
       </c>
-      <c r="AP31" s="11">
+      <c r="AT31" s="11">
         <v>18</v>
       </c>
-      <c r="AQ31" s="11">
+      <c r="AU31" s="11">
         <v>21.5</v>
       </c>
-      <c r="AR31" s="11">
+      <c r="AV31" s="11">
         <v>2.6</v>
       </c>
-      <c r="AS31" s="11" t="s">
+      <c r="AW31" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="AT31" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="AU31" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="AV31" s="11" t="s">
+      <c r="AX31" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AY31" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AZ31" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="AW31" s="11">
+      <c r="BA31" s="11">
         <v>4</v>
       </c>
-      <c r="AX31" s="11">
+      <c r="BB31" s="11">
         <v>36.4</v>
       </c>
-      <c r="AY31" s="11">
+      <c r="BC31" s="11">
         <v>33.299999999999997</v>
       </c>
-      <c r="AZ31" s="11">
+      <c r="BD31" s="11">
         <v>10.6</v>
       </c>
-      <c r="BA31" s="11" t="s">
+      <c r="BE31" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="BB31" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="BC31" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="CS31" s="11">
+      <c r="BF31" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="BG31" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="CX31" s="11">
         <v>2</v>
       </c>
-      <c r="CT31" s="11">
+      <c r="CY31" s="11">
         <v>5</v>
       </c>
-      <c r="CU31" s="11">
-        <v>0</v>
-      </c>
-      <c r="CV31" s="11">
+      <c r="CZ31" s="11">
+        <v>0</v>
+      </c>
+      <c r="DA31" s="11">
         <v>5</v>
       </c>
-      <c r="CY31" s="11">
+      <c r="DD31" s="11">
         <v>1</v>
       </c>
-      <c r="CZ31" s="11">
+      <c r="DE31" s="11">
         <v>5</v>
       </c>
-      <c r="DA31" s="11">
-        <v>0</v>
-      </c>
-      <c r="DB31" s="11">
+      <c r="DF31" s="11">
+        <v>0</v>
+      </c>
+      <c r="DG31" s="11">
         <v>5</v>
       </c>
-      <c r="DC31" s="11">
-        <v>0</v>
-      </c>
-      <c r="DD31" s="11">
+      <c r="DH31" s="11">
+        <v>0</v>
+      </c>
+      <c r="DI31" s="11">
         <v>5</v>
       </c>
-      <c r="DE31" s="11">
-        <v>0</v>
-      </c>
-      <c r="DF31" s="11">
+      <c r="DJ31" s="11">
+        <v>0</v>
+      </c>
+      <c r="DK31" s="11">
         <v>5</v>
       </c>
-      <c r="DO31" s="11">
-        <v>0</v>
-      </c>
-      <c r="DP31" s="11">
+      <c r="DT31" s="11">
+        <v>0</v>
+      </c>
+      <c r="DU31" s="11">
         <v>5</v>
       </c>
-      <c r="DW31" s="13" t="s">
+      <c r="EB31" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="DX31" t="s">
+      <c r="EC31" t="s">
         <v>161</v>
       </c>
-      <c r="DY31" t="s">
+      <c r="ED31" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="32" spans="1:129" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:134" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>256</v>
       </c>
       <c r="B32" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="16">
+        <v>2024</v>
+      </c>
+      <c r="E32">
         <v>1</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="F32" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E32" t="s">
+      <c r="G32" t="s">
         <v>267</v>
       </c>
-      <c r="F32" s="9">
+      <c r="H32" s="9">
         <v>150</v>
       </c>
-      <c r="G32" s="10" t="s">
+      <c r="I32" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="H32" s="9" t="s">
+      <c r="J32" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="I32" s="9">
+      <c r="K32" s="9">
         <v>104</v>
       </c>
-      <c r="J32" s="9">
+      <c r="L32" s="9">
         <v>30</v>
       </c>
-      <c r="K32" s="9">
+      <c r="M32" s="9">
         <v>40</v>
       </c>
-      <c r="L32" s="9">
+      <c r="N32" s="9">
         <v>11</v>
       </c>
-      <c r="M32" s="11">
+      <c r="O32" s="11">
         <v>12</v>
       </c>
-      <c r="N32" s="11">
+      <c r="P32" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q32" s="11">
         <v>4</v>
       </c>
-      <c r="O32" s="11">
+      <c r="R32" s="11">
         <v>20</v>
       </c>
-      <c r="P32" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="11">
+      <c r="S32" s="11">
+        <v>0</v>
+      </c>
+      <c r="T32" s="11">
         <v>30</v>
       </c>
-      <c r="R32" s="11">
+      <c r="U32" s="11">
         <v>3</v>
       </c>
-      <c r="S32" s="11">
+      <c r="V32" s="11">
         <v>30</v>
       </c>
-      <c r="T32" s="11">
+      <c r="W32" s="11">
         <v>1</v>
       </c>
-      <c r="U32" s="11">
+      <c r="X32" s="11">
         <v>30</v>
       </c>
-      <c r="V32" s="11">
-        <v>0</v>
-      </c>
-      <c r="W32" s="11">
+      <c r="Y32" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="11">
         <v>30</v>
       </c>
-      <c r="X32" s="11">
+      <c r="AA32" s="11">
         <v>2</v>
       </c>
-      <c r="Y32" s="11">
+      <c r="AB32" s="11">
         <v>30</v>
-      </c>
-      <c r="Z32" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AA32" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB32" s="12" t="s">
-        <v>156</v>
       </c>
       <c r="AC32" s="12" t="s">
         <v>155</v>
@@ -6357,214 +6722,223 @@
       <c r="AE32" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="AF32" s="11" t="s">
+      <c r="AF32" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="AG32" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="AH32" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="AI32" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="AG32" s="11">
+      <c r="AJ32" s="11">
         <v>20</v>
       </c>
-      <c r="AH32" s="11">
+      <c r="AK32" s="16">
+        <v>30</v>
+      </c>
+      <c r="AL32" s="11">
         <v>69.599999999999994</v>
       </c>
-      <c r="AI32" s="11">
+      <c r="AM32" s="11">
         <v>59</v>
       </c>
-      <c r="AJ32" s="11">
+      <c r="AN32" s="11">
         <v>11.1</v>
       </c>
-      <c r="AK32" s="11" t="s">
+      <c r="AO32" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="AL32" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="AM32" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="AN32" s="11" t="s">
+      <c r="AP32" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AQ32" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AR32" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="AO32" s="11">
+      <c r="AS32" s="11">
         <v>20</v>
       </c>
-      <c r="AP32" s="11">
+      <c r="AT32" s="11">
         <v>17.600000000000001</v>
       </c>
-      <c r="AQ32" s="11">
+      <c r="AU32" s="11">
         <v>16.5</v>
       </c>
-      <c r="AR32" s="11">
+      <c r="AV32" s="11">
         <v>4.7</v>
       </c>
-      <c r="AS32" s="11" t="s">
+      <c r="AW32" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="AT32" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="AU32" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="AV32" s="11" t="s">
+      <c r="AX32" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AY32" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AZ32" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="AW32" s="11">
+      <c r="BA32" s="11">
         <v>19</v>
       </c>
-      <c r="AX32" s="11">
+      <c r="BB32" s="11">
         <v>38.1</v>
       </c>
-      <c r="AY32" s="11">
+      <c r="BC32" s="11">
         <v>29.6</v>
       </c>
-      <c r="AZ32" s="11">
+      <c r="BD32" s="11">
         <v>9.1999999999999993</v>
       </c>
-      <c r="BA32" s="11" t="s">
+      <c r="BE32" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="BB32" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="BC32" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="CS32" s="11">
+      <c r="BF32" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="BG32" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="CX32" s="11">
         <v>8</v>
       </c>
-      <c r="CT32" s="11">
+      <c r="CY32" s="11">
         <v>30</v>
       </c>
-      <c r="CU32" s="11">
+      <c r="CZ32" s="11">
         <v>1</v>
       </c>
-      <c r="CV32" s="11">
+      <c r="DA32" s="11">
         <v>30</v>
       </c>
-      <c r="CY32" s="11">
+      <c r="DD32" s="11">
         <v>2</v>
       </c>
-      <c r="CZ32" s="11">
+      <c r="DE32" s="11">
         <v>30</v>
       </c>
-      <c r="DA32" s="11">
+      <c r="DF32" s="11">
         <v>1</v>
       </c>
-      <c r="DB32" s="11">
+      <c r="DG32" s="11">
         <v>30</v>
       </c>
-      <c r="DC32" s="11">
+      <c r="DH32" s="11">
         <v>1</v>
       </c>
-      <c r="DD32" s="11">
+      <c r="DI32" s="11">
         <v>30</v>
       </c>
-      <c r="DE32" s="11">
+      <c r="DJ32" s="11">
         <v>2</v>
       </c>
-      <c r="DF32" s="11">
+      <c r="DK32" s="11">
         <v>30</v>
       </c>
-      <c r="DO32" s="11">
-        <v>0</v>
-      </c>
-      <c r="DP32" s="11">
+      <c r="DT32" s="11">
+        <v>0</v>
+      </c>
+      <c r="DU32" s="11">
         <v>30</v>
       </c>
-      <c r="DW32" s="13" t="s">
+      <c r="EB32" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="DX32" t="s">
+      <c r="EC32" t="s">
         <v>161</v>
       </c>
-      <c r="DY32" t="s">
+      <c r="ED32" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="33" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>257</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="16">
+        <v>2024</v>
+      </c>
+      <c r="E33">
         <v>1</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="F33" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E33" t="s">
+      <c r="G33" t="s">
         <v>267</v>
       </c>
-      <c r="F33" s="9">
+      <c r="H33" s="9">
         <v>300</v>
       </c>
-      <c r="G33" s="10" t="s">
+      <c r="I33" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="H33" s="9" t="s">
+      <c r="J33" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="I33" s="9">
+      <c r="K33" s="9">
         <v>104</v>
       </c>
-      <c r="J33" s="9">
+      <c r="L33" s="9">
         <v>32</v>
       </c>
-      <c r="K33" s="9">
+      <c r="M33" s="9">
         <v>40.9</v>
       </c>
-      <c r="L33" s="9">
+      <c r="N33" s="9">
         <v>12</v>
       </c>
-      <c r="M33" s="11">
+      <c r="O33" s="11">
         <v>12</v>
       </c>
-      <c r="N33" s="11">
+      <c r="P33" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q33" s="11">
         <v>3</v>
       </c>
-      <c r="O33" s="11">
+      <c r="R33" s="11">
         <v>21</v>
       </c>
-      <c r="P33" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="11">
+      <c r="S33" s="11">
+        <v>0</v>
+      </c>
+      <c r="T33" s="11">
         <v>32</v>
       </c>
-      <c r="R33" s="11">
+      <c r="U33" s="11">
         <v>3</v>
       </c>
-      <c r="S33" s="11">
+      <c r="V33" s="11">
         <v>32</v>
       </c>
-      <c r="T33" s="11">
-        <v>0</v>
-      </c>
-      <c r="U33" s="11">
+      <c r="W33" s="11">
+        <v>0</v>
+      </c>
+      <c r="X33" s="11">
         <v>32</v>
       </c>
-      <c r="V33" s="11">
-        <v>0</v>
-      </c>
-      <c r="W33" s="11">
+      <c r="Y33" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="11">
         <v>32</v>
       </c>
-      <c r="X33" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y33" s="11">
+      <c r="AA33" s="11">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="11">
         <v>32</v>
-      </c>
-      <c r="Z33" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AA33" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB33" s="12" t="s">
-        <v>156</v>
       </c>
       <c r="AC33" s="12" t="s">
         <v>155</v>
@@ -6575,214 +6949,223 @@
       <c r="AE33" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="AF33" s="11" t="s">
+      <c r="AF33" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="AG33" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="AH33" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="AI33" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="AG33" s="11">
+      <c r="AJ33" s="11">
         <v>21</v>
       </c>
-      <c r="AH33" s="11">
+      <c r="AK33" s="16">
+        <v>32</v>
+      </c>
+      <c r="AL33" s="11">
         <v>67.8</v>
       </c>
-      <c r="AI33" s="11">
+      <c r="AM33" s="11">
         <v>60.9</v>
       </c>
-      <c r="AJ33" s="11">
+      <c r="AN33" s="11">
         <v>11.3</v>
       </c>
-      <c r="AK33" s="11" t="s">
+      <c r="AO33" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="AL33" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="AM33" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="AN33" s="11" t="s">
+      <c r="AP33" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AQ33" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AR33" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="AO33" s="11">
+      <c r="AS33" s="11">
         <v>21</v>
       </c>
-      <c r="AP33" s="11">
+      <c r="AT33" s="11">
         <v>17.2</v>
       </c>
-      <c r="AQ33" s="11">
+      <c r="AU33" s="11">
         <v>15.5</v>
       </c>
-      <c r="AR33" s="11">
+      <c r="AV33" s="11">
         <v>4.3</v>
       </c>
-      <c r="AS33" s="11" t="s">
+      <c r="AW33" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="AT33" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="AU33" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="AV33" s="11" t="s">
+      <c r="AX33" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AY33" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AZ33" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="AW33" s="11">
+      <c r="BA33" s="11">
         <v>21</v>
       </c>
-      <c r="AX33" s="11">
+      <c r="BB33" s="11">
         <v>38.4</v>
       </c>
-      <c r="AY33" s="11">
+      <c r="BC33" s="11">
         <v>29.2</v>
       </c>
-      <c r="AZ33" s="11">
+      <c r="BD33" s="11">
         <v>12.4</v>
       </c>
-      <c r="BA33" s="11" t="s">
+      <c r="BE33" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="BB33" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="BC33" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="CS33" s="11">
+      <c r="BF33" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="BG33" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="CX33" s="11">
         <v>4</v>
       </c>
-      <c r="CT33" s="11">
+      <c r="CY33" s="11">
         <v>32</v>
       </c>
-      <c r="CU33" s="11">
-        <v>0</v>
-      </c>
-      <c r="CV33" s="11">
+      <c r="CZ33" s="11">
+        <v>0</v>
+      </c>
+      <c r="DA33" s="11">
         <v>32</v>
       </c>
-      <c r="CY33" s="11">
+      <c r="DD33" s="11">
         <v>1</v>
       </c>
-      <c r="CZ33" s="11">
+      <c r="DE33" s="11">
         <v>32</v>
       </c>
-      <c r="DA33" s="11">
-        <v>0</v>
-      </c>
-      <c r="DB33" s="11">
+      <c r="DF33" s="11">
+        <v>0</v>
+      </c>
+      <c r="DG33" s="11">
         <v>32</v>
       </c>
-      <c r="DC33" s="11">
+      <c r="DH33" s="11">
         <v>1</v>
       </c>
-      <c r="DD33" s="11">
+      <c r="DI33" s="11">
         <v>32</v>
       </c>
-      <c r="DE33" s="11">
-        <v>0</v>
-      </c>
-      <c r="DF33" s="11">
+      <c r="DJ33" s="11">
+        <v>0</v>
+      </c>
+      <c r="DK33" s="11">
         <v>32</v>
       </c>
-      <c r="DO33" s="11">
-        <v>0</v>
-      </c>
-      <c r="DP33" s="11">
+      <c r="DT33" s="11">
+        <v>0</v>
+      </c>
+      <c r="DU33" s="11">
         <v>32</v>
       </c>
-      <c r="DW33" s="13" t="s">
+      <c r="EB33" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="DX33" t="s">
+      <c r="EC33" t="s">
         <v>161</v>
       </c>
-      <c r="DY33" t="s">
+      <c r="ED33" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="34" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>253</v>
       </c>
       <c r="B34" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="16">
+        <v>2024</v>
+      </c>
+      <c r="E34">
         <v>1</v>
       </c>
-      <c r="D34" s="10" t="s">
+      <c r="F34" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E34" t="s">
+      <c r="G34" t="s">
         <v>268</v>
       </c>
-      <c r="F34" s="9">
-        <v>0</v>
-      </c>
-      <c r="G34" s="10" t="s">
+      <c r="H34" s="9">
+        <v>0</v>
+      </c>
+      <c r="I34" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="H34" s="9" t="s">
+      <c r="J34" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="I34" s="9">
+      <c r="K34" s="9">
         <v>104</v>
       </c>
-      <c r="J34" s="9">
+      <c r="L34" s="9">
         <v>37</v>
       </c>
-      <c r="K34" s="9">
+      <c r="M34" s="9">
         <v>41.3</v>
       </c>
-      <c r="L34" s="9">
+      <c r="N34" s="9">
         <v>10</v>
       </c>
-      <c r="M34" s="11">
+      <c r="O34" s="11">
         <v>12</v>
       </c>
-      <c r="N34" s="11">
+      <c r="P34" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q34" s="11">
         <v>4</v>
       </c>
-      <c r="O34" s="11">
+      <c r="R34" s="11">
         <v>31</v>
       </c>
-      <c r="P34" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="11">
+      <c r="S34" s="11">
+        <v>0</v>
+      </c>
+      <c r="T34" s="11">
         <v>37</v>
       </c>
-      <c r="R34" s="11">
+      <c r="U34" s="11">
         <v>4</v>
       </c>
-      <c r="S34" s="11">
+      <c r="V34" s="11">
         <v>37</v>
       </c>
-      <c r="T34" s="11">
-        <v>0</v>
-      </c>
-      <c r="U34" s="11">
+      <c r="W34" s="11">
+        <v>0</v>
+      </c>
+      <c r="X34" s="11">
         <v>37</v>
       </c>
-      <c r="V34" s="11">
+      <c r="Y34" s="11">
         <v>1</v>
       </c>
-      <c r="W34" s="11">
+      <c r="Z34" s="11">
         <v>37</v>
       </c>
-      <c r="X34" s="11">
+      <c r="AA34" s="11">
         <v>1</v>
       </c>
-      <c r="Y34" s="11">
+      <c r="AB34" s="11">
         <v>37</v>
-      </c>
-      <c r="Z34" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AA34" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB34" s="12" t="s">
-        <v>156</v>
       </c>
       <c r="AC34" s="12" t="s">
         <v>155</v>
@@ -6793,313 +7176,355 @@
       <c r="AE34" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="AF34" s="11" t="s">
+      <c r="AF34" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="AG34" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="AH34" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="AI34" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="AG34" s="11">
+      <c r="AJ34" s="11">
         <v>31</v>
       </c>
-      <c r="AH34" s="11">
+      <c r="AK34" s="16">
+        <v>37</v>
+      </c>
+      <c r="AL34" s="11">
         <v>71.400000000000006</v>
       </c>
-      <c r="AI34" s="11">
+      <c r="AM34" s="11">
         <v>64.400000000000006</v>
       </c>
-      <c r="AJ34" s="11">
+      <c r="AN34" s="11">
         <v>12.2</v>
       </c>
-      <c r="AK34" s="11" t="s">
+      <c r="AO34" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="AL34" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="AM34" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="AN34" s="11" t="s">
+      <c r="AP34" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AQ34" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AR34" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="AO34" s="11">
+      <c r="AS34" s="11">
         <v>31</v>
       </c>
-      <c r="AP34" s="11">
+      <c r="AT34" s="11">
         <v>18.899999999999999</v>
       </c>
-      <c r="AQ34" s="11">
+      <c r="AU34" s="11">
         <v>17.3</v>
       </c>
-      <c r="AR34" s="11">
+      <c r="AV34" s="11">
         <v>4.5</v>
       </c>
-      <c r="AS34" s="11" t="s">
+      <c r="AW34" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="AT34" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="AU34" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="AV34" s="11" t="s">
+      <c r="AX34" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AY34" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AZ34" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="AW34" s="11">
+      <c r="BA34" s="11">
         <v>31</v>
       </c>
-      <c r="AX34" s="11">
+      <c r="BB34" s="11">
         <v>36.6</v>
       </c>
-      <c r="AY34" s="11">
+      <c r="BC34" s="11">
         <v>32.700000000000003</v>
       </c>
-      <c r="AZ34" s="11">
+      <c r="BD34" s="11">
         <v>13.4</v>
       </c>
-      <c r="BA34" s="11" t="s">
+      <c r="BE34" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="BB34" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="BC34" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="CS34" s="11">
+      <c r="BF34" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="BG34" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="CX34" s="11">
         <v>9</v>
       </c>
-      <c r="CT34" s="11">
+      <c r="CY34" s="11">
         <v>37</v>
       </c>
-      <c r="CU34" s="11">
-        <v>0</v>
-      </c>
-      <c r="CV34" s="11">
+      <c r="CZ34" s="11">
+        <v>0</v>
+      </c>
+      <c r="DA34" s="11">
         <v>37</v>
       </c>
-      <c r="CY34" s="11">
+      <c r="DD34" s="11">
         <v>1</v>
       </c>
-      <c r="CZ34" s="11">
+      <c r="DE34" s="11">
         <v>37</v>
       </c>
-      <c r="DA34" s="11">
+      <c r="DF34" s="11">
         <v>3</v>
       </c>
-      <c r="DB34" s="11">
+      <c r="DG34" s="11">
         <v>37</v>
       </c>
-      <c r="DC34" s="11">
+      <c r="DH34" s="11">
         <v>2</v>
       </c>
-      <c r="DD34" s="11">
+      <c r="DI34" s="11">
         <v>37</v>
       </c>
-      <c r="DE34" s="11">
+      <c r="DJ34" s="11">
         <v>2</v>
       </c>
-      <c r="DF34" s="11">
+      <c r="DK34" s="11">
         <v>37</v>
       </c>
-      <c r="DO34" s="11">
-        <v>0</v>
-      </c>
-      <c r="DP34" s="11">
+      <c r="DT34" s="11">
+        <v>0</v>
+      </c>
+      <c r="DU34" s="11">
         <v>37</v>
       </c>
-      <c r="DW34" s="13" t="s">
+      <c r="EB34" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="DX34" t="s">
+      <c r="EC34" t="s">
         <v>161</v>
       </c>
-      <c r="DY34" t="s">
+      <c r="ED34" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="35" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A35" s="11" t="s">
         <v>127</v>
       </c>
       <c r="B35" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="C35" s="10">
+      <c r="C35" s="16">
+        <v>2024</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="E35" s="10">
         <v>1</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="F35" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="E35" s="10" t="s">
+      <c r="G35" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="F35" s="9">
+      <c r="H35" s="9">
         <v>150</v>
       </c>
-      <c r="G35" s="10" t="s">
+      <c r="I35" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="H35" s="10" t="s">
+      <c r="J35" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I35" s="11">
+      <c r="K35" s="11">
         <v>31</v>
       </c>
-      <c r="J35" s="11">
+      <c r="L35" s="11">
         <v>31</v>
       </c>
-      <c r="K35" s="11">
+      <c r="M35" s="11">
         <v>46.2</v>
       </c>
-      <c r="L35" s="11">
+      <c r="N35" s="11">
         <v>6</v>
       </c>
-      <c r="M35" s="11">
+      <c r="O35" s="11">
         <v>0.14000000000000001</v>
       </c>
-      <c r="V35" s="11">
-        <v>0</v>
-      </c>
-      <c r="W35" s="11">
+      <c r="P35" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="Y35" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="11">
         <v>29</v>
       </c>
-      <c r="X35" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y35" s="11">
+      <c r="AA35" s="11">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="11">
         <v>29</v>
       </c>
-      <c r="CS35" s="10">
+      <c r="CX35" s="10">
         <v>20</v>
       </c>
-      <c r="CT35" s="10">
+      <c r="CY35" s="10">
         <v>29</v>
       </c>
-      <c r="CY35" s="10">
+      <c r="DD35" s="10">
         <v>4</v>
       </c>
-      <c r="CZ35" s="10">
+      <c r="DE35" s="10">
         <v>29</v>
       </c>
-      <c r="DC35" s="10">
+      <c r="DH35" s="10">
         <v>8</v>
       </c>
-      <c r="DD35" s="10">
+      <c r="DI35" s="10">
         <v>29</v>
       </c>
-      <c r="DE35" s="10">
+      <c r="DJ35" s="10">
         <v>4</v>
       </c>
-      <c r="DF35" s="10">
+      <c r="DK35" s="10">
         <v>29</v>
       </c>
-      <c r="DI35" s="11">
-        <v>0</v>
-      </c>
-      <c r="DJ35" s="11">
+      <c r="DN35" s="11">
+        <v>0</v>
+      </c>
+      <c r="DO35" s="11">
         <v>29</v>
       </c>
-      <c r="DW35" s="14" t="s">
+      <c r="EB35" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="DX35" s="11" t="s">
+      <c r="EC35" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="DY35" s="11" t="s">
+      <c r="ED35" s="11" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="36" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
         <v>261</v>
       </c>
       <c r="B36" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="C36" s="10">
+      <c r="C36" s="16">
+        <v>2024</v>
+      </c>
+      <c r="D36" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="E36" s="10">
         <v>1</v>
       </c>
-      <c r="D36" s="10" t="s">
+      <c r="F36" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="E36" s="10" t="s">
+      <c r="G36" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="G36" s="10" t="s">
+      <c r="I36" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="H36" s="10" t="s">
+      <c r="J36" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I36" s="11">
+      <c r="K36" s="11">
         <v>31</v>
       </c>
-      <c r="J36" s="11">
+      <c r="L36" s="11">
         <v>31</v>
       </c>
-      <c r="K36" s="11">
+      <c r="M36" s="11">
         <v>46.2</v>
       </c>
-      <c r="L36" s="11">
+      <c r="N36" s="11">
         <v>6</v>
       </c>
-      <c r="M36" s="11">
+      <c r="O36" s="11">
         <v>0.14000000000000001</v>
       </c>
-      <c r="V36" s="11">
-        <v>0</v>
-      </c>
-      <c r="W36" s="11">
+      <c r="P36" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="Y36" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="11">
         <v>26</v>
       </c>
-      <c r="X36" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y36" s="11">
+      <c r="AA36" s="11">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="11">
         <v>26</v>
       </c>
-      <c r="CS36" s="10">
+      <c r="CX36" s="10">
         <v>9</v>
       </c>
-      <c r="CT36" s="10">
+      <c r="CY36" s="10">
         <v>26</v>
       </c>
-      <c r="CY36" s="10">
-        <v>0</v>
-      </c>
-      <c r="CZ36" s="10">
+      <c r="DD36" s="10">
+        <v>0</v>
+      </c>
+      <c r="DE36" s="10">
         <v>26</v>
       </c>
-      <c r="DC36" s="10">
-        <v>0</v>
-      </c>
-      <c r="DD36" s="10">
+      <c r="DH36" s="10">
+        <v>0</v>
+      </c>
+      <c r="DI36" s="10">
         <v>26</v>
       </c>
-      <c r="DE36" s="10">
+      <c r="DJ36" s="10">
         <v>1</v>
       </c>
-      <c r="DF36" s="10">
+      <c r="DK36" s="10">
         <v>26</v>
       </c>
-      <c r="DI36" s="11">
-        <v>0</v>
-      </c>
-      <c r="DJ36" s="11">
+      <c r="DN36" s="11">
+        <v>0</v>
+      </c>
+      <c r="DO36" s="11">
         <v>26</v>
       </c>
-      <c r="DW36" s="14" t="s">
+      <c r="EB36" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="DX36" s="11" t="s">
+      <c r="EC36" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="DY36" s="11" t="s">
+      <c r="ED36" s="11" t="s">
         <v>132</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D26" r:id="rId1" xr:uid="{A13D4466-568C-034C-847D-7A36B1B7372A}"/>
+    <hyperlink ref="D25" r:id="rId2" xr:uid="{42D3DC47-24E8-974E-AC74-D9E40FB0D873}"/>
+    <hyperlink ref="D24" r:id="rId3" xr:uid="{91029A47-185B-6A47-8CE3-7310883C8CCA}"/>
+    <hyperlink ref="D4" r:id="rId4" xr:uid="{34C41CDA-16BB-A141-A49F-A13FB6D5D5E7}"/>
+    <hyperlink ref="D5" r:id="rId5" xr:uid="{A159392F-A0E5-6E4F-9C13-0D55452E3B75}"/>
+    <hyperlink ref="D16" r:id="rId6" xr:uid="{F0609477-390E-BC41-B898-8AEA76FDD183}"/>
+    <hyperlink ref="D19" r:id="rId7" xr:uid="{13DAA794-A7D9-4345-9B3E-182D818FEB81}"/>
+    <hyperlink ref="D20" r:id="rId8" xr:uid="{3FCDDBD9-56BC-C749-BB76-D0B15C422E37}"/>
+    <hyperlink ref="D35" r:id="rId9" xr:uid="{A31C1C9D-E44E-7E45-B744-61D3C3B6A050}"/>
+    <hyperlink ref="D36" r:id="rId10" xr:uid="{75DC2334-CE5B-D44A-BEF6-C0CB14654AA3}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <legacyDrawing r:id="rId11"/>
 </worksheet>
 </file>
--- a/data_u1/LSR3_H_2025-01-16.xlsx
+++ b/data_u1/LSR3_H_2025-01-16.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sksiafis/Documents/GitHub/LSR3_taar1_H/data_u1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35B00FF1-2DC1-4B4D-933A-2292B07EF117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{477491FF-13AF-8A4B-92E3-749202705B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19560" yWindow="-17600" windowWidth="30180" windowHeight="17720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22300" yWindow="-20260" windowWidth="30180" windowHeight="17720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5516,7 +5516,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="25" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:134" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>241</v>
       </c>

--- a/data_u1/LSR3_H_2025-01-16.xlsx
+++ b/data_u1/LSR3_H_2025-01-16.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sksiafis/Documents/GitHub/LSR3_taar1_H/data_u1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{477491FF-13AF-8A4B-92E3-749202705B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A73D962C-1E82-0D43-A93D-8DC17D78DB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22300" yWindow="-20260" windowWidth="30180" windowHeight="17720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23500" yWindow="-18540" windowWidth="30180" windowHeight="17720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
     <author>tc={63125C18-1CF7-5340-80AF-3F079B6ADA33}</author>
   </authors>
   <commentList>
-    <comment ref="AZ4" authorId="0" shapeId="0" xr:uid="{F49B5693-3906-8543-B427-4EC42AF420FE}">
+    <comment ref="BA4" authorId="0" shapeId="0" xr:uid="{F49B5693-3906-8543-B427-4EC42AF420FE}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1097" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1102" uniqueCount="288">
   <si>
     <t>arm_name</t>
   </si>
@@ -908,6 +908,21 @@
   </si>
   <si>
     <t>weeks</t>
+  </si>
+  <si>
+    <t>positive_baseline_n</t>
+  </si>
+  <si>
+    <t>negative_baseline_n</t>
+  </si>
+  <si>
+    <t>cognition_baseline_n</t>
+  </si>
+  <si>
+    <t>weight_baseline_n</t>
+  </si>
+  <si>
+    <t>prolactin_baseline_n</t>
   </si>
 </sst>
 </file>
@@ -1363,7 +1378,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="AZ4" dT="2025-01-16T13:52:36.05" personId="{9C02175C-AB95-C54D-8A67-708063150B15}" id="{F49B5693-3906-8543-B427-4EC42AF420FE}">
+  <threadedComment ref="BA4" dT="2025-01-16T13:52:36.05" personId="{9C02175C-AB95-C54D-8A67-708063150B15}" id="{F49B5693-3906-8543-B427-4EC42AF420FE}">
     <text>Changed from first version because BNSS total has been recently been show that has a better validity compared to PANSS negative (Weigel et al)</text>
   </threadedComment>
   <threadedComment ref="Q29" dT="2025-01-16T13:52:04.57" personId="{9C02175C-AB95-C54D-8A67-708063150B15}" id="{63125C18-1CF7-5340-80AF-3F079B6ADA33}">
@@ -1374,7 +1389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:ED36"/>
+  <dimension ref="A1:EI36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.6640625" customWidth="1"/>
@@ -1384,10 +1399,16 @@
     <col min="16" max="16" width="8.83203125" style="16"/>
     <col min="37" max="37" width="8.83203125" style="16"/>
     <col min="38" max="38" width="12.83203125" customWidth="1"/>
-    <col min="78" max="78" width="8.83203125" style="16"/>
+    <col min="46" max="46" width="8.83203125" style="16"/>
+    <col min="55" max="55" width="8.83203125" style="16"/>
+    <col min="71" max="71" width="9" customWidth="1"/>
+    <col min="72" max="72" width="9" style="16" customWidth="1"/>
+    <col min="81" max="81" width="8.83203125" style="16"/>
+    <col min="90" max="90" width="8.83203125" style="16"/>
+    <col min="100" max="100" width="8.83203125" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:134" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:139" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1523,275 +1544,290 @@
       <c r="AS1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AT1" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="AU1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BC1" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="BD1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BE1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BF1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BG1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BH1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BI1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BJ1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BK1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BL1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BM1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BN1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BO1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BP1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BQ1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BR1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BS1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BT1" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="BU1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BV1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BW1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BX1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BY1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="BZ1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="CA1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="CB1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="BZ1" s="15" t="s">
+      <c r="CC1" s="15" t="s">
         <v>276</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CD1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CE1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CF1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CG1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CH1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="CI1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CJ1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="CH1" s="1" t="s">
+      <c r="CK1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CL1" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="CM1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="CJ1" s="1" t="s">
+      <c r="CN1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="CK1" s="1" t="s">
+      <c r="CO1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="CL1" s="1" t="s">
+      <c r="CP1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="CM1" s="1" t="s">
+      <c r="CQ1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="CN1" s="1" t="s">
+      <c r="CR1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="CO1" s="1" t="s">
+      <c r="CS1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="CP1" s="1" t="s">
+      <c r="CT1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="CQ1" s="1" t="s">
+      <c r="CU1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="CR1" s="1" t="s">
+      <c r="CV1" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="CW1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="CS1" s="1" t="s">
+      <c r="CX1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="CT1" s="1" t="s">
+      <c r="CY1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="CU1" s="1" t="s">
+      <c r="CZ1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="CV1" s="1" t="s">
+      <c r="DA1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="CW1" s="1" t="s">
+      <c r="DB1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="CX1" s="1" t="s">
+      <c r="DC1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="CY1" s="1" t="s">
+      <c r="DD1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="CZ1" s="7" t="s">
+      <c r="DE1" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="DA1" s="7" t="s">
+      <c r="DF1" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="DB1" s="1" t="s">
+      <c r="DG1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="DC1" s="1" t="s">
+      <c r="DH1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="DD1" s="1" t="s">
+      <c r="DI1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="DE1" s="1" t="s">
+      <c r="DJ1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="DF1" s="1" t="s">
+      <c r="DK1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="DG1" s="1" t="s">
+      <c r="DL1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="DH1" s="1" t="s">
+      <c r="DM1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="DI1" s="1" t="s">
+      <c r="DN1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="DJ1" s="1" t="s">
+      <c r="DO1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="DK1" s="1" t="s">
+      <c r="DP1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="DL1" s="1" t="s">
+      <c r="DQ1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="DM1" s="1" t="s">
+      <c r="DR1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="DN1" s="1" t="s">
+      <c r="DS1" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="DO1" s="1" t="s">
+      <c r="DT1" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="DP1" s="1" t="s">
+      <c r="DU1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="DQ1" s="1" t="s">
+      <c r="DV1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="DR1" s="1" t="s">
+      <c r="DW1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="DS1" s="1" t="s">
+      <c r="DX1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="DT1" s="1" t="s">
+      <c r="DY1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="DU1" s="1" t="s">
+      <c r="DZ1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="DV1" s="1" t="s">
+      <c r="EA1" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="DW1" s="1" t="s">
+      <c r="EB1" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="DX1" s="1" t="s">
+      <c r="EC1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="DY1" s="1" t="s">
+      <c r="ED1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="DZ1" s="1" t="s">
+      <c r="EE1" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="EA1" s="1" t="s">
+      <c r="EF1" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="EB1" s="1" t="s">
+      <c r="EG1" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="EC1" s="1" t="s">
+      <c r="EH1" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="ED1" s="1" t="s">
+      <c r="EI1" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:134" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:139" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>127</v>
       </c>
@@ -1915,96 +1951,102 @@
       <c r="AS2">
         <v>24</v>
       </c>
-      <c r="AT2">
+      <c r="AT2" s="16">
+        <v>24</v>
+      </c>
+      <c r="AU2">
         <v>13.1</v>
       </c>
-      <c r="AU2">
+      <c r="AV2">
         <v>-2.5</v>
       </c>
-      <c r="AV2">
+      <c r="AW2">
         <v>7.94</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AX2" t="s">
         <v>130</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AY2" t="s">
         <v>131</v>
       </c>
-      <c r="AY2" t="s">
-        <v>132</v>
-      </c>
-      <c r="BP2" t="s">
+      <c r="AZ2" t="s">
+        <v>132</v>
+      </c>
+      <c r="BR2" t="s">
         <v>160</v>
       </c>
-      <c r="BQ2">
+      <c r="BS2">
         <v>23</v>
       </c>
-      <c r="BR2">
+      <c r="BT2" s="16">
+        <v>24</v>
+      </c>
+      <c r="BU2">
         <v>-25.1</v>
       </c>
-      <c r="BS2">
+      <c r="BV2">
         <v>0.8</v>
       </c>
-      <c r="BT2">
+      <c r="BW2">
         <v>2.2000000000000002</v>
       </c>
-      <c r="BU2" t="s">
+      <c r="BX2" t="s">
         <v>130</v>
       </c>
-      <c r="BV2" t="s">
+      <c r="BY2" t="s">
         <v>131</v>
       </c>
-      <c r="BW2" t="s">
-        <v>132</v>
-      </c>
-      <c r="CX2">
+      <c r="BZ2" t="s">
+        <v>132</v>
+      </c>
+      <c r="DC2">
         <v>18</v>
       </c>
-      <c r="CY2">
+      <c r="DD2">
         <v>25</v>
       </c>
-      <c r="DB2" s="9"/>
-      <c r="DC2" s="9"/>
-      <c r="DD2">
+      <c r="DG2" s="9"/>
+      <c r="DH2" s="9"/>
+      <c r="DI2">
         <v>4</v>
       </c>
-      <c r="DE2">
+      <c r="DJ2">
         <v>25</v>
       </c>
-      <c r="DH2">
+      <c r="DM2">
         <v>3</v>
       </c>
-      <c r="DI2">
+      <c r="DN2">
         <v>25</v>
       </c>
-      <c r="DJ2">
+      <c r="DO2">
         <v>2</v>
       </c>
-      <c r="DK2">
+      <c r="DP2">
         <v>25</v>
       </c>
-      <c r="DP2" s="9"/>
-      <c r="DQ2" s="9"/>
-      <c r="DR2">
+      <c r="DU2" s="9"/>
+      <c r="DV2" s="9"/>
+      <c r="DW2">
         <v>13</v>
       </c>
-      <c r="DS2">
+      <c r="DX2">
         <v>25</v>
       </c>
-      <c r="DT2" s="8">
+      <c r="DY2" s="8">
         <v>2</v>
       </c>
-      <c r="EB2" t="s">
+      <c r="EG2" t="s">
         <v>138</v>
       </c>
-      <c r="EC2" t="s">
+      <c r="EH2" t="s">
         <v>161</v>
       </c>
-      <c r="ED2" t="s">
+      <c r="EI2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="3" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>162</v>
       </c>
@@ -2128,107 +2170,113 @@
       <c r="AS3">
         <v>14</v>
       </c>
-      <c r="AT3">
+      <c r="AT3" s="16">
+        <v>14</v>
+      </c>
+      <c r="AU3">
         <v>14.7</v>
       </c>
-      <c r="AU3">
+      <c r="AV3">
         <v>-1.4</v>
       </c>
-      <c r="AV3">
+      <c r="AW3">
         <v>7.71</v>
       </c>
-      <c r="AW3" t="s">
+      <c r="AX3" t="s">
         <v>130</v>
       </c>
-      <c r="AX3" t="s">
+      <c r="AY3" t="s">
         <v>131</v>
       </c>
-      <c r="AY3" t="s">
-        <v>132</v>
-      </c>
-      <c r="BP3" t="s">
+      <c r="AZ3" t="s">
+        <v>132</v>
+      </c>
+      <c r="BR3" t="s">
         <v>160</v>
       </c>
-      <c r="BQ3">
+      <c r="BS3">
         <v>14</v>
       </c>
-      <c r="BR3">
+      <c r="BT3" s="16">
+        <v>14</v>
+      </c>
+      <c r="BU3">
         <v>-24.7</v>
       </c>
-      <c r="BS3">
+      <c r="BV3">
         <v>-0.3</v>
       </c>
-      <c r="BT3">
+      <c r="BW3">
         <v>1.99</v>
       </c>
-      <c r="BU3" t="s">
+      <c r="BX3" t="s">
         <v>130</v>
       </c>
-      <c r="BV3" t="s">
+      <c r="BY3" t="s">
         <v>131</v>
       </c>
-      <c r="BW3" t="s">
-        <v>132</v>
-      </c>
-      <c r="CX3">
+      <c r="BZ3" t="s">
+        <v>132</v>
+      </c>
+      <c r="DC3">
         <v>12</v>
       </c>
-      <c r="CY3">
+      <c r="DD3">
         <v>14</v>
       </c>
-      <c r="DB3">
-        <v>0</v>
-      </c>
-      <c r="DC3">
+      <c r="DG3">
+        <v>0</v>
+      </c>
+      <c r="DH3">
         <v>14</v>
       </c>
-      <c r="DD3">
+      <c r="DI3">
         <v>1</v>
       </c>
-      <c r="DE3">
+      <c r="DJ3">
         <v>14</v>
       </c>
-      <c r="DH3">
+      <c r="DM3">
         <v>1</v>
       </c>
-      <c r="DI3">
+      <c r="DN3">
         <v>14</v>
       </c>
-      <c r="DJ3">
+      <c r="DO3">
         <v>2</v>
       </c>
-      <c r="DK3">
+      <c r="DP3">
         <v>14</v>
       </c>
-      <c r="DP3">
+      <c r="DU3">
         <v>1</v>
       </c>
-      <c r="DQ3">
+      <c r="DV3">
         <v>14</v>
       </c>
-      <c r="DR3">
+      <c r="DW3">
         <v>11</v>
       </c>
-      <c r="DS3">
+      <c r="DX3">
         <v>14</v>
       </c>
-      <c r="DT3">
+      <c r="DY3">
         <v>1</v>
       </c>
-      <c r="DU3">
+      <c r="DZ3">
         <v>14</v>
       </c>
-      <c r="EB3" t="s">
+      <c r="EG3" t="s">
         <v>162</v>
       </c>
-      <c r="EC3" t="s">
+      <c r="EH3" t="s">
         <v>161</v>
       </c>
-      <c r="ED3" t="s">
+      <c r="EI3" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="4" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>127</v>
       </c>
@@ -2358,200 +2406,209 @@
       <c r="AS4">
         <v>120</v>
       </c>
-      <c r="AT4">
+      <c r="AT4" s="16">
+        <v>120</v>
+      </c>
+      <c r="AU4">
         <v>25.8</v>
       </c>
-      <c r="AU4">
+      <c r="AV4">
         <v>-5.5</v>
       </c>
-      <c r="AV4">
+      <c r="AW4">
         <v>5.48</v>
       </c>
-      <c r="AW4" t="s">
+      <c r="AX4" t="s">
         <v>130</v>
       </c>
-      <c r="AX4" t="s">
+      <c r="AY4" t="s">
         <v>131</v>
       </c>
-      <c r="AY4" t="s">
-        <v>132</v>
-      </c>
-      <c r="AZ4" s="9" t="s">
+      <c r="AZ4" t="s">
+        <v>132</v>
+      </c>
+      <c r="BA4" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="BA4">
+      <c r="BB4">
         <v>120</v>
       </c>
-      <c r="BB4" s="9">
+      <c r="BC4" s="16">
+        <v>120</v>
+      </c>
+      <c r="BD4" s="9">
         <v>37.200000000000003</v>
       </c>
-      <c r="BC4" s="9">
+      <c r="BE4" s="9">
         <v>-7.1</v>
       </c>
-      <c r="BD4" s="9">
+      <c r="BF4" s="9">
         <v>10.95</v>
       </c>
-      <c r="BE4" t="s">
+      <c r="BG4" t="s">
         <v>130</v>
       </c>
-      <c r="BF4" t="s">
+      <c r="BH4" t="s">
         <v>131</v>
       </c>
-      <c r="BG4" t="s">
-        <v>132</v>
-      </c>
-      <c r="BX4" t="s">
+      <c r="BI4" t="s">
+        <v>132</v>
+      </c>
+      <c r="CA4" t="s">
         <v>135</v>
       </c>
-      <c r="BY4">
+      <c r="CB4">
         <v>120</v>
       </c>
-      <c r="BZ4" s="16">
+      <c r="CC4" s="16">
         <v>120</v>
       </c>
-      <c r="CA4">
+      <c r="CD4">
         <v>13.1</v>
       </c>
-      <c r="CB4">
+      <c r="CE4">
         <v>-3.3</v>
       </c>
-      <c r="CC4">
+      <c r="CF4">
         <v>6.57</v>
       </c>
-      <c r="CD4" t="s">
+      <c r="CG4" t="s">
         <v>130</v>
       </c>
-      <c r="CE4" t="s">
+      <c r="CH4" t="s">
         <v>131</v>
       </c>
-      <c r="CF4" t="s">
-        <v>132</v>
-      </c>
-      <c r="CG4" t="s">
+      <c r="CI4" t="s">
+        <v>132</v>
+      </c>
+      <c r="CJ4" t="s">
         <v>136</v>
       </c>
-      <c r="CH4">
+      <c r="CK4">
         <v>120</v>
       </c>
-      <c r="CI4">
+      <c r="CL4" s="16">
+        <v>120</v>
+      </c>
+      <c r="CM4">
         <v>75.400000000000006</v>
       </c>
-      <c r="CJ4">
+      <c r="CN4">
         <v>0.3</v>
       </c>
-      <c r="CK4">
+      <c r="CO4">
         <v>1.9</v>
       </c>
-      <c r="CL4" t="s">
+      <c r="CP4" t="s">
         <v>130</v>
       </c>
-      <c r="CM4" t="s">
+      <c r="CQ4" t="s">
         <v>131</v>
       </c>
-      <c r="CN4" t="s">
-        <v>132</v>
-      </c>
-      <c r="CO4" t="s">
+      <c r="CR4" t="s">
+        <v>132</v>
+      </c>
+      <c r="CS4" t="s">
         <v>172</v>
       </c>
-      <c r="CP4" t="s">
+      <c r="CT4" t="s">
         <v>137</v>
       </c>
-      <c r="CQ4">
+      <c r="CU4">
         <v>114</v>
       </c>
-      <c r="CS4">
+      <c r="CX4">
         <v>-1.965789473684211</v>
       </c>
-      <c r="CT4">
+      <c r="CY4">
         <v>28</v>
       </c>
-      <c r="CU4" t="s">
+      <c r="CZ4" t="s">
         <v>130</v>
       </c>
-      <c r="CV4" t="s">
-        <v>132</v>
-      </c>
-      <c r="CW4" t="s">
+      <c r="DA4" t="s">
+        <v>132</v>
+      </c>
+      <c r="DB4" t="s">
         <v>131</v>
       </c>
-      <c r="CX4">
+      <c r="DC4">
         <v>55</v>
       </c>
-      <c r="CY4">
+      <c r="DD4">
         <v>120</v>
       </c>
-      <c r="DB4">
+      <c r="DG4">
         <v>2</v>
       </c>
-      <c r="DC4">
+      <c r="DH4">
         <v>120</v>
       </c>
-      <c r="DF4">
+      <c r="DK4">
         <v>11</v>
       </c>
-      <c r="DG4">
+      <c r="DL4">
         <v>120</v>
       </c>
-      <c r="DH4">
+      <c r="DM4">
         <v>6</v>
       </c>
-      <c r="DI4">
+      <c r="DN4">
         <v>120</v>
       </c>
-      <c r="DJ4">
+      <c r="DO4">
         <v>8</v>
       </c>
-      <c r="DK4">
+      <c r="DP4">
         <v>120</v>
       </c>
-      <c r="DN4">
-        <v>0</v>
-      </c>
-      <c r="DO4">
+      <c r="DS4">
+        <v>0</v>
+      </c>
+      <c r="DT4">
         <v>120</v>
       </c>
-      <c r="DP4">
+      <c r="DU4">
         <v>6</v>
       </c>
-      <c r="DQ4">
+      <c r="DV4">
         <v>120</v>
       </c>
-      <c r="DT4">
+      <c r="DY4">
         <v>4</v>
       </c>
-      <c r="DU4">
+      <c r="DZ4">
         <v>120</v>
       </c>
-      <c r="DV4">
+      <c r="EA4">
         <v>1</v>
       </c>
-      <c r="DW4">
+      <c r="EB4">
         <v>120</v>
       </c>
-      <c r="DX4">
+      <c r="EC4">
         <v>4</v>
       </c>
-      <c r="DY4">
+      <c r="ED4">
         <v>120</v>
       </c>
-      <c r="DZ4">
+      <c r="EE4">
         <v>1</v>
       </c>
-      <c r="EA4">
+      <c r="EF4">
         <v>120</v>
       </c>
-      <c r="EB4" t="s">
+      <c r="EG4" t="s">
         <v>138</v>
       </c>
-      <c r="EC4" t="s">
+      <c r="EH4" t="s">
         <v>161</v>
       </c>
-      <c r="ED4" t="s">
+      <c r="EI4" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="5" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>162</v>
       </c>
@@ -2681,200 +2738,209 @@
       <c r="AS5">
         <v>125</v>
       </c>
-      <c r="AT5">
+      <c r="AT5" s="16">
+        <v>125</v>
+      </c>
+      <c r="AU5">
         <v>25.4</v>
       </c>
-      <c r="AU5">
+      <c r="AV5">
         <v>-3.9</v>
       </c>
-      <c r="AV5">
+      <c r="AW5">
         <v>5.59</v>
       </c>
-      <c r="AW5" t="s">
+      <c r="AX5" t="s">
         <v>130</v>
       </c>
-      <c r="AX5" t="s">
+      <c r="AY5" t="s">
         <v>131</v>
       </c>
-      <c r="AY5" t="s">
-        <v>132</v>
-      </c>
-      <c r="AZ5" s="9" t="s">
+      <c r="AZ5" t="s">
+        <v>132</v>
+      </c>
+      <c r="BA5" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="BA5">
+      <c r="BB5">
         <v>125</v>
       </c>
-      <c r="BB5" s="9">
+      <c r="BC5" s="16">
+        <v>125</v>
+      </c>
+      <c r="BD5" s="9">
         <v>37.4</v>
       </c>
-      <c r="BC5" s="9">
+      <c r="BE5" s="9">
         <v>-2.7</v>
       </c>
-      <c r="BD5" s="9">
+      <c r="BF5" s="9">
         <v>10.06</v>
       </c>
-      <c r="BE5" t="s">
+      <c r="BG5" t="s">
         <v>130</v>
       </c>
-      <c r="BF5" t="s">
+      <c r="BH5" t="s">
         <v>131</v>
       </c>
-      <c r="BG5" t="s">
-        <v>132</v>
-      </c>
-      <c r="BX5" t="s">
+      <c r="BI5" t="s">
+        <v>132</v>
+      </c>
+      <c r="CA5" t="s">
         <v>135</v>
       </c>
-      <c r="BY5">
+      <c r="CB5">
         <v>125</v>
       </c>
-      <c r="BZ5" s="16">
+      <c r="CC5" s="16">
         <v>125</v>
       </c>
-      <c r="CA5">
+      <c r="CD5">
         <v>12.6</v>
       </c>
-      <c r="CB5">
+      <c r="CE5">
         <v>-1.6</v>
       </c>
-      <c r="CC5">
+      <c r="CF5">
         <v>6.71</v>
       </c>
-      <c r="CD5" t="s">
+      <c r="CG5" t="s">
         <v>130</v>
       </c>
-      <c r="CE5" t="s">
+      <c r="CH5" t="s">
         <v>131</v>
       </c>
-      <c r="CF5" t="s">
-        <v>132</v>
-      </c>
-      <c r="CG5" t="s">
+      <c r="CI5" t="s">
+        <v>132</v>
+      </c>
+      <c r="CJ5" t="s">
         <v>136</v>
       </c>
-      <c r="CH5">
+      <c r="CK5">
         <v>125</v>
       </c>
-      <c r="CI5">
+      <c r="CL5" s="16">
+        <v>125</v>
+      </c>
+      <c r="CM5">
         <v>75.400000000000006</v>
       </c>
-      <c r="CJ5">
+      <c r="CN5">
         <v>-0.1</v>
       </c>
-      <c r="CK5">
+      <c r="CO5">
         <v>2.2999999999999998</v>
       </c>
-      <c r="CL5" t="s">
+      <c r="CP5" t="s">
         <v>130</v>
       </c>
-      <c r="CM5" t="s">
+      <c r="CQ5" t="s">
         <v>131</v>
       </c>
-      <c r="CN5" t="s">
-        <v>132</v>
-      </c>
-      <c r="CO5" t="s">
+      <c r="CR5" t="s">
+        <v>132</v>
+      </c>
+      <c r="CS5" t="s">
         <v>172</v>
       </c>
-      <c r="CP5" t="s">
+      <c r="CT5" t="s">
         <v>137</v>
       </c>
-      <c r="CQ5">
+      <c r="CU5">
         <v>113</v>
       </c>
-      <c r="CS5">
+      <c r="CX5">
         <v>-1.3838053097345131</v>
       </c>
-      <c r="CT5">
+      <c r="CY5">
         <v>28</v>
       </c>
-      <c r="CU5" t="s">
+      <c r="CZ5" t="s">
         <v>130</v>
       </c>
-      <c r="CV5" t="s">
-        <v>132</v>
-      </c>
-      <c r="CW5" t="s">
+      <c r="DA5" t="s">
+        <v>132</v>
+      </c>
+      <c r="DB5" t="s">
         <v>131</v>
       </c>
-      <c r="CX5">
+      <c r="DC5">
         <v>63</v>
       </c>
-      <c r="CY5">
+      <c r="DD5">
         <v>125</v>
       </c>
-      <c r="DB5">
+      <c r="DG5">
         <v>9</v>
       </c>
-      <c r="DC5">
+      <c r="DH5">
         <v>125</v>
       </c>
-      <c r="DF5">
+      <c r="DK5">
         <v>15</v>
       </c>
-      <c r="DG5">
+      <c r="DL5">
         <v>125</v>
       </c>
-      <c r="DH5">
+      <c r="DM5">
         <v>4</v>
       </c>
-      <c r="DI5">
+      <c r="DN5">
         <v>125</v>
       </c>
-      <c r="DJ5">
+      <c r="DO5">
         <v>6</v>
       </c>
-      <c r="DK5">
+      <c r="DP5">
         <v>125</v>
       </c>
-      <c r="DN5">
-        <v>0</v>
-      </c>
-      <c r="DO5">
+      <c r="DS5">
+        <v>0</v>
+      </c>
+      <c r="DT5">
         <v>125</v>
       </c>
-      <c r="DP5">
+      <c r="DU5">
         <v>6</v>
       </c>
-      <c r="DQ5">
+      <c r="DV5">
         <v>125</v>
       </c>
-      <c r="DT5">
+      <c r="DY5">
         <v>13</v>
       </c>
-      <c r="DU5">
+      <c r="DZ5">
         <v>125</v>
       </c>
-      <c r="DV5">
-        <v>0</v>
-      </c>
-      <c r="DW5">
+      <c r="EA5">
+        <v>0</v>
+      </c>
+      <c r="EB5">
         <v>125</v>
       </c>
-      <c r="DX5">
+      <c r="EC5">
         <v>4</v>
       </c>
-      <c r="DY5">
+      <c r="ED5">
         <v>125</v>
       </c>
-      <c r="DZ5">
+      <c r="EE5">
         <v>1</v>
       </c>
-      <c r="EA5">
+      <c r="EF5">
         <v>125</v>
       </c>
-      <c r="EB5" t="s">
+      <c r="EG5" t="s">
         <v>162</v>
       </c>
-      <c r="EC5" t="s">
+      <c r="EH5" t="s">
         <v>161</v>
       </c>
-      <c r="ED5" t="s">
+      <c r="EI5" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>177</v>
       </c>
@@ -2974,17 +3040,17 @@
       <c r="AQ6" t="s">
         <v>132</v>
       </c>
-      <c r="EB6" t="s">
+      <c r="EG6" t="s">
         <v>138</v>
       </c>
-      <c r="EC6" t="s">
+      <c r="EH6" t="s">
         <v>161</v>
       </c>
-      <c r="ED6" t="s">
+      <c r="EI6" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="7" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>182</v>
       </c>
@@ -3084,17 +3150,17 @@
       <c r="AQ7" t="s">
         <v>132</v>
       </c>
-      <c r="EB7" t="s">
+      <c r="EG7" t="s">
         <v>138</v>
       </c>
-      <c r="EC7" t="s">
+      <c r="EH7" t="s">
         <v>161</v>
       </c>
-      <c r="ED7" t="s">
+      <c r="EI7" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="8" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>184</v>
       </c>
@@ -3194,17 +3260,17 @@
       <c r="AQ8" t="s">
         <v>132</v>
       </c>
-      <c r="EB8" t="s">
+      <c r="EG8" t="s">
         <v>162</v>
       </c>
-      <c r="EC8" t="s">
+      <c r="EH8" t="s">
         <v>161</v>
       </c>
-      <c r="ED8" t="s">
+      <c r="EI8" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="9" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>185</v>
       </c>
@@ -3304,17 +3370,17 @@
       <c r="AQ9" t="s">
         <v>132</v>
       </c>
-      <c r="EB9" t="s">
+      <c r="EG9" t="s">
         <v>138</v>
       </c>
-      <c r="EC9" t="s">
+      <c r="EH9" t="s">
         <v>161</v>
       </c>
-      <c r="ED9" t="s">
+      <c r="EI9" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="10" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>188</v>
       </c>
@@ -3414,17 +3480,17 @@
       <c r="AQ10" t="s">
         <v>132</v>
       </c>
-      <c r="EB10" t="s">
+      <c r="EG10" t="s">
         <v>138</v>
       </c>
-      <c r="EC10" t="s">
+      <c r="EH10" t="s">
         <v>161</v>
       </c>
-      <c r="ED10" t="s">
+      <c r="EI10" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="11" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>162</v>
       </c>
@@ -3524,17 +3590,17 @@
       <c r="AQ11" t="s">
         <v>132</v>
       </c>
-      <c r="EB11" t="s">
+      <c r="EG11" t="s">
         <v>162</v>
       </c>
-      <c r="EC11" t="s">
+      <c r="EH11" t="s">
         <v>161</v>
       </c>
-      <c r="ED11" t="s">
+      <c r="EI11" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="12" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>191</v>
       </c>
@@ -3661,128 +3727,134 @@
       <c r="AS12">
         <v>54</v>
       </c>
-      <c r="AT12">
+      <c r="AT12" s="16">
+        <v>72</v>
+      </c>
+      <c r="AU12">
         <v>26.86</v>
       </c>
-      <c r="AU12">
+      <c r="AV12">
         <v>23.61</v>
       </c>
-      <c r="AV12">
+      <c r="AW12">
         <v>6.64</v>
       </c>
-      <c r="AW12" t="s">
+      <c r="AX12" t="s">
         <v>198</v>
       </c>
-      <c r="AX12" t="s">
-        <v>132</v>
-      </c>
       <c r="AY12" t="s">
         <v>132</v>
       </c>
       <c r="AZ12" t="s">
+        <v>132</v>
+      </c>
+      <c r="BA12" t="s">
         <v>134</v>
       </c>
-      <c r="BA12">
+      <c r="BB12">
         <v>54</v>
       </c>
-      <c r="BB12">
+      <c r="BC12" s="16">
+        <v>72</v>
+      </c>
+      <c r="BD12">
         <v>24.1</v>
       </c>
-      <c r="BC12">
+      <c r="BE12">
         <v>22.65</v>
       </c>
-      <c r="BD12">
+      <c r="BF12">
         <v>5.81</v>
       </c>
-      <c r="BE12" t="s">
+      <c r="BG12" t="s">
         <v>198</v>
       </c>
-      <c r="BF12" t="s">
-        <v>132</v>
-      </c>
-      <c r="BG12" t="s">
-        <v>132</v>
-      </c>
-      <c r="BX12" t="s">
+      <c r="BH12" t="s">
+        <v>132</v>
+      </c>
+      <c r="BI12" t="s">
+        <v>132</v>
+      </c>
+      <c r="CA12" t="s">
         <v>199</v>
       </c>
-      <c r="BY12">
+      <c r="CB12">
         <v>54</v>
       </c>
-      <c r="BZ12" s="16">
+      <c r="CC12" s="16">
         <v>72</v>
       </c>
-      <c r="CA12">
+      <c r="CD12">
         <v>11.58</v>
       </c>
-      <c r="CB12">
+      <c r="CE12">
         <v>9.56</v>
       </c>
-      <c r="CC12">
+      <c r="CF12">
         <v>4.03</v>
       </c>
-      <c r="CD12" t="s">
+      <c r="CG12" t="s">
         <v>198</v>
       </c>
-      <c r="CE12" t="s">
-        <v>132</v>
-      </c>
-      <c r="CF12" t="s">
-        <v>132</v>
-      </c>
-      <c r="CX12">
+      <c r="CH12" t="s">
+        <v>132</v>
+      </c>
+      <c r="CI12" t="s">
+        <v>132</v>
+      </c>
+      <c r="DC12">
         <v>23</v>
       </c>
-      <c r="CY12">
+      <c r="DD12">
         <v>72</v>
       </c>
-      <c r="DB12">
+      <c r="DG12">
         <v>6</v>
       </c>
-      <c r="DC12">
+      <c r="DH12">
         <v>72</v>
       </c>
-      <c r="DF12">
+      <c r="DK12">
         <v>4</v>
       </c>
-      <c r="DG12">
+      <c r="DL12">
         <v>72</v>
       </c>
-      <c r="DH12">
+      <c r="DM12">
         <v>4</v>
       </c>
-      <c r="DI12">
+      <c r="DN12">
         <v>72</v>
       </c>
-      <c r="DP12">
+      <c r="DU12">
         <v>2</v>
       </c>
-      <c r="DQ12">
+      <c r="DV12">
         <v>72</v>
       </c>
-      <c r="DT12">
+      <c r="DY12">
         <v>1</v>
       </c>
-      <c r="DU12">
+      <c r="DZ12">
         <v>72</v>
       </c>
-      <c r="DZ12">
+      <c r="EE12">
         <v>1</v>
       </c>
-      <c r="EA12">
+      <c r="EF12">
         <v>72</v>
       </c>
-      <c r="EB12" t="s">
+      <c r="EG12" t="s">
         <v>162</v>
       </c>
-      <c r="EC12" t="s">
+      <c r="EH12" t="s">
         <v>161</v>
       </c>
-      <c r="ED12" t="s">
+      <c r="EI12" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="13" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>200</v>
       </c>
@@ -3909,128 +3981,134 @@
       <c r="AS13">
         <v>49</v>
       </c>
-      <c r="AT13">
+      <c r="AT13" s="16">
+        <v>65</v>
+      </c>
+      <c r="AU13">
         <v>26.2</v>
       </c>
-      <c r="AU13">
+      <c r="AV13">
         <v>23.41</v>
       </c>
-      <c r="AV13">
+      <c r="AW13">
         <v>6.14</v>
       </c>
-      <c r="AW13" t="s">
+      <c r="AX13" t="s">
         <v>198</v>
       </c>
-      <c r="AX13" t="s">
-        <v>132</v>
-      </c>
       <c r="AY13" t="s">
         <v>132</v>
       </c>
       <c r="AZ13" t="s">
+        <v>132</v>
+      </c>
+      <c r="BA13" t="s">
         <v>134</v>
       </c>
-      <c r="BA13">
+      <c r="BB13">
         <v>49</v>
       </c>
-      <c r="BB13">
+      <c r="BC13" s="16">
+        <v>65</v>
+      </c>
+      <c r="BD13">
         <v>23.65</v>
       </c>
-      <c r="BC13">
+      <c r="BE13">
         <v>21.82</v>
       </c>
-      <c r="BD13">
+      <c r="BF13">
         <v>5.85</v>
       </c>
-      <c r="BE13" t="s">
+      <c r="BG13" t="s">
         <v>198</v>
       </c>
-      <c r="BF13" t="s">
-        <v>132</v>
-      </c>
-      <c r="BG13" t="s">
-        <v>132</v>
-      </c>
-      <c r="BX13" t="s">
+      <c r="BH13" t="s">
+        <v>132</v>
+      </c>
+      <c r="BI13" t="s">
+        <v>132</v>
+      </c>
+      <c r="CA13" t="s">
         <v>199</v>
       </c>
-      <c r="BY13">
+      <c r="CB13">
         <v>49</v>
       </c>
-      <c r="BZ13" s="16">
+      <c r="CC13" s="16">
         <v>65</v>
       </c>
-      <c r="CA13">
+      <c r="CD13">
         <v>12.91</v>
       </c>
-      <c r="CB13">
+      <c r="CE13">
         <v>9.8800000000000008</v>
       </c>
-      <c r="CC13">
+      <c r="CF13">
         <v>4.1500000000000004</v>
       </c>
-      <c r="CD13" t="s">
+      <c r="CG13" t="s">
         <v>198</v>
       </c>
-      <c r="CE13" t="s">
-        <v>132</v>
-      </c>
-      <c r="CF13" t="s">
-        <v>132</v>
-      </c>
-      <c r="CX13">
+      <c r="CH13" t="s">
+        <v>132</v>
+      </c>
+      <c r="CI13" t="s">
+        <v>132</v>
+      </c>
+      <c r="DC13">
         <v>14</v>
       </c>
-      <c r="CY13">
+      <c r="DD13">
         <v>65</v>
       </c>
-      <c r="DB13">
+      <c r="DG13">
         <v>3</v>
       </c>
-      <c r="DC13">
+      <c r="DH13">
         <v>65</v>
       </c>
-      <c r="DF13">
+      <c r="DK13">
         <v>4</v>
       </c>
-      <c r="DG13">
+      <c r="DL13">
         <v>65</v>
       </c>
-      <c r="DH13">
-        <v>0</v>
-      </c>
-      <c r="DI13">
+      <c r="DM13">
+        <v>0</v>
+      </c>
+      <c r="DN13">
         <v>65</v>
       </c>
-      <c r="DP13">
-        <v>0</v>
-      </c>
-      <c r="DQ13">
+      <c r="DU13">
+        <v>0</v>
+      </c>
+      <c r="DV13">
         <v>65</v>
       </c>
-      <c r="DT13">
+      <c r="DY13">
         <v>3</v>
       </c>
-      <c r="DU13">
+      <c r="DZ13">
         <v>65</v>
       </c>
-      <c r="DZ13">
+      <c r="EE13">
         <v>2</v>
       </c>
-      <c r="EA13">
+      <c r="EF13">
         <v>65</v>
       </c>
-      <c r="EB13" t="s">
+      <c r="EG13" t="s">
         <v>138</v>
       </c>
-      <c r="EC13" t="s">
+      <c r="EH13" t="s">
         <v>161</v>
       </c>
-      <c r="ED13" t="s">
+      <c r="EI13" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="14" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>205</v>
       </c>
@@ -4157,128 +4235,134 @@
       <c r="AS14">
         <v>51</v>
       </c>
-      <c r="AT14">
+      <c r="AT14" s="16">
+        <v>68</v>
+      </c>
+      <c r="AU14">
         <v>27.26</v>
       </c>
-      <c r="AU14">
+      <c r="AV14">
         <v>22.22</v>
       </c>
-      <c r="AV14">
+      <c r="AW14">
         <v>6.5</v>
       </c>
-      <c r="AW14" t="s">
+      <c r="AX14" t="s">
         <v>198</v>
       </c>
-      <c r="AX14" t="s">
-        <v>132</v>
-      </c>
       <c r="AY14" t="s">
         <v>132</v>
       </c>
       <c r="AZ14" t="s">
+        <v>132</v>
+      </c>
+      <c r="BA14" t="s">
         <v>134</v>
       </c>
-      <c r="BA14">
+      <c r="BB14">
         <v>51</v>
       </c>
-      <c r="BB14">
+      <c r="BC14" s="16">
+        <v>68</v>
+      </c>
+      <c r="BD14">
         <v>24.59</v>
       </c>
-      <c r="BC14">
+      <c r="BE14">
         <v>22.53</v>
       </c>
-      <c r="BD14">
+      <c r="BF14">
         <v>5.41</v>
       </c>
-      <c r="BE14" t="s">
+      <c r="BG14" t="s">
         <v>198</v>
       </c>
-      <c r="BF14" t="s">
-        <v>132</v>
-      </c>
-      <c r="BG14" t="s">
-        <v>132</v>
-      </c>
-      <c r="BX14" t="s">
+      <c r="BH14" t="s">
+        <v>132</v>
+      </c>
+      <c r="BI14" t="s">
+        <v>132</v>
+      </c>
+      <c r="CA14" t="s">
         <v>199</v>
       </c>
-      <c r="BY14">
+      <c r="CB14">
         <v>51</v>
       </c>
-      <c r="BZ14" s="16">
+      <c r="CC14" s="16">
         <v>68</v>
       </c>
-      <c r="CA14">
+      <c r="CD14">
         <v>11.54</v>
       </c>
-      <c r="CB14">
+      <c r="CE14">
         <v>9.06</v>
       </c>
-      <c r="CC14">
+      <c r="CF14">
         <v>4.08</v>
       </c>
-      <c r="CD14" t="s">
+      <c r="CG14" t="s">
         <v>198</v>
       </c>
-      <c r="CE14" t="s">
-        <v>132</v>
-      </c>
-      <c r="CF14" t="s">
-        <v>132</v>
-      </c>
-      <c r="CX14">
+      <c r="CH14" t="s">
+        <v>132</v>
+      </c>
+      <c r="CI14" t="s">
+        <v>132</v>
+      </c>
+      <c r="DC14">
         <v>23</v>
       </c>
-      <c r="CY14">
+      <c r="DD14">
         <v>68</v>
       </c>
-      <c r="DB14">
+      <c r="DG14">
         <v>2</v>
       </c>
-      <c r="DC14">
+      <c r="DH14">
         <v>68</v>
       </c>
-      <c r="DF14">
+      <c r="DK14">
         <v>5</v>
       </c>
-      <c r="DG14">
+      <c r="DL14">
         <v>68</v>
       </c>
-      <c r="DH14">
+      <c r="DM14">
         <v>2</v>
       </c>
-      <c r="DI14">
+      <c r="DN14">
         <v>68</v>
       </c>
-      <c r="DP14">
+      <c r="DU14">
         <v>8</v>
       </c>
-      <c r="DQ14">
+      <c r="DV14">
         <v>68</v>
       </c>
-      <c r="DT14">
+      <c r="DY14">
         <v>5</v>
       </c>
-      <c r="DU14">
+      <c r="DZ14">
         <v>68</v>
       </c>
-      <c r="DZ14">
-        <v>0</v>
-      </c>
-      <c r="EA14">
+      <c r="EE14">
+        <v>0</v>
+      </c>
+      <c r="EF14">
         <v>68</v>
       </c>
-      <c r="EB14" t="s">
+      <c r="EG14" t="s">
         <v>138</v>
       </c>
-      <c r="EC14" t="s">
+      <c r="EH14" t="s">
         <v>161</v>
       </c>
-      <c r="ED14" t="s">
+      <c r="EI14" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="15" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>209</v>
       </c>
@@ -4405,128 +4489,134 @@
       <c r="AS15">
         <v>56</v>
       </c>
-      <c r="AT15">
+      <c r="AT15" s="16">
+        <v>71</v>
+      </c>
+      <c r="AU15">
         <v>27.49</v>
       </c>
-      <c r="AU15">
+      <c r="AV15">
         <v>19.52</v>
       </c>
-      <c r="AV15">
+      <c r="AW15">
         <v>5.1100000000000003</v>
       </c>
-      <c r="AW15" t="s">
+      <c r="AX15" t="s">
         <v>198</v>
       </c>
-      <c r="AX15" t="s">
-        <v>132</v>
-      </c>
       <c r="AY15" t="s">
         <v>132</v>
       </c>
       <c r="AZ15" t="s">
+        <v>132</v>
+      </c>
+      <c r="BA15" t="s">
         <v>134</v>
       </c>
-      <c r="BA15">
+      <c r="BB15">
         <v>56</v>
       </c>
-      <c r="BB15">
+      <c r="BC15" s="16">
+        <v>71</v>
+      </c>
+      <c r="BD15">
         <v>23.65</v>
       </c>
-      <c r="BC15">
+      <c r="BE15">
         <v>21.45</v>
       </c>
-      <c r="BD15">
+      <c r="BF15">
         <v>5.13</v>
       </c>
-      <c r="BE15" t="s">
+      <c r="BG15" t="s">
         <v>198</v>
       </c>
-      <c r="BF15" t="s">
-        <v>132</v>
-      </c>
-      <c r="BG15" t="s">
-        <v>132</v>
-      </c>
-      <c r="BX15" t="s">
+      <c r="BH15" t="s">
+        <v>132</v>
+      </c>
+      <c r="BI15" t="s">
+        <v>132</v>
+      </c>
+      <c r="CA15" t="s">
         <v>199</v>
       </c>
-      <c r="BY15">
+      <c r="CB15">
         <v>56</v>
       </c>
-      <c r="BZ15" s="16">
+      <c r="CC15" s="16">
         <v>71</v>
       </c>
-      <c r="CA15">
+      <c r="CD15">
         <v>12.58</v>
       </c>
-      <c r="CB15">
+      <c r="CE15">
         <v>8.5</v>
       </c>
-      <c r="CC15">
+      <c r="CF15">
         <v>4.09</v>
       </c>
-      <c r="CD15" t="s">
+      <c r="CG15" t="s">
         <v>198</v>
       </c>
-      <c r="CE15" t="s">
-        <v>132</v>
-      </c>
-      <c r="CF15" t="s">
-        <v>132</v>
-      </c>
-      <c r="CX15">
+      <c r="CH15" t="s">
+        <v>132</v>
+      </c>
+      <c r="CI15" t="s">
+        <v>132</v>
+      </c>
+      <c r="DC15">
         <v>36</v>
       </c>
-      <c r="CY15">
+      <c r="DD15">
         <v>71</v>
       </c>
-      <c r="DB15">
+      <c r="DG15">
         <v>5</v>
       </c>
-      <c r="DC15">
+      <c r="DH15">
         <v>71</v>
       </c>
-      <c r="DF15">
+      <c r="DK15">
         <v>6</v>
       </c>
-      <c r="DG15">
+      <c r="DL15">
         <v>71</v>
       </c>
-      <c r="DH15">
+      <c r="DM15">
         <v>6</v>
       </c>
-      <c r="DI15">
+      <c r="DN15">
         <v>71</v>
       </c>
-      <c r="DP15">
-        <v>0</v>
-      </c>
-      <c r="DQ15">
+      <c r="DU15">
+        <v>0</v>
+      </c>
+      <c r="DV15">
         <v>71</v>
       </c>
-      <c r="DT15">
+      <c r="DY15">
         <v>5</v>
       </c>
-      <c r="DU15">
+      <c r="DZ15">
         <v>71</v>
       </c>
-      <c r="DZ15">
+      <c r="EE15">
         <v>8</v>
       </c>
-      <c r="EA15">
+      <c r="EF15">
         <v>71</v>
       </c>
-      <c r="EB15" t="s">
+      <c r="EG15" t="s">
         <v>212</v>
       </c>
-      <c r="EC15" t="s">
+      <c r="EH15" t="s">
         <v>161</v>
       </c>
-      <c r="ED15" t="s">
+      <c r="EI15" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="16" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>213</v>
       </c>
@@ -4596,59 +4686,59 @@
       <c r="AB16" t="s">
         <v>218</v>
       </c>
-      <c r="CX16">
+      <c r="DC16">
         <v>16</v>
       </c>
-      <c r="CY16">
+      <c r="DD16">
         <v>34</v>
       </c>
-      <c r="CZ16">
-        <v>0</v>
-      </c>
-      <c r="DA16">
+      <c r="DE16">
+        <v>0</v>
+      </c>
+      <c r="DF16">
         <v>34</v>
       </c>
-      <c r="DB16">
-        <v>0</v>
-      </c>
-      <c r="DC16">
+      <c r="DG16">
+        <v>0</v>
+      </c>
+      <c r="DH16">
         <v>34</v>
       </c>
-      <c r="DD16">
+      <c r="DI16">
         <v>2</v>
       </c>
-      <c r="DE16">
+      <c r="DJ16">
         <v>34</v>
       </c>
-      <c r="DF16">
+      <c r="DK16">
         <v>7</v>
       </c>
-      <c r="DG16">
+      <c r="DL16">
         <v>34</v>
       </c>
-      <c r="DH16">
-        <v>0</v>
-      </c>
-      <c r="DI16">
+      <c r="DM16">
+        <v>0</v>
+      </c>
+      <c r="DN16">
         <v>34</v>
       </c>
-      <c r="DJ16">
+      <c r="DO16">
         <v>5</v>
       </c>
-      <c r="DK16">
+      <c r="DP16">
         <v>34</v>
       </c>
-      <c r="EB16" t="s">
+      <c r="EG16" t="s">
         <v>162</v>
       </c>
-      <c r="EC16" t="s">
+      <c r="EH16" t="s">
         <v>219</v>
       </c>
-      <c r="ED16" t="s">
+      <c r="EI16" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="17" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>220</v>
       </c>
@@ -4718,59 +4808,59 @@
       <c r="AB17" t="s">
         <v>222</v>
       </c>
-      <c r="CX17">
+      <c r="DC17">
         <v>34</v>
       </c>
-      <c r="CY17">
+      <c r="DD17">
         <v>35</v>
       </c>
-      <c r="CZ17">
+      <c r="DE17">
         <v>5</v>
       </c>
-      <c r="DA17">
+      <c r="DF17">
         <v>35</v>
       </c>
-      <c r="DB17">
-        <v>0</v>
-      </c>
-      <c r="DC17">
+      <c r="DG17">
+        <v>0</v>
+      </c>
+      <c r="DH17">
         <v>35</v>
       </c>
-      <c r="DD17">
+      <c r="DI17">
         <v>10</v>
       </c>
-      <c r="DE17">
+      <c r="DJ17">
         <v>35</v>
       </c>
-      <c r="DF17">
+      <c r="DK17">
         <v>4</v>
       </c>
-      <c r="DG17">
+      <c r="DL17">
         <v>35</v>
       </c>
-      <c r="DH17">
+      <c r="DM17">
         <v>12</v>
       </c>
-      <c r="DI17">
+      <c r="DN17">
         <v>35</v>
       </c>
-      <c r="DJ17">
+      <c r="DO17">
         <v>21</v>
       </c>
-      <c r="DK17">
+      <c r="DP17">
         <v>35</v>
       </c>
-      <c r="EB17" t="s">
+      <c r="EG17" t="s">
         <v>138</v>
       </c>
-      <c r="EC17" t="s">
+      <c r="EH17" t="s">
         <v>219</v>
       </c>
-      <c r="ED17" t="s">
+      <c r="EI17" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="18" spans="1:134" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:139" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>223</v>
       </c>
@@ -4840,59 +4930,59 @@
       <c r="AB18" t="s">
         <v>227</v>
       </c>
-      <c r="CX18">
+      <c r="DC18">
         <v>15</v>
       </c>
-      <c r="CY18">
+      <c r="DD18">
         <v>36</v>
       </c>
-      <c r="CZ18">
-        <v>0</v>
-      </c>
-      <c r="DA18">
+      <c r="DE18">
+        <v>0</v>
+      </c>
+      <c r="DF18">
         <v>36</v>
       </c>
-      <c r="DB18">
+      <c r="DG18">
         <v>3</v>
       </c>
-      <c r="DC18">
+      <c r="DH18">
         <v>36</v>
       </c>
-      <c r="DD18">
+      <c r="DI18">
         <v>1</v>
       </c>
-      <c r="DE18">
+      <c r="DJ18">
         <v>36</v>
       </c>
-      <c r="DF18">
+      <c r="DK18">
         <v>1</v>
       </c>
-      <c r="DG18">
+      <c r="DL18">
         <v>36</v>
       </c>
-      <c r="DH18">
-        <v>0</v>
-      </c>
-      <c r="DI18">
+      <c r="DM18">
+        <v>0</v>
+      </c>
+      <c r="DN18">
         <v>36</v>
       </c>
-      <c r="DJ18">
+      <c r="DO18">
         <v>5</v>
       </c>
-      <c r="DK18">
+      <c r="DP18">
         <v>36</v>
       </c>
-      <c r="EB18" t="s">
+      <c r="EG18" t="s">
         <v>212</v>
       </c>
-      <c r="EC18" t="s">
+      <c r="EH18" t="s">
         <v>219</v>
       </c>
-      <c r="ED18" t="s">
+      <c r="EI18" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="19" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>162</v>
       </c>
@@ -4959,47 +5049,47 @@
       <c r="AB19" t="s">
         <v>232</v>
       </c>
-      <c r="CX19">
+      <c r="DC19">
         <v>2</v>
       </c>
-      <c r="CY19">
+      <c r="DD19">
         <v>63</v>
       </c>
-      <c r="DD19">
+      <c r="DI19">
         <v>1</v>
       </c>
-      <c r="DE19">
+      <c r="DJ19">
         <v>63</v>
       </c>
-      <c r="DH19">
+      <c r="DM19">
         <v>1</v>
       </c>
-      <c r="DI19">
+      <c r="DN19">
         <v>63</v>
       </c>
-      <c r="DJ19" s="8">
-        <v>0</v>
-      </c>
-      <c r="DK19">
+      <c r="DO19" s="8">
+        <v>0</v>
+      </c>
+      <c r="DP19">
         <v>63</v>
       </c>
-      <c r="DN19">
+      <c r="DS19">
         <v>1</v>
       </c>
-      <c r="DO19">
+      <c r="DT19">
         <v>59</v>
       </c>
-      <c r="EB19" t="s">
+      <c r="EG19" t="s">
         <v>162</v>
       </c>
-      <c r="EC19" t="s">
+      <c r="EH19" t="s">
         <v>219</v>
       </c>
-      <c r="ED19" t="s">
+      <c r="EI19" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="20" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>233</v>
       </c>
@@ -5072,47 +5162,47 @@
       <c r="AB20" t="s">
         <v>232</v>
       </c>
-      <c r="CX20">
+      <c r="DC20">
         <v>32</v>
       </c>
-      <c r="CY20">
+      <c r="DD20">
         <v>63</v>
       </c>
-      <c r="DD20">
+      <c r="DI20">
         <v>7</v>
       </c>
-      <c r="DE20">
+      <c r="DJ20">
         <v>63</v>
       </c>
-      <c r="DH20">
+      <c r="DM20">
         <v>16</v>
       </c>
-      <c r="DI20">
+      <c r="DN20">
         <v>63</v>
       </c>
-      <c r="DJ20">
+      <c r="DO20">
         <v>16</v>
       </c>
-      <c r="DK20">
+      <c r="DP20">
         <v>63</v>
       </c>
-      <c r="DN20">
+      <c r="DS20">
         <v>5</v>
       </c>
-      <c r="DO20">
+      <c r="DT20">
         <v>62</v>
       </c>
-      <c r="EB20" t="s">
+      <c r="EG20" t="s">
         <v>138</v>
       </c>
-      <c r="EC20" t="s">
+      <c r="EH20" t="s">
         <v>219</v>
       </c>
-      <c r="ED20" t="s">
+      <c r="EI20" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="21" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>234</v>
       </c>
@@ -5182,47 +5272,47 @@
       <c r="AB21" t="s">
         <v>140</v>
       </c>
-      <c r="CX21">
+      <c r="DC21">
         <v>1</v>
       </c>
-      <c r="CY21">
+      <c r="DD21">
         <v>12</v>
       </c>
-      <c r="DH21">
+      <c r="DM21">
         <v>1</v>
       </c>
-      <c r="DI21">
+      <c r="DN21">
         <v>12</v>
       </c>
-      <c r="DJ21">
-        <v>0</v>
-      </c>
-      <c r="DK21">
+      <c r="DO21">
+        <v>0</v>
+      </c>
+      <c r="DP21">
         <v>12</v>
       </c>
-      <c r="DL21">
-        <v>0</v>
-      </c>
-      <c r="DM21">
+      <c r="DQ21">
+        <v>0</v>
+      </c>
+      <c r="DR21">
         <v>12</v>
       </c>
-      <c r="DN21">
-        <v>0</v>
-      </c>
-      <c r="DO21">
+      <c r="DS21">
+        <v>0</v>
+      </c>
+      <c r="DT21">
         <v>12</v>
       </c>
-      <c r="EB21" t="s">
+      <c r="EG21" t="s">
         <v>138</v>
       </c>
-      <c r="EC21" t="s">
+      <c r="EH21" t="s">
         <v>219</v>
       </c>
-      <c r="ED21" t="s">
+      <c r="EI21" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="22" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>237</v>
       </c>
@@ -5292,47 +5382,47 @@
       <c r="AB22" t="s">
         <v>140</v>
       </c>
-      <c r="CX22">
+      <c r="DC22">
         <v>1</v>
       </c>
-      <c r="CY22">
+      <c r="DD22">
         <v>12</v>
       </c>
-      <c r="DH22">
-        <v>0</v>
-      </c>
-      <c r="DI22">
+      <c r="DM22">
+        <v>0</v>
+      </c>
+      <c r="DN22">
         <v>12</v>
       </c>
-      <c r="DJ22">
+      <c r="DO22">
         <v>1</v>
       </c>
-      <c r="DK22">
+      <c r="DP22">
         <v>12</v>
       </c>
-      <c r="DL22">
-        <v>0</v>
-      </c>
-      <c r="DM22">
+      <c r="DQ22">
+        <v>0</v>
+      </c>
+      <c r="DR22">
         <v>12</v>
       </c>
-      <c r="DN22">
-        <v>0</v>
-      </c>
-      <c r="DO22">
+      <c r="DS22">
+        <v>0</v>
+      </c>
+      <c r="DT22">
         <v>12</v>
       </c>
-      <c r="EB22" t="s">
+      <c r="EG22" t="s">
         <v>138</v>
       </c>
-      <c r="EC22" t="s">
+      <c r="EH22" t="s">
         <v>219</v>
       </c>
-      <c r="ED22" t="s">
+      <c r="EI22" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="23" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>162</v>
       </c>
@@ -5402,47 +5492,47 @@
       <c r="AB23" t="s">
         <v>190</v>
       </c>
-      <c r="CX23">
+      <c r="DC23">
         <v>1</v>
       </c>
-      <c r="CY23">
+      <c r="DD23">
         <v>24</v>
       </c>
-      <c r="DH23">
-        <v>0</v>
-      </c>
-      <c r="DI23">
+      <c r="DM23">
+        <v>0</v>
+      </c>
+      <c r="DN23">
         <v>24</v>
       </c>
-      <c r="DJ23">
-        <v>0</v>
-      </c>
-      <c r="DK23">
+      <c r="DO23">
+        <v>0</v>
+      </c>
+      <c r="DP23">
         <v>24</v>
       </c>
-      <c r="DL23">
-        <v>0</v>
-      </c>
-      <c r="DM23">
+      <c r="DQ23">
+        <v>0</v>
+      </c>
+      <c r="DR23">
         <v>24</v>
       </c>
-      <c r="DN23">
-        <v>0</v>
-      </c>
-      <c r="DO23">
+      <c r="DS23">
+        <v>0</v>
+      </c>
+      <c r="DT23">
         <v>24</v>
       </c>
-      <c r="EB23" t="s">
+      <c r="EG23" t="s">
         <v>162</v>
       </c>
-      <c r="EC23" t="s">
+      <c r="EH23" t="s">
         <v>219</v>
       </c>
-      <c r="ED23" t="s">
+      <c r="EI23" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="24" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>237</v>
       </c>
@@ -5500,23 +5590,23 @@
       <c r="AB24" t="s">
         <v>151</v>
       </c>
-      <c r="CX24" s="6">
+      <c r="DC24" s="6">
         <v>6</v>
       </c>
-      <c r="CY24" s="6">
+      <c r="DD24" s="6">
         <v>15</v>
       </c>
-      <c r="EB24" t="s">
+      <c r="EG24" t="s">
         <v>138</v>
       </c>
-      <c r="EC24" t="s">
+      <c r="EH24" t="s">
         <v>219</v>
       </c>
-      <c r="ED24" t="s">
+      <c r="EI24" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="25" spans="1:134" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:139" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>241</v>
       </c>
@@ -5574,23 +5664,23 @@
       <c r="AB25" t="s">
         <v>151</v>
       </c>
-      <c r="CX25" s="6">
+      <c r="DC25" s="6">
         <v>1</v>
       </c>
-      <c r="CY25" s="6">
+      <c r="DD25" s="6">
         <v>13</v>
       </c>
-      <c r="EB25" t="s">
+      <c r="EG25" t="s">
         <v>138</v>
       </c>
-      <c r="EC25" t="s">
+      <c r="EH25" t="s">
         <v>219</v>
       </c>
-      <c r="ED25" t="s">
+      <c r="EI25" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="26" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>162</v>
       </c>
@@ -5648,23 +5738,23 @@
       <c r="AB26" t="s">
         <v>151</v>
       </c>
-      <c r="CX26" s="6">
+      <c r="DC26" s="6">
         <v>2</v>
       </c>
-      <c r="CY26" s="6">
+      <c r="DD26" s="6">
         <v>14</v>
       </c>
-      <c r="EB26" t="s">
+      <c r="EG26" t="s">
         <v>162</v>
       </c>
-      <c r="EC26" t="s">
+      <c r="EH26" t="s">
         <v>219</v>
       </c>
-      <c r="ED26" t="s">
+      <c r="EI26" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="27" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A27" s="10" t="s">
         <v>127</v>
       </c>
@@ -5743,71 +5833,71 @@
       <c r="AH27" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="CG27" s="10" t="s">
+      <c r="CJ27" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="CH27" s="10">
+      <c r="CK27" s="10">
         <v>201</v>
       </c>
-      <c r="CJ27" s="10">
+      <c r="CN27" s="10">
         <v>-1.2</v>
       </c>
-      <c r="CK27" s="11">
+      <c r="CO27" s="11">
         <v>6.4</v>
       </c>
-      <c r="CL27" s="10" t="s">
+      <c r="CP27" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="CM27" s="10" t="s">
+      <c r="CQ27" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="CN27" s="10" t="s">
+      <c r="CR27" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="CO27" s="10" t="s">
+      <c r="CS27" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="CZ27" s="11">
+      <c r="DE27" s="11">
         <v>7</v>
       </c>
-      <c r="DA27" s="11">
+      <c r="DF27" s="11">
         <v>201</v>
       </c>
-      <c r="DB27" s="11">
+      <c r="DG27" s="11">
         <v>28</v>
       </c>
-      <c r="DC27" s="11">
+      <c r="DH27" s="11">
         <v>201</v>
       </c>
-      <c r="DJ27" s="11">
+      <c r="DO27" s="11">
         <v>12</v>
       </c>
-      <c r="DK27" s="11">
+      <c r="DP27" s="11">
         <v>201</v>
       </c>
-      <c r="DT27" s="10">
+      <c r="DY27" s="10">
         <v>30</v>
       </c>
-      <c r="DU27" s="10">
+      <c r="DZ27" s="10">
         <v>201</v>
       </c>
-      <c r="DZ27" s="10">
+      <c r="EE27" s="10">
         <v>8</v>
       </c>
-      <c r="EA27" s="10">
+      <c r="EF27" s="10">
         <v>201</v>
       </c>
-      <c r="EB27" t="s">
+      <c r="EG27" t="s">
         <v>138</v>
       </c>
-      <c r="EC27" t="s">
+      <c r="EH27" t="s">
         <v>266</v>
       </c>
-      <c r="ED27" t="s">
+      <c r="EI27" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="28" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A28" s="10" t="s">
         <v>245</v>
       </c>
@@ -5886,71 +5976,71 @@
       <c r="AH28" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="CG28" s="10" t="s">
+      <c r="CJ28" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="CH28" s="10">
+      <c r="CK28" s="10">
         <v>102</v>
       </c>
-      <c r="CJ28" s="10">
+      <c r="CN28" s="10">
         <v>1.4</v>
       </c>
-      <c r="CK28" s="11">
+      <c r="CO28" s="11">
         <v>6.4</v>
       </c>
-      <c r="CL28" s="10" t="s">
+      <c r="CP28" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="CM28" s="10" t="s">
+      <c r="CQ28" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="CN28" s="10" t="s">
+      <c r="CR28" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="CO28" s="10" t="s">
+      <c r="CS28" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="CZ28" s="11">
+      <c r="DE28" s="11">
         <v>12</v>
       </c>
-      <c r="DA28" s="11">
+      <c r="DF28" s="11">
         <v>102</v>
       </c>
-      <c r="DB28" s="11">
+      <c r="DG28" s="11">
         <v>10</v>
       </c>
-      <c r="DC28" s="11">
+      <c r="DH28" s="11">
         <v>102</v>
       </c>
-      <c r="DJ28" s="11">
+      <c r="DO28" s="11">
         <v>21</v>
       </c>
-      <c r="DK28" s="11">
+      <c r="DP28" s="11">
         <v>102</v>
       </c>
-      <c r="DT28" s="10">
+      <c r="DY28" s="10">
         <v>11</v>
       </c>
-      <c r="DU28" s="10">
+      <c r="DZ28" s="10">
         <v>102</v>
       </c>
-      <c r="DZ28" s="10">
+      <c r="EE28" s="10">
         <v>11</v>
       </c>
-      <c r="EA28" s="10">
+      <c r="EF28" s="10">
         <v>102</v>
       </c>
-      <c r="EB28" t="s">
+      <c r="EG28" t="s">
         <v>212</v>
       </c>
-      <c r="EC28" t="s">
+      <c r="EH28" t="s">
         <v>266</v>
       </c>
-      <c r="ED28" t="s">
+      <c r="EI28" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="29" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>258</v>
       </c>
@@ -6083,101 +6173,107 @@
       <c r="AS29" s="11">
         <v>6</v>
       </c>
-      <c r="AT29" s="11">
+      <c r="AT29" s="16">
+        <v>15</v>
+      </c>
+      <c r="AU29" s="11">
         <v>19.75</v>
       </c>
-      <c r="AU29" s="11">
+      <c r="AV29" s="11">
         <v>19.670000000000002</v>
       </c>
-      <c r="AV29" s="11">
+      <c r="AW29" s="11">
         <v>3.61</v>
       </c>
-      <c r="AW29" s="11" t="s">
+      <c r="AX29" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="AX29" s="11" t="s">
-        <v>132</v>
-      </c>
       <c r="AY29" s="11" t="s">
         <v>132</v>
       </c>
       <c r="AZ29" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="BA29" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="BA29" s="11">
+      <c r="BB29" s="11">
         <v>6</v>
       </c>
-      <c r="BB29" s="11">
+      <c r="BC29" s="16">
+        <v>15</v>
+      </c>
+      <c r="BD29" s="11">
         <v>35.17</v>
       </c>
-      <c r="BC29" s="11">
+      <c r="BE29" s="11">
         <v>28.17</v>
       </c>
-      <c r="BD29" s="11">
+      <c r="BF29" s="11">
         <v>20.440000000000001</v>
       </c>
-      <c r="BE29" s="11" t="s">
+      <c r="BG29" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="BF29" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="BG29" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="CX29" s="11">
+      <c r="BH29" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="BI29" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="DC29" s="11">
         <v>4</v>
       </c>
-      <c r="CY29" s="11">
+      <c r="DD29" s="11">
         <v>12</v>
       </c>
-      <c r="CZ29" s="11">
+      <c r="DE29" s="11">
         <v>1</v>
       </c>
-      <c r="DA29" s="11">
+      <c r="DF29" s="11">
         <v>12</v>
       </c>
-      <c r="DD29" s="11">
-        <v>0</v>
-      </c>
-      <c r="DE29" s="11">
+      <c r="DI29" s="11">
+        <v>0</v>
+      </c>
+      <c r="DJ29" s="11">
         <v>12</v>
       </c>
-      <c r="DF29" s="11">
-        <v>0</v>
-      </c>
-      <c r="DG29" s="11">
+      <c r="DK29" s="11">
+        <v>0</v>
+      </c>
+      <c r="DL29" s="11">
         <v>12</v>
       </c>
-      <c r="DH29" s="11">
+      <c r="DM29" s="11">
         <v>2</v>
       </c>
-      <c r="DI29" s="11">
+      <c r="DN29" s="11">
         <v>12</v>
       </c>
-      <c r="DJ29" s="11">
-        <v>0</v>
-      </c>
-      <c r="DK29" s="11">
+      <c r="DO29" s="11">
+        <v>0</v>
+      </c>
+      <c r="DP29" s="11">
         <v>12</v>
       </c>
-      <c r="DT29" s="11">
+      <c r="DY29" s="11">
         <v>2</v>
       </c>
-      <c r="DU29" s="11">
+      <c r="DZ29" s="11">
         <v>12</v>
       </c>
-      <c r="EB29" t="s">
+      <c r="EG29" t="s">
         <v>138</v>
       </c>
-      <c r="EC29" t="s">
+      <c r="EH29" t="s">
         <v>161</v>
       </c>
-      <c r="ED29" t="s">
+      <c r="EI29" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="30" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>251</v>
       </c>
@@ -6310,101 +6406,107 @@
       <c r="AS30" s="11">
         <v>10</v>
       </c>
-      <c r="AT30" s="11">
+      <c r="AT30" s="16">
+        <v>12</v>
+      </c>
+      <c r="AU30" s="11">
         <v>17.93</v>
       </c>
-      <c r="AU30" s="11">
+      <c r="AV30" s="11">
         <v>17.7</v>
       </c>
-      <c r="AV30" s="11">
+      <c r="AW30" s="11">
         <v>5.25</v>
       </c>
-      <c r="AW30" s="11" t="s">
+      <c r="AX30" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="AX30" s="11" t="s">
-        <v>132</v>
-      </c>
       <c r="AY30" s="11" t="s">
         <v>132</v>
       </c>
       <c r="AZ30" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="BA30" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="BA30" s="11">
+      <c r="BB30" s="11">
         <v>10</v>
       </c>
-      <c r="BB30" s="11">
+      <c r="BC30" s="16">
+        <v>12</v>
+      </c>
+      <c r="BD30" s="11">
         <v>34.79</v>
       </c>
-      <c r="BC30" s="11">
+      <c r="BE30" s="11">
         <v>30.4</v>
       </c>
-      <c r="BD30" s="11">
+      <c r="BF30" s="11">
         <v>12.86</v>
       </c>
-      <c r="BE30" s="11" t="s">
+      <c r="BG30" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="BF30" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="BG30" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="CX30" s="11">
+      <c r="BH30" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="BI30" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="DC30" s="11">
         <v>7</v>
       </c>
-      <c r="CY30" s="11">
+      <c r="DD30" s="11">
         <v>15</v>
       </c>
-      <c r="CZ30" s="11">
-        <v>0</v>
-      </c>
-      <c r="DA30" s="11">
+      <c r="DE30" s="11">
+        <v>0</v>
+      </c>
+      <c r="DF30" s="11">
         <v>15</v>
       </c>
-      <c r="DD30" s="11">
-        <v>0</v>
-      </c>
-      <c r="DE30" s="11">
+      <c r="DI30" s="11">
+        <v>0</v>
+      </c>
+      <c r="DJ30" s="11">
         <v>15</v>
       </c>
-      <c r="DF30" s="11">
-        <v>0</v>
-      </c>
-      <c r="DG30" s="11">
+      <c r="DK30" s="11">
+        <v>0</v>
+      </c>
+      <c r="DL30" s="11">
         <v>15</v>
       </c>
-      <c r="DH30" s="11">
-        <v>0</v>
-      </c>
-      <c r="DI30" s="11">
+      <c r="DM30" s="11">
+        <v>0</v>
+      </c>
+      <c r="DN30" s="11">
         <v>15</v>
       </c>
-      <c r="DJ30" s="11">
-        <v>0</v>
-      </c>
-      <c r="DK30" s="11">
+      <c r="DO30" s="11">
+        <v>0</v>
+      </c>
+      <c r="DP30" s="11">
         <v>15</v>
       </c>
-      <c r="DT30" s="11">
+      <c r="DY30" s="11">
         <v>1</v>
       </c>
-      <c r="DU30" s="11">
+      <c r="DZ30" s="11">
         <v>15</v>
       </c>
-      <c r="EB30" t="s">
+      <c r="EG30" t="s">
         <v>162</v>
       </c>
-      <c r="EC30" t="s">
+      <c r="EH30" t="s">
         <v>161</v>
       </c>
-      <c r="ED30" t="s">
+      <c r="EI30" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="31" spans="1:134" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:139" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>255</v>
       </c>
@@ -6537,101 +6639,107 @@
       <c r="AS31" s="11">
         <v>4</v>
       </c>
-      <c r="AT31" s="11">
+      <c r="AT31" s="16">
+        <v>5</v>
+      </c>
+      <c r="AU31" s="11">
         <v>18</v>
       </c>
-      <c r="AU31" s="11">
+      <c r="AV31" s="11">
         <v>21.5</v>
       </c>
-      <c r="AV31" s="11">
+      <c r="AW31" s="11">
         <v>2.6</v>
       </c>
-      <c r="AW31" s="11" t="s">
+      <c r="AX31" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="AX31" s="11" t="s">
-        <v>132</v>
-      </c>
       <c r="AY31" s="11" t="s">
         <v>132</v>
       </c>
       <c r="AZ31" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="BA31" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="BA31" s="11">
+      <c r="BB31" s="11">
         <v>4</v>
       </c>
-      <c r="BB31" s="11">
+      <c r="BC31" s="16">
+        <v>5</v>
+      </c>
+      <c r="BD31" s="11">
         <v>36.4</v>
       </c>
-      <c r="BC31" s="11">
+      <c r="BE31" s="11">
         <v>33.299999999999997</v>
       </c>
-      <c r="BD31" s="11">
+      <c r="BF31" s="11">
         <v>10.6</v>
       </c>
-      <c r="BE31" s="11" t="s">
+      <c r="BG31" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="BF31" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="BG31" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="CX31" s="11">
+      <c r="BH31" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="BI31" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="DC31" s="11">
         <v>2</v>
       </c>
-      <c r="CY31" s="11">
+      <c r="DD31" s="11">
         <v>5</v>
       </c>
-      <c r="CZ31" s="11">
-        <v>0</v>
-      </c>
-      <c r="DA31" s="11">
+      <c r="DE31" s="11">
+        <v>0</v>
+      </c>
+      <c r="DF31" s="11">
         <v>5</v>
       </c>
-      <c r="DD31" s="11">
+      <c r="DI31" s="11">
         <v>1</v>
       </c>
-      <c r="DE31" s="11">
+      <c r="DJ31" s="11">
         <v>5</v>
       </c>
-      <c r="DF31" s="11">
-        <v>0</v>
-      </c>
-      <c r="DG31" s="11">
+      <c r="DK31" s="11">
+        <v>0</v>
+      </c>
+      <c r="DL31" s="11">
         <v>5</v>
       </c>
-      <c r="DH31" s="11">
-        <v>0</v>
-      </c>
-      <c r="DI31" s="11">
+      <c r="DM31" s="11">
+        <v>0</v>
+      </c>
+      <c r="DN31" s="11">
         <v>5</v>
       </c>
-      <c r="DJ31" s="11">
-        <v>0</v>
-      </c>
-      <c r="DK31" s="11">
+      <c r="DO31" s="11">
+        <v>0</v>
+      </c>
+      <c r="DP31" s="11">
         <v>5</v>
       </c>
-      <c r="DT31" s="11">
-        <v>0</v>
-      </c>
-      <c r="DU31" s="11">
+      <c r="DY31" s="11">
+        <v>0</v>
+      </c>
+      <c r="DZ31" s="11">
         <v>5</v>
       </c>
-      <c r="EB31" s="13" t="s">
+      <c r="EG31" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="EC31" t="s">
+      <c r="EH31" t="s">
         <v>161</v>
       </c>
-      <c r="ED31" t="s">
+      <c r="EI31" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="32" spans="1:134" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:139" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>256</v>
       </c>
@@ -6764,101 +6872,107 @@
       <c r="AS32" s="11">
         <v>20</v>
       </c>
-      <c r="AT32" s="11">
+      <c r="AT32" s="16">
+        <v>30</v>
+      </c>
+      <c r="AU32" s="11">
         <v>17.600000000000001</v>
       </c>
-      <c r="AU32" s="11">
+      <c r="AV32" s="11">
         <v>16.5</v>
       </c>
-      <c r="AV32" s="11">
+      <c r="AW32" s="11">
         <v>4.7</v>
       </c>
-      <c r="AW32" s="11" t="s">
+      <c r="AX32" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="AX32" s="11" t="s">
-        <v>132</v>
-      </c>
       <c r="AY32" s="11" t="s">
         <v>132</v>
       </c>
       <c r="AZ32" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="BA32" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="BA32" s="11">
+      <c r="BB32" s="11">
         <v>19</v>
       </c>
-      <c r="BB32" s="11">
+      <c r="BC32" s="16">
+        <v>30</v>
+      </c>
+      <c r="BD32" s="11">
         <v>38.1</v>
       </c>
-      <c r="BC32" s="11">
+      <c r="BE32" s="11">
         <v>29.6</v>
       </c>
-      <c r="BD32" s="11">
+      <c r="BF32" s="11">
         <v>9.1999999999999993</v>
       </c>
-      <c r="BE32" s="11" t="s">
+      <c r="BG32" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="BF32" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="BG32" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="CX32" s="11">
+      <c r="BH32" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="BI32" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="DC32" s="11">
         <v>8</v>
       </c>
-      <c r="CY32" s="11">
+      <c r="DD32" s="11">
         <v>30</v>
       </c>
-      <c r="CZ32" s="11">
+      <c r="DE32" s="11">
         <v>1</v>
       </c>
-      <c r="DA32" s="11">
+      <c r="DF32" s="11">
         <v>30</v>
       </c>
-      <c r="DD32" s="11">
+      <c r="DI32" s="11">
         <v>2</v>
       </c>
-      <c r="DE32" s="11">
+      <c r="DJ32" s="11">
         <v>30</v>
       </c>
-      <c r="DF32" s="11">
+      <c r="DK32" s="11">
         <v>1</v>
       </c>
-      <c r="DG32" s="11">
+      <c r="DL32" s="11">
         <v>30</v>
       </c>
-      <c r="DH32" s="11">
+      <c r="DM32" s="11">
         <v>1</v>
       </c>
-      <c r="DI32" s="11">
+      <c r="DN32" s="11">
         <v>30</v>
       </c>
-      <c r="DJ32" s="11">
+      <c r="DO32" s="11">
         <v>2</v>
       </c>
-      <c r="DK32" s="11">
+      <c r="DP32" s="11">
         <v>30</v>
       </c>
-      <c r="DT32" s="11">
-        <v>0</v>
-      </c>
-      <c r="DU32" s="11">
+      <c r="DY32" s="11">
+        <v>0</v>
+      </c>
+      <c r="DZ32" s="11">
         <v>30</v>
       </c>
-      <c r="EB32" s="13" t="s">
+      <c r="EG32" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="EC32" t="s">
+      <c r="EH32" t="s">
         <v>161</v>
       </c>
-      <c r="ED32" t="s">
+      <c r="EI32" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="33" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>257</v>
       </c>
@@ -6991,101 +7105,107 @@
       <c r="AS33" s="11">
         <v>21</v>
       </c>
-      <c r="AT33" s="11">
+      <c r="AT33" s="16">
+        <v>32</v>
+      </c>
+      <c r="AU33" s="11">
         <v>17.2</v>
       </c>
-      <c r="AU33" s="11">
+      <c r="AV33" s="11">
         <v>15.5</v>
       </c>
-      <c r="AV33" s="11">
+      <c r="AW33" s="11">
         <v>4.3</v>
       </c>
-      <c r="AW33" s="11" t="s">
+      <c r="AX33" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="AX33" s="11" t="s">
-        <v>132</v>
-      </c>
       <c r="AY33" s="11" t="s">
         <v>132</v>
       </c>
       <c r="AZ33" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="BA33" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="BA33" s="11">
+      <c r="BB33" s="11">
         <v>21</v>
       </c>
-      <c r="BB33" s="11">
+      <c r="BC33" s="16">
+        <v>32</v>
+      </c>
+      <c r="BD33" s="11">
         <v>38.4</v>
       </c>
-      <c r="BC33" s="11">
+      <c r="BE33" s="11">
         <v>29.2</v>
       </c>
-      <c r="BD33" s="11">
+      <c r="BF33" s="11">
         <v>12.4</v>
       </c>
-      <c r="BE33" s="11" t="s">
+      <c r="BG33" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="BF33" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="BG33" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="CX33" s="11">
+      <c r="BH33" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="BI33" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="DC33" s="11">
         <v>4</v>
       </c>
-      <c r="CY33" s="11">
+      <c r="DD33" s="11">
         <v>32</v>
       </c>
-      <c r="CZ33" s="11">
-        <v>0</v>
-      </c>
-      <c r="DA33" s="11">
+      <c r="DE33" s="11">
+        <v>0</v>
+      </c>
+      <c r="DF33" s="11">
         <v>32</v>
       </c>
-      <c r="DD33" s="11">
+      <c r="DI33" s="11">
         <v>1</v>
       </c>
-      <c r="DE33" s="11">
+      <c r="DJ33" s="11">
         <v>32</v>
       </c>
-      <c r="DF33" s="11">
-        <v>0</v>
-      </c>
-      <c r="DG33" s="11">
+      <c r="DK33" s="11">
+        <v>0</v>
+      </c>
+      <c r="DL33" s="11">
         <v>32</v>
       </c>
-      <c r="DH33" s="11">
+      <c r="DM33" s="11">
         <v>1</v>
       </c>
-      <c r="DI33" s="11">
+      <c r="DN33" s="11">
         <v>32</v>
       </c>
-      <c r="DJ33" s="11">
-        <v>0</v>
-      </c>
-      <c r="DK33" s="11">
+      <c r="DO33" s="11">
+        <v>0</v>
+      </c>
+      <c r="DP33" s="11">
         <v>32</v>
       </c>
-      <c r="DT33" s="11">
-        <v>0</v>
-      </c>
-      <c r="DU33" s="11">
+      <c r="DY33" s="11">
+        <v>0</v>
+      </c>
+      <c r="DZ33" s="11">
         <v>32</v>
       </c>
-      <c r="EB33" s="13" t="s">
+      <c r="EG33" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="EC33" t="s">
+      <c r="EH33" t="s">
         <v>161</v>
       </c>
-      <c r="ED33" t="s">
+      <c r="EI33" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="34" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>253</v>
       </c>
@@ -7218,101 +7338,107 @@
       <c r="AS34" s="11">
         <v>31</v>
       </c>
-      <c r="AT34" s="11">
+      <c r="AT34" s="16">
+        <v>37</v>
+      </c>
+      <c r="AU34" s="11">
         <v>18.899999999999999</v>
       </c>
-      <c r="AU34" s="11">
+      <c r="AV34" s="11">
         <v>17.3</v>
       </c>
-      <c r="AV34" s="11">
+      <c r="AW34" s="11">
         <v>4.5</v>
       </c>
-      <c r="AW34" s="11" t="s">
+      <c r="AX34" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="AX34" s="11" t="s">
-        <v>132</v>
-      </c>
       <c r="AY34" s="11" t="s">
         <v>132</v>
       </c>
       <c r="AZ34" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="BA34" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="BA34" s="11">
+      <c r="BB34" s="11">
         <v>31</v>
       </c>
-      <c r="BB34" s="11">
+      <c r="BC34" s="16">
+        <v>37</v>
+      </c>
+      <c r="BD34" s="11">
         <v>36.6</v>
       </c>
-      <c r="BC34" s="11">
+      <c r="BE34" s="11">
         <v>32.700000000000003</v>
       </c>
-      <c r="BD34" s="11">
+      <c r="BF34" s="11">
         <v>13.4</v>
       </c>
-      <c r="BE34" s="11" t="s">
+      <c r="BG34" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="BF34" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="BG34" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="CX34" s="11">
+      <c r="BH34" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="BI34" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="DC34" s="11">
         <v>9</v>
       </c>
-      <c r="CY34" s="11">
+      <c r="DD34" s="11">
         <v>37</v>
       </c>
-      <c r="CZ34" s="11">
-        <v>0</v>
-      </c>
-      <c r="DA34" s="11">
+      <c r="DE34" s="11">
+        <v>0</v>
+      </c>
+      <c r="DF34" s="11">
         <v>37</v>
       </c>
-      <c r="DD34" s="11">
+      <c r="DI34" s="11">
         <v>1</v>
       </c>
-      <c r="DE34" s="11">
+      <c r="DJ34" s="11">
         <v>37</v>
       </c>
-      <c r="DF34" s="11">
+      <c r="DK34" s="11">
         <v>3</v>
       </c>
-      <c r="DG34" s="11">
+      <c r="DL34" s="11">
         <v>37</v>
       </c>
-      <c r="DH34" s="11">
+      <c r="DM34" s="11">
         <v>2</v>
       </c>
-      <c r="DI34" s="11">
+      <c r="DN34" s="11">
         <v>37</v>
       </c>
-      <c r="DJ34" s="11">
+      <c r="DO34" s="11">
         <v>2</v>
       </c>
-      <c r="DK34" s="11">
+      <c r="DP34" s="11">
         <v>37</v>
       </c>
-      <c r="DT34" s="11">
-        <v>0</v>
-      </c>
-      <c r="DU34" s="11">
+      <c r="DY34" s="11">
+        <v>0</v>
+      </c>
+      <c r="DZ34" s="11">
         <v>37</v>
       </c>
-      <c r="EB34" s="13" t="s">
+      <c r="EG34" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="EC34" t="s">
+      <c r="EH34" t="s">
         <v>161</v>
       </c>
-      <c r="ED34" t="s">
+      <c r="EI34" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="35" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A35" s="11" t="s">
         <v>127</v>
       </c>
@@ -7373,47 +7499,47 @@
       <c r="AB35" s="11">
         <v>29</v>
       </c>
-      <c r="CX35" s="10">
+      <c r="DC35" s="10">
         <v>20</v>
       </c>
-      <c r="CY35" s="10">
+      <c r="DD35" s="10">
         <v>29</v>
       </c>
-      <c r="DD35" s="10">
+      <c r="DI35" s="10">
         <v>4</v>
       </c>
-      <c r="DE35" s="10">
+      <c r="DJ35" s="10">
         <v>29</v>
       </c>
-      <c r="DH35" s="10">
+      <c r="DM35" s="10">
         <v>8</v>
       </c>
-      <c r="DI35" s="10">
+      <c r="DN35" s="10">
         <v>29</v>
       </c>
-      <c r="DJ35" s="10">
+      <c r="DO35" s="10">
         <v>4</v>
       </c>
-      <c r="DK35" s="10">
+      <c r="DP35" s="10">
         <v>29</v>
       </c>
-      <c r="DN35" s="11">
-        <v>0</v>
-      </c>
-      <c r="DO35" s="11">
+      <c r="DS35" s="11">
+        <v>0</v>
+      </c>
+      <c r="DT35" s="11">
         <v>29</v>
       </c>
-      <c r="EB35" s="14" t="s">
+      <c r="EG35" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="EC35" s="11" t="s">
+      <c r="EH35" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="ED35" s="11" t="s">
+      <c r="EI35" s="11" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="36" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
         <v>261</v>
       </c>
@@ -7471,43 +7597,43 @@
       <c r="AB36" s="11">
         <v>26</v>
       </c>
-      <c r="CX36" s="10">
+      <c r="DC36" s="10">
         <v>9</v>
       </c>
-      <c r="CY36" s="10">
+      <c r="DD36" s="10">
         <v>26</v>
       </c>
-      <c r="DD36" s="10">
-        <v>0</v>
-      </c>
-      <c r="DE36" s="10">
+      <c r="DI36" s="10">
+        <v>0</v>
+      </c>
+      <c r="DJ36" s="10">
         <v>26</v>
       </c>
-      <c r="DH36" s="10">
-        <v>0</v>
-      </c>
-      <c r="DI36" s="10">
+      <c r="DM36" s="10">
+        <v>0</v>
+      </c>
+      <c r="DN36" s="10">
         <v>26</v>
       </c>
-      <c r="DJ36" s="10">
+      <c r="DO36" s="10">
         <v>1</v>
       </c>
-      <c r="DK36" s="10">
+      <c r="DP36" s="10">
         <v>26</v>
       </c>
-      <c r="DN36" s="11">
-        <v>0</v>
-      </c>
-      <c r="DO36" s="11">
+      <c r="DS36" s="11">
+        <v>0</v>
+      </c>
+      <c r="DT36" s="11">
         <v>26</v>
       </c>
-      <c r="EB36" s="14" t="s">
+      <c r="EG36" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="EC36" s="11" t="s">
+      <c r="EH36" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="ED36" s="11" t="s">
+      <c r="EI36" s="11" t="s">
         <v>132</v>
       </c>
     </row>

--- a/data_u1/LSR3_H_2025-01-16.xlsx
+++ b/data_u1/LSR3_H_2025-01-16.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sksiafis/Documents/GitHub/LSR3_taar1_H/data_u1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A73D962C-1E82-0D43-A93D-8DC17D78DB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F84E762-47FF-8845-95C2-90AFED838E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23500" yWindow="-18540" windowWidth="30180" windowHeight="17720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-21600" windowWidth="38400" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1102" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1097" uniqueCount="285">
   <si>
     <t>arm_name</t>
   </si>
@@ -322,9 +322,6 @@
     <t>weight_sd_origin</t>
   </si>
   <si>
-    <t>Timepoint</t>
-  </si>
-  <si>
     <t>prolactin_scale_name</t>
   </si>
   <si>
@@ -577,9 +574,6 @@
     <t>26</t>
   </si>
   <si>
-    <t>4 weeks</t>
-  </si>
-  <si>
     <t>55</t>
   </si>
   <si>
@@ -809,9 +803,6 @@
   </si>
   <si>
     <t>18-65</t>
-  </si>
-  <si>
-    <t>52 weeks</t>
   </si>
   <si>
     <t>placebo (monotherapy)</t>
@@ -1389,7 +1380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:EI36"/>
+  <dimension ref="A1:EH36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.6640625" customWidth="1"/>
@@ -1405,10 +1396,10 @@
     <col min="72" max="72" width="9" style="16" customWidth="1"/>
     <col min="81" max="81" width="8.83203125" style="16"/>
     <col min="90" max="90" width="8.83203125" style="16"/>
-    <col min="100" max="100" width="8.83203125" style="16"/>
+    <col min="99" max="99" width="8.83203125" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:139" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:138" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1416,10 +1407,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -1455,7 +1446,7 @@
         <v>12</v>
       </c>
       <c r="P1" s="15" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>13</v>
@@ -1518,7 +1509,7 @@
         <v>32</v>
       </c>
       <c r="AK1" s="15" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="AL1" s="1" t="s">
         <v>33</v>
@@ -1545,7 +1536,7 @@
         <v>40</v>
       </c>
       <c r="AT1" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="AU1" s="1" t="s">
         <v>41</v>
@@ -1572,7 +1563,7 @@
         <v>48</v>
       </c>
       <c r="BC1" s="15" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="BD1" s="1" t="s">
         <v>49</v>
@@ -1623,7 +1614,7 @@
         <v>64</v>
       </c>
       <c r="BT1" s="15" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="BU1" s="1" t="s">
         <v>65</v>
@@ -1650,7 +1641,7 @@
         <v>72</v>
       </c>
       <c r="CC1" s="15" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="CD1" s="1" t="s">
         <v>73</v>
@@ -1677,7 +1668,7 @@
         <v>80</v>
       </c>
       <c r="CL1" s="15" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="CM1" s="1" t="s">
         <v>81</v>
@@ -1703,11 +1694,11 @@
       <c r="CT1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="CU1" s="1" t="s">
+      <c r="CU1" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="CV1" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="CV1" s="15" t="s">
-        <v>287</v>
       </c>
       <c r="CW1" s="1" t="s">
         <v>90</v>
@@ -1730,14 +1721,14 @@
       <c r="DC1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="DD1" s="1" t="s">
+      <c r="DD1" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="DE1" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="DF1" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="DE1" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="DF1" s="7" t="s">
-        <v>243</v>
       </c>
       <c r="DG1" s="1" t="s">
         <v>98</v>
@@ -1823,49 +1814,46 @@
       <c r="EH1" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="EI1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:138" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="2" spans="1:139" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>127</v>
-      </c>
       <c r="B2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C2" s="16">
         <v>2023</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H2" t="s">
         <v>144</v>
       </c>
-      <c r="G2" t="s">
-        <v>127</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>145</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>146</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>147</v>
-      </c>
-      <c r="K2" t="s">
-        <v>148</v>
       </c>
       <c r="L2">
         <v>25</v>
       </c>
       <c r="M2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="N2">
         <v>4</v>
@@ -1874,58 +1862,58 @@
         <v>6</v>
       </c>
       <c r="P2" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Q2" t="s">
+        <v>149</v>
+      </c>
+      <c r="R2" t="s">
         <v>150</v>
       </c>
-      <c r="R2" t="s">
+      <c r="U2" t="s">
         <v>151</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
+        <v>140</v>
+      </c>
+      <c r="W2" t="s">
         <v>152</v>
       </c>
-      <c r="V2" t="s">
-        <v>141</v>
-      </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
+        <v>140</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>140</v>
+      </c>
+      <c r="AA2" t="s">
         <v>153</v>
       </c>
-      <c r="X2" t="s">
-        <v>141</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>128</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>141</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>154</v>
-      </c>
       <c r="AB2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AC2" t="s">
+        <v>154</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>154</v>
+      </c>
+      <c r="AE2" t="s">
         <v>155</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AF2" t="s">
+        <v>154</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>154</v>
+      </c>
+      <c r="AH2" t="s">
         <v>155</v>
       </c>
-      <c r="AE2" t="s">
-        <v>156</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>155</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>155</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>156</v>
-      </c>
       <c r="AI2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AJ2">
         <v>23</v>
@@ -1937,16 +1925,16 @@
         <v>20.12</v>
       </c>
       <c r="AO2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AP2" t="s">
         <v>130</v>
       </c>
-      <c r="AP2" t="s">
-        <v>131</v>
-      </c>
       <c r="AQ2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AR2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AS2">
         <v>24</v>
@@ -1964,16 +1952,16 @@
         <v>7.94</v>
       </c>
       <c r="AX2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AY2" t="s">
         <v>130</v>
       </c>
-      <c r="AY2" t="s">
-        <v>131</v>
-      </c>
       <c r="AZ2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BR2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="BS2">
         <v>23</v>
@@ -1991,100 +1979,100 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="BX2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BY2" t="s">
         <v>130</v>
       </c>
-      <c r="BY2" t="s">
-        <v>131</v>
-      </c>
       <c r="BZ2" t="s">
-        <v>132</v>
+        <v>131</v>
+      </c>
+      <c r="DB2">
+        <v>18</v>
       </c>
       <c r="DC2">
-        <v>18</v>
-      </c>
-      <c r="DD2">
         <v>25</v>
       </c>
+      <c r="DF2" s="9"/>
       <c r="DG2" s="9"/>
-      <c r="DH2" s="9"/>
+      <c r="DH2">
+        <v>4</v>
+      </c>
       <c r="DI2">
-        <v>4</v>
-      </c>
-      <c r="DJ2">
         <v>25</v>
       </c>
+      <c r="DL2">
+        <v>3</v>
+      </c>
       <c r="DM2">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="DN2">
+        <v>2</v>
+      </c>
+      <c r="DO2">
         <v>25</v>
       </c>
-      <c r="DO2">
+      <c r="DT2" s="9"/>
+      <c r="DU2" s="9"/>
+      <c r="DV2">
+        <v>13</v>
+      </c>
+      <c r="DW2">
+        <v>25</v>
+      </c>
+      <c r="DX2" s="8">
         <v>2</v>
       </c>
-      <c r="DP2">
-        <v>25</v>
-      </c>
-      <c r="DU2" s="9"/>
-      <c r="DV2" s="9"/>
-      <c r="DW2">
-        <v>13</v>
-      </c>
-      <c r="DX2">
-        <v>25</v>
-      </c>
-      <c r="DY2" s="8">
-        <v>2</v>
+      <c r="EF2" t="s">
+        <v>137</v>
       </c>
       <c r="EG2" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="EH2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:138" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>161</v>
       </c>
-      <c r="EI2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="3" spans="1:139" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>162</v>
-      </c>
       <c r="B3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C3" s="16">
         <v>2023</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I3" t="s">
+        <v>145</v>
+      </c>
+      <c r="J3" t="s">
         <v>146</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>147</v>
-      </c>
-      <c r="K3" t="s">
-        <v>148</v>
       </c>
       <c r="L3">
         <v>14</v>
       </c>
       <c r="M3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="N3">
         <v>1</v>
@@ -2093,58 +2081,58 @@
         <v>6</v>
       </c>
       <c r="P3" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Q3" t="s">
+        <v>162</v>
+      </c>
+      <c r="R3" t="s">
+        <v>141</v>
+      </c>
+      <c r="U3" t="s">
+        <v>162</v>
+      </c>
+      <c r="V3" t="s">
         <v>163</v>
       </c>
-      <c r="R3" t="s">
-        <v>142</v>
-      </c>
-      <c r="U3" t="s">
+      <c r="W3" t="s">
+        <v>164</v>
+      </c>
+      <c r="X3" t="s">
         <v>163</v>
       </c>
-      <c r="V3" t="s">
-        <v>164</v>
-      </c>
-      <c r="W3" t="s">
-        <v>165</v>
-      </c>
-      <c r="X3" t="s">
-        <v>164</v>
-      </c>
       <c r="Y3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Z3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AA3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AB3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AC3" t="s">
+        <v>154</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>154</v>
+      </c>
+      <c r="AE3" t="s">
         <v>155</v>
       </c>
-      <c r="AD3" t="s">
+      <c r="AF3" t="s">
+        <v>154</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>154</v>
+      </c>
+      <c r="AH3" t="s">
         <v>155</v>
       </c>
-      <c r="AE3" t="s">
-        <v>156</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>155</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>155</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>156</v>
-      </c>
       <c r="AI3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AJ3">
         <v>14</v>
@@ -2156,16 +2144,16 @@
         <v>19.57</v>
       </c>
       <c r="AO3" t="s">
+        <v>129</v>
+      </c>
+      <c r="AP3" t="s">
         <v>130</v>
       </c>
-      <c r="AP3" t="s">
-        <v>131</v>
-      </c>
       <c r="AQ3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AR3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AS3">
         <v>14</v>
@@ -2183,16 +2171,16 @@
         <v>7.71</v>
       </c>
       <c r="AX3" t="s">
+        <v>129</v>
+      </c>
+      <c r="AY3" t="s">
         <v>130</v>
       </c>
-      <c r="AY3" t="s">
-        <v>131</v>
-      </c>
       <c r="AZ3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BR3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="BS3">
         <v>14</v>
@@ -2210,111 +2198,111 @@
         <v>1.99</v>
       </c>
       <c r="BX3" t="s">
+        <v>129</v>
+      </c>
+      <c r="BY3" t="s">
         <v>130</v>
       </c>
-      <c r="BY3" t="s">
-        <v>131</v>
-      </c>
       <c r="BZ3" t="s">
-        <v>132</v>
+        <v>131</v>
+      </c>
+      <c r="DB3">
+        <v>12</v>
       </c>
       <c r="DC3">
-        <v>12</v>
-      </c>
-      <c r="DD3">
         <v>14</v>
       </c>
+      <c r="DF3">
+        <v>0</v>
+      </c>
       <c r="DG3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="DH3">
+        <v>1</v>
+      </c>
+      <c r="DI3">
         <v>14</v>
       </c>
-      <c r="DI3">
+      <c r="DL3">
         <v>1</v>
       </c>
-      <c r="DJ3">
+      <c r="DM3">
         <v>14</v>
       </c>
-      <c r="DM3">
+      <c r="DN3">
+        <v>2</v>
+      </c>
+      <c r="DO3">
+        <v>14</v>
+      </c>
+      <c r="DT3">
         <v>1</v>
       </c>
-      <c r="DN3">
+      <c r="DU3">
         <v>14</v>
       </c>
-      <c r="DO3">
-        <v>2</v>
-      </c>
-      <c r="DP3">
+      <c r="DV3">
+        <v>11</v>
+      </c>
+      <c r="DW3">
         <v>14</v>
       </c>
-      <c r="DU3">
+      <c r="DX3">
         <v>1</v>
       </c>
-      <c r="DV3">
+      <c r="DY3">
         <v>14</v>
       </c>
-      <c r="DW3">
-        <v>11</v>
-      </c>
-      <c r="DX3">
-        <v>14</v>
-      </c>
-      <c r="DY3">
-        <v>1</v>
-      </c>
-      <c r="DZ3">
-        <v>14</v>
+      <c r="EF3" t="s">
+        <v>161</v>
       </c>
       <c r="EG3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="EH3" t="s">
-        <v>161</v>
-      </c>
-      <c r="EI3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="4" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C4" s="16">
         <v>2020</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H4" t="s">
+        <v>166</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="J4" t="s">
+        <v>146</v>
+      </c>
+      <c r="K4" t="s">
         <v>167</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="J4" t="s">
-        <v>147</v>
-      </c>
-      <c r="K4" t="s">
-        <v>168</v>
       </c>
       <c r="L4">
         <v>120</v>
       </c>
       <c r="M4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="N4">
         <v>43</v>
@@ -2323,58 +2311,58 @@
         <v>4</v>
       </c>
       <c r="P4" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Q4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="R4" t="s">
+        <v>169</v>
+      </c>
+      <c r="U4" t="s">
         <v>170</v>
       </c>
-      <c r="U4" t="s">
-        <v>171</v>
-      </c>
       <c r="V4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="W4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="X4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Y4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Z4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AA4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AB4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AC4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AD4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AE4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AF4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AG4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AH4" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AI4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AJ4">
         <v>120</v>
@@ -2392,16 +2380,16 @@
         <v>18.63</v>
       </c>
       <c r="AO4" t="s">
+        <v>129</v>
+      </c>
+      <c r="AP4" t="s">
         <v>130</v>
       </c>
-      <c r="AP4" t="s">
-        <v>131</v>
-      </c>
       <c r="AQ4" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR4" t="s">
         <v>132</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>133</v>
       </c>
       <c r="AS4">
         <v>120</v>
@@ -2419,16 +2407,16 @@
         <v>5.48</v>
       </c>
       <c r="AX4" t="s">
+        <v>129</v>
+      </c>
+      <c r="AY4" t="s">
         <v>130</v>
       </c>
-      <c r="AY4" t="s">
-        <v>131</v>
-      </c>
       <c r="AZ4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BA4" s="9" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="BB4">
         <v>120</v>
@@ -2446,16 +2434,16 @@
         <v>10.95</v>
       </c>
       <c r="BG4" t="s">
+        <v>129</v>
+      </c>
+      <c r="BH4" t="s">
         <v>130</v>
       </c>
-      <c r="BH4" t="s">
-        <v>131</v>
-      </c>
       <c r="BI4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="CA4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="CB4">
         <v>120</v>
@@ -2473,16 +2461,16 @@
         <v>6.57</v>
       </c>
       <c r="CG4" t="s">
+        <v>129</v>
+      </c>
+      <c r="CH4" t="s">
         <v>130</v>
       </c>
-      <c r="CH4" t="s">
-        <v>131</v>
-      </c>
       <c r="CI4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="CJ4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="CK4">
         <v>120</v>
@@ -2500,153 +2488,150 @@
         <v>1.9</v>
       </c>
       <c r="CP4" t="s">
+        <v>129</v>
+      </c>
+      <c r="CQ4" t="s">
         <v>130</v>
       </c>
-      <c r="CQ4" t="s">
-        <v>131</v>
-      </c>
       <c r="CR4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="CS4" t="s">
-        <v>172</v>
-      </c>
-      <c r="CT4" t="s">
+        <v>136</v>
+      </c>
+      <c r="CT4">
+        <v>114</v>
+      </c>
+      <c r="CW4">
+        <v>-1.965789473684211</v>
+      </c>
+      <c r="CX4">
+        <v>28</v>
+      </c>
+      <c r="CY4" t="s">
+        <v>129</v>
+      </c>
+      <c r="CZ4" t="s">
+        <v>131</v>
+      </c>
+      <c r="DA4" t="s">
+        <v>130</v>
+      </c>
+      <c r="DB4">
+        <v>55</v>
+      </c>
+      <c r="DC4">
+        <v>120</v>
+      </c>
+      <c r="DF4">
+        <v>2</v>
+      </c>
+      <c r="DG4">
+        <v>120</v>
+      </c>
+      <c r="DJ4">
+        <v>11</v>
+      </c>
+      <c r="DK4">
+        <v>120</v>
+      </c>
+      <c r="DL4">
+        <v>6</v>
+      </c>
+      <c r="DM4">
+        <v>120</v>
+      </c>
+      <c r="DN4">
+        <v>8</v>
+      </c>
+      <c r="DO4">
+        <v>120</v>
+      </c>
+      <c r="DR4">
+        <v>0</v>
+      </c>
+      <c r="DS4">
+        <v>120</v>
+      </c>
+      <c r="DT4">
+        <v>6</v>
+      </c>
+      <c r="DU4">
+        <v>120</v>
+      </c>
+      <c r="DX4">
+        <v>4</v>
+      </c>
+      <c r="DY4">
+        <v>120</v>
+      </c>
+      <c r="DZ4">
+        <v>1</v>
+      </c>
+      <c r="EA4">
+        <v>120</v>
+      </c>
+      <c r="EB4">
+        <v>4</v>
+      </c>
+      <c r="EC4">
+        <v>120</v>
+      </c>
+      <c r="ED4">
+        <v>1</v>
+      </c>
+      <c r="EE4">
+        <v>120</v>
+      </c>
+      <c r="EF4" t="s">
         <v>137</v>
       </c>
-      <c r="CU4">
-        <v>114</v>
-      </c>
-      <c r="CX4">
-        <v>-1.965789473684211</v>
-      </c>
-      <c r="CY4">
-        <v>28</v>
-      </c>
-      <c r="CZ4" t="s">
-        <v>130</v>
-      </c>
-      <c r="DA4" t="s">
-        <v>132</v>
-      </c>
-      <c r="DB4" t="s">
-        <v>131</v>
-      </c>
-      <c r="DC4">
-        <v>55</v>
-      </c>
-      <c r="DD4">
-        <v>120</v>
-      </c>
-      <c r="DG4">
-        <v>2</v>
-      </c>
-      <c r="DH4">
-        <v>120</v>
-      </c>
-      <c r="DK4">
-        <v>11</v>
-      </c>
-      <c r="DL4">
-        <v>120</v>
-      </c>
-      <c r="DM4">
-        <v>6</v>
-      </c>
-      <c r="DN4">
-        <v>120</v>
-      </c>
-      <c r="DO4">
-        <v>8</v>
-      </c>
-      <c r="DP4">
-        <v>120</v>
-      </c>
-      <c r="DS4">
-        <v>0</v>
-      </c>
-      <c r="DT4">
-        <v>120</v>
-      </c>
-      <c r="DU4">
-        <v>6</v>
-      </c>
-      <c r="DV4">
-        <v>120</v>
-      </c>
-      <c r="DY4">
-        <v>4</v>
-      </c>
-      <c r="DZ4">
-        <v>120</v>
-      </c>
-      <c r="EA4">
-        <v>1</v>
-      </c>
-      <c r="EB4">
-        <v>120</v>
-      </c>
-      <c r="EC4">
-        <v>4</v>
-      </c>
-      <c r="ED4">
-        <v>120</v>
-      </c>
-      <c r="EE4">
-        <v>1</v>
-      </c>
-      <c r="EF4">
-        <v>120</v>
-      </c>
       <c r="EG4" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="EH4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="5" spans="1:138" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>161</v>
       </c>
-      <c r="EI4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="5" spans="1:139" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>162</v>
-      </c>
       <c r="B5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C5" s="16">
         <v>2020</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="J5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L5">
         <v>125</v>
       </c>
       <c r="M5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="N5">
         <v>46</v>
@@ -2655,58 +2640,58 @@
         <v>4</v>
       </c>
       <c r="P5" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Q5" t="s">
+        <v>171</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="U5" t="s">
+        <v>170</v>
+      </c>
+      <c r="V5" t="s">
+        <v>172</v>
+      </c>
+      <c r="W5" t="s">
         <v>173</v>
       </c>
-      <c r="R5" s="4" t="s">
+      <c r="X5" t="s">
+        <v>172</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>172</v>
+      </c>
+      <c r="AA5" t="s">
         <v>174</v>
       </c>
-      <c r="U5" t="s">
-        <v>171</v>
-      </c>
-      <c r="V5" t="s">
-        <v>174</v>
-      </c>
-      <c r="W5" t="s">
-        <v>175</v>
-      </c>
-      <c r="X5" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y5" t="s">
+      <c r="AB5" t="s">
+        <v>172</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>154</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>154</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>156</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>154</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>154</v>
+      </c>
+      <c r="AH5" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="AI5" t="s">
         <v>128</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>174</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>176</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>174</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>155</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>155</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>157</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>155</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>155</v>
-      </c>
-      <c r="AH5" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>129</v>
       </c>
       <c r="AJ5">
         <v>125</v>
@@ -2724,16 +2709,16 @@
         <v>17.89</v>
       </c>
       <c r="AO5" t="s">
+        <v>129</v>
+      </c>
+      <c r="AP5" t="s">
         <v>130</v>
       </c>
-      <c r="AP5" t="s">
-        <v>131</v>
-      </c>
       <c r="AQ5" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR5" t="s">
         <v>132</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>133</v>
       </c>
       <c r="AS5">
         <v>125</v>
@@ -2751,16 +2736,16 @@
         <v>5.59</v>
       </c>
       <c r="AX5" t="s">
+        <v>129</v>
+      </c>
+      <c r="AY5" t="s">
         <v>130</v>
       </c>
-      <c r="AY5" t="s">
-        <v>131</v>
-      </c>
       <c r="AZ5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BA5" s="9" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="BB5">
         <v>125</v>
@@ -2778,16 +2763,16 @@
         <v>10.06</v>
       </c>
       <c r="BG5" t="s">
+        <v>129</v>
+      </c>
+      <c r="BH5" t="s">
         <v>130</v>
       </c>
-      <c r="BH5" t="s">
-        <v>131</v>
-      </c>
       <c r="BI5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="CA5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="CB5">
         <v>125</v>
@@ -2805,16 +2790,16 @@
         <v>6.71</v>
       </c>
       <c r="CG5" t="s">
+        <v>129</v>
+      </c>
+      <c r="CH5" t="s">
         <v>130</v>
       </c>
-      <c r="CH5" t="s">
-        <v>131</v>
-      </c>
       <c r="CI5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="CJ5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="CK5">
         <v>125</v>
@@ -2832,120 +2817,117 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="CP5" t="s">
+        <v>129</v>
+      </c>
+      <c r="CQ5" t="s">
         <v>130</v>
       </c>
-      <c r="CQ5" t="s">
-        <v>131</v>
-      </c>
       <c r="CR5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="CS5" t="s">
-        <v>172</v>
-      </c>
-      <c r="CT5" t="s">
-        <v>137</v>
-      </c>
-      <c r="CU5">
+        <v>136</v>
+      </c>
+      <c r="CT5">
         <v>113</v>
       </c>
+      <c r="CW5">
+        <v>-1.3838053097345131</v>
+      </c>
       <c r="CX5">
-        <v>-1.3838053097345131</v>
-      </c>
-      <c r="CY5">
         <v>28</v>
       </c>
+      <c r="CY5" t="s">
+        <v>129</v>
+      </c>
       <c r="CZ5" t="s">
+        <v>131</v>
+      </c>
+      <c r="DA5" t="s">
         <v>130</v>
       </c>
-      <c r="DA5" t="s">
-        <v>132</v>
-      </c>
-      <c r="DB5" t="s">
-        <v>131</v>
+      <c r="DB5">
+        <v>63</v>
       </c>
       <c r="DC5">
-        <v>63</v>
-      </c>
-      <c r="DD5">
         <v>125</v>
       </c>
+      <c r="DF5">
+        <v>9</v>
+      </c>
       <c r="DG5">
-        <v>9</v>
-      </c>
-      <c r="DH5">
         <v>125</v>
       </c>
+      <c r="DJ5">
+        <v>15</v>
+      </c>
       <c r="DK5">
-        <v>15</v>
+        <v>125</v>
       </c>
       <c r="DL5">
+        <v>4</v>
+      </c>
+      <c r="DM5">
         <v>125</v>
       </c>
-      <c r="DM5">
+      <c r="DN5">
+        <v>6</v>
+      </c>
+      <c r="DO5">
+        <v>125</v>
+      </c>
+      <c r="DR5">
+        <v>0</v>
+      </c>
+      <c r="DS5">
+        <v>125</v>
+      </c>
+      <c r="DT5">
+        <v>6</v>
+      </c>
+      <c r="DU5">
+        <v>125</v>
+      </c>
+      <c r="DX5">
+        <v>13</v>
+      </c>
+      <c r="DY5">
+        <v>125</v>
+      </c>
+      <c r="DZ5">
+        <v>0</v>
+      </c>
+      <c r="EA5">
+        <v>125</v>
+      </c>
+      <c r="EB5">
         <v>4</v>
       </c>
-      <c r="DN5">
+      <c r="EC5">
         <v>125</v>
       </c>
-      <c r="DO5">
-        <v>6</v>
-      </c>
-      <c r="DP5">
+      <c r="ED5">
+        <v>1</v>
+      </c>
+      <c r="EE5">
         <v>125</v>
       </c>
-      <c r="DS5">
-        <v>0</v>
-      </c>
-      <c r="DT5">
-        <v>125</v>
-      </c>
-      <c r="DU5">
-        <v>6</v>
-      </c>
-      <c r="DV5">
-        <v>125</v>
-      </c>
-      <c r="DY5">
-        <v>13</v>
-      </c>
-      <c r="DZ5">
-        <v>125</v>
-      </c>
-      <c r="EA5">
-        <v>0</v>
-      </c>
-      <c r="EB5">
-        <v>125</v>
-      </c>
-      <c r="EC5">
-        <v>4</v>
-      </c>
-      <c r="ED5">
-        <v>125</v>
-      </c>
-      <c r="EE5">
-        <v>1</v>
-      </c>
-      <c r="EF5">
-        <v>125</v>
+      <c r="EF5" t="s">
+        <v>161</v>
       </c>
       <c r="EG5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="EH5" t="s">
-        <v>161</v>
-      </c>
-      <c r="EI5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="6" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C6" s="16">
         <v>2023</v>
@@ -2954,19 +2936,19 @@
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="J6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K6" s="2">
         <v>435</v>
@@ -2975,13 +2957,13 @@
         <v>144</v>
       </c>
       <c r="M6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="O6">
         <v>6</v>
       </c>
       <c r="P6" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Q6" s="2">
         <v>22</v>
@@ -2996,25 +2978,25 @@
         <v>144</v>
       </c>
       <c r="AC6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AD6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AE6" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AF6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AG6" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AH6" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AI6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AJ6" s="2">
         <v>142</v>
@@ -3032,30 +3014,30 @@
         <v>19.07</v>
       </c>
       <c r="AO6" t="s">
+        <v>129</v>
+      </c>
+      <c r="AP6" t="s">
         <v>130</v>
       </c>
-      <c r="AP6" t="s">
-        <v>131</v>
-      </c>
       <c r="AQ6" t="s">
-        <v>132</v>
+        <v>131</v>
+      </c>
+      <c r="EF6" t="s">
+        <v>137</v>
       </c>
       <c r="EG6" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="EH6" t="s">
-        <v>161</v>
-      </c>
-      <c r="EI6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="7" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C7" s="16">
         <v>2023</v>
@@ -3064,19 +3046,19 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="J7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K7" s="2">
         <v>435</v>
@@ -3085,13 +3067,13 @@
         <v>145</v>
       </c>
       <c r="M7" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="O7">
         <v>6</v>
       </c>
       <c r="P7" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Q7" s="2">
         <v>29</v>
@@ -3106,25 +3088,25 @@
         <v>145</v>
       </c>
       <c r="AC7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AD7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AE7" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AF7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AG7" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AH7" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AI7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AJ7" s="2">
         <v>145</v>
@@ -3142,30 +3124,30 @@
         <v>19.27</v>
       </c>
       <c r="AO7" t="s">
+        <v>129</v>
+      </c>
+      <c r="AP7" t="s">
         <v>130</v>
       </c>
-      <c r="AP7" t="s">
-        <v>131</v>
-      </c>
       <c r="AQ7" t="s">
-        <v>132</v>
+        <v>131</v>
+      </c>
+      <c r="EF7" t="s">
+        <v>137</v>
       </c>
       <c r="EG7" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="EH7" t="s">
-        <v>161</v>
-      </c>
-      <c r="EI7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="8" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C8" s="16">
         <v>2023</v>
@@ -3174,34 +3156,34 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="J8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="L8" s="3">
         <v>146</v>
       </c>
       <c r="M8" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="O8">
         <v>6</v>
       </c>
       <c r="P8" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Q8" s="2">
         <v>26</v>
@@ -3216,25 +3198,25 @@
         <v>146</v>
       </c>
       <c r="AC8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AD8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AF8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AG8" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AH8" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AI8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AJ8">
         <v>145</v>
@@ -3252,30 +3234,30 @@
         <v>18.059999999999999</v>
       </c>
       <c r="AO8" t="s">
+        <v>129</v>
+      </c>
+      <c r="AP8" t="s">
         <v>130</v>
       </c>
-      <c r="AP8" t="s">
-        <v>131</v>
-      </c>
       <c r="AQ8" t="s">
-        <v>132</v>
+        <v>131</v>
+      </c>
+      <c r="EF8" t="s">
+        <v>161</v>
       </c>
       <c r="EG8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="EH8" t="s">
-        <v>161</v>
-      </c>
-      <c r="EI8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="9" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C9" s="16">
         <v>2023</v>
@@ -3284,34 +3266,34 @@
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="J9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="L9" s="2">
         <v>155</v>
       </c>
       <c r="M9" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="O9">
         <v>6</v>
       </c>
       <c r="P9" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Q9" s="2">
         <v>23</v>
@@ -3326,25 +3308,25 @@
         <v>155</v>
       </c>
       <c r="AC9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AD9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AE9" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AF9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AG9" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AH9" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AI9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AJ9" s="2">
         <v>153</v>
@@ -3362,30 +3344,30 @@
         <v>18.55</v>
       </c>
       <c r="AO9" t="s">
+        <v>129</v>
+      </c>
+      <c r="AP9" t="s">
         <v>130</v>
       </c>
-      <c r="AP9" t="s">
-        <v>131</v>
-      </c>
       <c r="AQ9" t="s">
-        <v>132</v>
+        <v>131</v>
+      </c>
+      <c r="EF9" t="s">
+        <v>137</v>
       </c>
       <c r="EG9" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="EH9" t="s">
-        <v>161</v>
-      </c>
-      <c r="EI9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="10" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B10" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C10" s="16">
         <v>2023</v>
@@ -3394,34 +3376,34 @@
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H10" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="J10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K10" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="L10" s="2">
         <v>154</v>
       </c>
       <c r="M10" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="O10">
         <v>6</v>
       </c>
       <c r="P10" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Q10" s="2">
         <v>27</v>
@@ -3436,25 +3418,25 @@
         <v>154</v>
       </c>
       <c r="AC10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AD10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AE10" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AF10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AG10" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AH10" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AI10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AJ10" s="2">
         <v>152</v>
@@ -3472,30 +3454,30 @@
         <v>18.489999999999998</v>
       </c>
       <c r="AO10" t="s">
+        <v>129</v>
+      </c>
+      <c r="AP10" t="s">
         <v>130</v>
       </c>
-      <c r="AP10" t="s">
-        <v>131</v>
-      </c>
       <c r="AQ10" t="s">
-        <v>132</v>
+        <v>131</v>
+      </c>
+      <c r="EF10" t="s">
+        <v>137</v>
       </c>
       <c r="EG10" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="EH10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="11" spans="1:138" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>161</v>
       </c>
-      <c r="EI10" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="11" spans="1:139" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>162</v>
-      </c>
       <c r="B11" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C11" s="16">
         <v>2023</v>
@@ -3504,34 +3486,34 @@
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="J11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="L11" s="2">
         <v>155</v>
       </c>
       <c r="M11" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="O11">
         <v>6</v>
       </c>
       <c r="P11" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Q11" s="2">
         <v>21</v>
@@ -3546,25 +3528,25 @@
         <v>155</v>
       </c>
       <c r="AC11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AD11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AE11" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AF11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AG11" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AH11" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AI11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AJ11" s="2">
         <v>155</v>
@@ -3582,30 +3564,30 @@
         <v>18.670000000000002</v>
       </c>
       <c r="AO11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AP11" t="s">
         <v>130</v>
       </c>
-      <c r="AP11" t="s">
-        <v>131</v>
-      </c>
       <c r="AQ11" t="s">
-        <v>132</v>
+        <v>131</v>
+      </c>
+      <c r="EF11" t="s">
+        <v>161</v>
       </c>
       <c r="EG11" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="EH11" t="s">
-        <v>161</v>
-      </c>
-      <c r="EI11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="12" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B12" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C12" s="16">
         <v>2023</v>
@@ -3614,28 +3596,28 @@
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="J12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L12">
         <v>73</v>
       </c>
       <c r="M12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N12">
         <v>19</v>
@@ -3644,58 +3626,58 @@
         <v>4</v>
       </c>
       <c r="P12" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Q12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="R12" t="s">
+        <v>193</v>
+      </c>
+      <c r="U12" t="s">
+        <v>194</v>
+      </c>
+      <c r="V12" t="s">
         <v>195</v>
       </c>
-      <c r="U12" t="s">
-        <v>196</v>
-      </c>
-      <c r="V12" t="s">
-        <v>197</v>
-      </c>
       <c r="W12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="X12" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="Y12" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>164</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>193</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>156</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AH12" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="AI12" t="s">
         <v>128</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>195</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>165</v>
-      </c>
-      <c r="AB12" t="s">
-        <v>195</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AE12" t="s">
-        <v>157</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AH12" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="AI12" t="s">
-        <v>129</v>
       </c>
       <c r="AJ12">
         <v>54</v>
@@ -3713,16 +3695,16 @@
         <v>20.18</v>
       </c>
       <c r="AO12" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AP12" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ12" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR12" t="s">
         <v>132</v>
-      </c>
-      <c r="AQ12" t="s">
-        <v>132</v>
-      </c>
-      <c r="AR12" t="s">
-        <v>133</v>
       </c>
       <c r="AS12">
         <v>54</v>
@@ -3740,16 +3722,16 @@
         <v>6.64</v>
       </c>
       <c r="AX12" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AY12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AZ12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BA12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="BB12">
         <v>54</v>
@@ -3767,16 +3749,16 @@
         <v>5.81</v>
       </c>
       <c r="BG12" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="BH12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BI12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="CA12" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="CB12">
         <v>54</v>
@@ -3794,72 +3776,72 @@
         <v>4.03</v>
       </c>
       <c r="CG12" t="s">
+        <v>196</v>
+      </c>
+      <c r="CH12" t="s">
+        <v>131</v>
+      </c>
+      <c r="CI12" t="s">
+        <v>131</v>
+      </c>
+      <c r="DB12">
+        <v>23</v>
+      </c>
+      <c r="DC12">
+        <v>72</v>
+      </c>
+      <c r="DF12">
+        <v>6</v>
+      </c>
+      <c r="DG12">
+        <v>72</v>
+      </c>
+      <c r="DJ12">
+        <v>4</v>
+      </c>
+      <c r="DK12">
+        <v>72</v>
+      </c>
+      <c r="DL12">
+        <v>4</v>
+      </c>
+      <c r="DM12">
+        <v>72</v>
+      </c>
+      <c r="DT12">
+        <v>2</v>
+      </c>
+      <c r="DU12">
+        <v>72</v>
+      </c>
+      <c r="DX12">
+        <v>1</v>
+      </c>
+      <c r="DY12">
+        <v>72</v>
+      </c>
+      <c r="ED12">
+        <v>1</v>
+      </c>
+      <c r="EE12">
+        <v>72</v>
+      </c>
+      <c r="EF12" t="s">
+        <v>161</v>
+      </c>
+      <c r="EG12" t="s">
+        <v>160</v>
+      </c>
+      <c r="EH12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="13" spans="1:138" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>198</v>
       </c>
-      <c r="CH12" t="s">
-        <v>132</v>
-      </c>
-      <c r="CI12" t="s">
-        <v>132</v>
-      </c>
-      <c r="DC12">
-        <v>23</v>
-      </c>
-      <c r="DD12">
-        <v>72</v>
-      </c>
-      <c r="DG12">
-        <v>6</v>
-      </c>
-      <c r="DH12">
-        <v>72</v>
-      </c>
-      <c r="DK12">
-        <v>4</v>
-      </c>
-      <c r="DL12">
-        <v>72</v>
-      </c>
-      <c r="DM12">
-        <v>4</v>
-      </c>
-      <c r="DN12">
-        <v>72</v>
-      </c>
-      <c r="DU12">
-        <v>2</v>
-      </c>
-      <c r="DV12">
-        <v>72</v>
-      </c>
-      <c r="DY12">
-        <v>1</v>
-      </c>
-      <c r="DZ12">
-        <v>72</v>
-      </c>
-      <c r="EE12">
-        <v>1</v>
-      </c>
-      <c r="EF12">
-        <v>72</v>
-      </c>
-      <c r="EG12" t="s">
-        <v>162</v>
-      </c>
-      <c r="EH12" t="s">
-        <v>161</v>
-      </c>
-      <c r="EI12" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="13" spans="1:139" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>200</v>
-      </c>
       <c r="B13" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C13" s="16">
         <v>2023</v>
@@ -3868,28 +3850,28 @@
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G13" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H13" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="J13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K13" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L13">
         <v>71</v>
       </c>
       <c r="M13" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N13">
         <v>19</v>
@@ -3898,58 +3880,58 @@
         <v>4</v>
       </c>
       <c r="P13" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Q13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="R13" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="U13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="V13" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="W13" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="X13" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="Y13" s="5">
         <v>0</v>
       </c>
       <c r="Z13" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="AA13" s="5">
         <v>2</v>
       </c>
       <c r="AB13" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="AC13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AD13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AE13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AF13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AG13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AH13" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AI13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AJ13">
         <v>49</v>
@@ -3967,16 +3949,16 @@
         <v>17.03</v>
       </c>
       <c r="AO13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AP13" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ13" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR13" t="s">
         <v>132</v>
-      </c>
-      <c r="AQ13" t="s">
-        <v>132</v>
-      </c>
-      <c r="AR13" t="s">
-        <v>133</v>
       </c>
       <c r="AS13">
         <v>49</v>
@@ -3994,16 +3976,16 @@
         <v>6.14</v>
       </c>
       <c r="AX13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AY13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AZ13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BA13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="BB13">
         <v>49</v>
@@ -4021,16 +4003,16 @@
         <v>5.85</v>
       </c>
       <c r="BG13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="BH13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BI13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="CA13" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="CB13">
         <v>49</v>
@@ -4048,72 +4030,72 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="CG13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="CH13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="CI13" t="s">
-        <v>132</v>
+        <v>131</v>
+      </c>
+      <c r="DB13">
+        <v>14</v>
       </c>
       <c r="DC13">
-        <v>14</v>
-      </c>
-      <c r="DD13">
         <v>65</v>
       </c>
+      <c r="DF13">
+        <v>3</v>
+      </c>
       <c r="DG13">
+        <v>65</v>
+      </c>
+      <c r="DJ13">
+        <v>4</v>
+      </c>
+      <c r="DK13">
+        <v>65</v>
+      </c>
+      <c r="DL13">
+        <v>0</v>
+      </c>
+      <c r="DM13">
+        <v>65</v>
+      </c>
+      <c r="DT13">
+        <v>0</v>
+      </c>
+      <c r="DU13">
+        <v>65</v>
+      </c>
+      <c r="DX13">
         <v>3</v>
       </c>
-      <c r="DH13">
+      <c r="DY13">
         <v>65</v>
       </c>
-      <c r="DK13">
-        <v>4</v>
-      </c>
-      <c r="DL13">
+      <c r="ED13">
+        <v>2</v>
+      </c>
+      <c r="EE13">
         <v>65</v>
       </c>
-      <c r="DM13">
-        <v>0</v>
-      </c>
-      <c r="DN13">
-        <v>65</v>
-      </c>
-      <c r="DU13">
-        <v>0</v>
-      </c>
-      <c r="DV13">
-        <v>65</v>
-      </c>
-      <c r="DY13">
-        <v>3</v>
-      </c>
-      <c r="DZ13">
-        <v>65</v>
-      </c>
-      <c r="EE13">
-        <v>2</v>
-      </c>
-      <c r="EF13">
-        <v>65</v>
+      <c r="EF13" t="s">
+        <v>137</v>
       </c>
       <c r="EG13" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="EH13" t="s">
-        <v>161</v>
-      </c>
-      <c r="EI13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="14" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C14" s="16">
         <v>2023</v>
@@ -4122,28 +4104,28 @@
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G14" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H14" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="J14" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K14" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L14">
         <v>69</v>
       </c>
       <c r="M14" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N14">
         <v>15</v>
@@ -4152,58 +4134,58 @@
         <v>4</v>
       </c>
       <c r="P14" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Q14" t="s">
+        <v>149</v>
+      </c>
+      <c r="R14" t="s">
+        <v>205</v>
+      </c>
+      <c r="U14" t="s">
         <v>150</v>
       </c>
-      <c r="R14" t="s">
-        <v>207</v>
-      </c>
-      <c r="U14" t="s">
-        <v>151</v>
-      </c>
       <c r="V14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="W14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="X14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Y14" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>205</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>164</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>205</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>154</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>154</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>156</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>154</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>154</v>
+      </c>
+      <c r="AH14" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="AI14" t="s">
         <v>128</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>207</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>165</v>
-      </c>
-      <c r="AB14" t="s">
-        <v>207</v>
-      </c>
-      <c r="AC14" t="s">
-        <v>155</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>155</v>
-      </c>
-      <c r="AE14" t="s">
-        <v>157</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>155</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>155</v>
-      </c>
-      <c r="AH14" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="AI14" t="s">
-        <v>129</v>
       </c>
       <c r="AJ14">
         <v>51</v>
@@ -4221,16 +4203,16 @@
         <v>17.670000000000002</v>
       </c>
       <c r="AO14" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AP14" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ14" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR14" t="s">
         <v>132</v>
-      </c>
-      <c r="AQ14" t="s">
-        <v>132</v>
-      </c>
-      <c r="AR14" t="s">
-        <v>133</v>
       </c>
       <c r="AS14">
         <v>51</v>
@@ -4248,16 +4230,16 @@
         <v>6.5</v>
       </c>
       <c r="AX14" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AY14" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AZ14" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BA14" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="BB14">
         <v>51</v>
@@ -4275,16 +4257,16 @@
         <v>5.41</v>
       </c>
       <c r="BG14" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="BH14" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BI14" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="CA14" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="CB14">
         <v>51</v>
@@ -4302,72 +4284,72 @@
         <v>4.08</v>
       </c>
       <c r="CG14" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="CH14" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="CI14" t="s">
-        <v>132</v>
+        <v>131</v>
+      </c>
+      <c r="DB14">
+        <v>23</v>
       </c>
       <c r="DC14">
-        <v>23</v>
-      </c>
-      <c r="DD14">
         <v>68</v>
       </c>
+      <c r="DF14">
+        <v>2</v>
+      </c>
       <c r="DG14">
+        <v>68</v>
+      </c>
+      <c r="DJ14">
+        <v>5</v>
+      </c>
+      <c r="DK14">
+        <v>68</v>
+      </c>
+      <c r="DL14">
         <v>2</v>
       </c>
-      <c r="DH14">
+      <c r="DM14">
         <v>68</v>
       </c>
-      <c r="DK14">
+      <c r="DT14">
+        <v>8</v>
+      </c>
+      <c r="DU14">
+        <v>68</v>
+      </c>
+      <c r="DX14">
         <v>5</v>
       </c>
-      <c r="DL14">
+      <c r="DY14">
         <v>68</v>
       </c>
-      <c r="DM14">
-        <v>2</v>
-      </c>
-      <c r="DN14">
+      <c r="ED14">
+        <v>0</v>
+      </c>
+      <c r="EE14">
         <v>68</v>
       </c>
-      <c r="DU14">
-        <v>8</v>
-      </c>
-      <c r="DV14">
-        <v>68</v>
-      </c>
-      <c r="DY14">
-        <v>5</v>
-      </c>
-      <c r="DZ14">
-        <v>68</v>
-      </c>
-      <c r="EE14">
-        <v>0</v>
-      </c>
-      <c r="EF14">
-        <v>68</v>
+      <c r="EF14" t="s">
+        <v>137</v>
       </c>
       <c r="EG14" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="EH14" t="s">
-        <v>161</v>
-      </c>
-      <c r="EI14" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="15" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B15" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C15" s="16">
         <v>2023</v>
@@ -4376,28 +4358,28 @@
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G15" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H15" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="J15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K15" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L15">
         <v>74</v>
       </c>
       <c r="M15" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N15">
         <v>18</v>
@@ -4406,58 +4388,58 @@
         <v>4</v>
       </c>
       <c r="P15" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Q15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="R15" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="U15" t="s">
+        <v>163</v>
+      </c>
+      <c r="V15" t="s">
+        <v>209</v>
+      </c>
+      <c r="W15" t="s">
         <v>164</v>
       </c>
-      <c r="V15" t="s">
-        <v>211</v>
-      </c>
-      <c r="W15" t="s">
-        <v>165</v>
-      </c>
       <c r="X15" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="Y15" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>202</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>127</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>202</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>154</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>154</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>154</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>154</v>
+      </c>
+      <c r="AH15" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="AI15" t="s">
         <v>128</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>204</v>
-      </c>
-      <c r="AA15" t="s">
-        <v>128</v>
-      </c>
-      <c r="AB15" t="s">
-        <v>204</v>
-      </c>
-      <c r="AC15" t="s">
-        <v>155</v>
-      </c>
-      <c r="AD15" t="s">
-        <v>155</v>
-      </c>
-      <c r="AE15" t="s">
-        <v>157</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>155</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>155</v>
-      </c>
-      <c r="AH15" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="AI15" t="s">
-        <v>129</v>
       </c>
       <c r="AJ15">
         <v>56</v>
@@ -4475,16 +4457,16 @@
         <v>15.78</v>
       </c>
       <c r="AO15" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AP15" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ15" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR15" t="s">
         <v>132</v>
-      </c>
-      <c r="AQ15" t="s">
-        <v>132</v>
-      </c>
-      <c r="AR15" t="s">
-        <v>133</v>
       </c>
       <c r="AS15">
         <v>56</v>
@@ -4502,16 +4484,16 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="AX15" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AY15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AZ15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BA15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="BB15">
         <v>56</v>
@@ -4529,16 +4511,16 @@
         <v>5.13</v>
       </c>
       <c r="BG15" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="BH15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BI15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="CA15" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="CB15">
         <v>56</v>
@@ -4556,102 +4538,102 @@
         <v>4.09</v>
       </c>
       <c r="CG15" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="CH15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="CI15" t="s">
-        <v>132</v>
+        <v>131</v>
+      </c>
+      <c r="DB15">
+        <v>36</v>
       </c>
       <c r="DC15">
-        <v>36</v>
-      </c>
-      <c r="DD15">
         <v>71</v>
       </c>
+      <c r="DF15">
+        <v>5</v>
+      </c>
       <c r="DG15">
+        <v>71</v>
+      </c>
+      <c r="DJ15">
+        <v>6</v>
+      </c>
+      <c r="DK15">
+        <v>71</v>
+      </c>
+      <c r="DL15">
+        <v>6</v>
+      </c>
+      <c r="DM15">
+        <v>71</v>
+      </c>
+      <c r="DT15">
+        <v>0</v>
+      </c>
+      <c r="DU15">
+        <v>71</v>
+      </c>
+      <c r="DX15">
         <v>5</v>
       </c>
-      <c r="DH15">
+      <c r="DY15">
         <v>71</v>
       </c>
-      <c r="DK15">
-        <v>6</v>
-      </c>
-      <c r="DL15">
+      <c r="ED15">
+        <v>8</v>
+      </c>
+      <c r="EE15">
         <v>71</v>
       </c>
-      <c r="DM15">
-        <v>6</v>
-      </c>
-      <c r="DN15">
-        <v>71</v>
-      </c>
-      <c r="DU15">
-        <v>0</v>
-      </c>
-      <c r="DV15">
-        <v>71</v>
-      </c>
-      <c r="DY15">
-        <v>5</v>
-      </c>
-      <c r="DZ15">
-        <v>71</v>
-      </c>
-      <c r="EE15">
-        <v>8</v>
-      </c>
-      <c r="EF15">
-        <v>71</v>
+      <c r="EF15" t="s">
+        <v>210</v>
       </c>
       <c r="EG15" t="s">
+        <v>160</v>
+      </c>
+      <c r="EH15" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="16" spans="1:138" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>211</v>
+      </c>
+      <c r="B16" t="s">
         <v>212</v>
-      </c>
-      <c r="EH15" t="s">
-        <v>161</v>
-      </c>
-      <c r="EI15" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="16" spans="1:139" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>213</v>
-      </c>
-      <c r="B16" t="s">
-        <v>214</v>
       </c>
       <c r="C16" s="16">
         <v>2023</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E16">
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G16" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H16" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I16" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="K16" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L16">
         <v>34</v>
       </c>
       <c r="M16" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="N16">
         <v>18</v>
@@ -4660,120 +4642,120 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="P16" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="U16" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="V16" t="s">
+        <v>216</v>
+      </c>
+      <c r="W16" t="s">
+        <v>127</v>
+      </c>
+      <c r="X16" t="s">
+        <v>216</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>216</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>127</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>216</v>
+      </c>
+      <c r="DB16">
+        <v>16</v>
+      </c>
+      <c r="DC16">
+        <v>34</v>
+      </c>
+      <c r="DD16">
+        <v>0</v>
+      </c>
+      <c r="DE16">
+        <v>34</v>
+      </c>
+      <c r="DF16">
+        <v>0</v>
+      </c>
+      <c r="DG16">
+        <v>34</v>
+      </c>
+      <c r="DH16">
+        <v>2</v>
+      </c>
+      <c r="DI16">
+        <v>34</v>
+      </c>
+      <c r="DJ16">
+        <v>7</v>
+      </c>
+      <c r="DK16">
+        <v>34</v>
+      </c>
+      <c r="DL16">
+        <v>0</v>
+      </c>
+      <c r="DM16">
+        <v>34</v>
+      </c>
+      <c r="DN16">
+        <v>5</v>
+      </c>
+      <c r="DO16">
+        <v>34</v>
+      </c>
+      <c r="EF16" t="s">
+        <v>161</v>
+      </c>
+      <c r="EG16" t="s">
+        <v>217</v>
+      </c>
+      <c r="EH16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="17" spans="1:138" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>218</v>
       </c>
-      <c r="W16" t="s">
-        <v>128</v>
-      </c>
-      <c r="X16" t="s">
-        <v>218</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>128</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>218</v>
-      </c>
-      <c r="AA16" t="s">
-        <v>128</v>
-      </c>
-      <c r="AB16" t="s">
-        <v>218</v>
-      </c>
-      <c r="DC16">
-        <v>16</v>
-      </c>
-      <c r="DD16">
-        <v>34</v>
-      </c>
-      <c r="DE16">
-        <v>0</v>
-      </c>
-      <c r="DF16">
-        <v>34</v>
-      </c>
-      <c r="DG16">
-        <v>0</v>
-      </c>
-      <c r="DH16">
-        <v>34</v>
-      </c>
-      <c r="DI16">
-        <v>2</v>
-      </c>
-      <c r="DJ16">
-        <v>34</v>
-      </c>
-      <c r="DK16">
-        <v>7</v>
-      </c>
-      <c r="DL16">
-        <v>34</v>
-      </c>
-      <c r="DM16">
-        <v>0</v>
-      </c>
-      <c r="DN16">
-        <v>34</v>
-      </c>
-      <c r="DO16">
-        <v>5</v>
-      </c>
-      <c r="DP16">
-        <v>34</v>
-      </c>
-      <c r="EG16" t="s">
-        <v>162</v>
-      </c>
-      <c r="EH16" t="s">
-        <v>219</v>
-      </c>
-      <c r="EI16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="17" spans="1:139" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>220</v>
-      </c>
       <c r="B17" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C17" s="16">
         <v>2023</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E17">
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H17" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I17" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="K17" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L17">
         <v>35</v>
       </c>
       <c r="M17" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="N17">
         <v>14</v>
@@ -4782,120 +4764,120 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="P17" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="U17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="V17" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="W17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="X17" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Y17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Z17" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AA17" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AB17" t="s">
-        <v>222</v>
+        <v>220</v>
+      </c>
+      <c r="DB17">
+        <v>34</v>
       </c>
       <c r="DC17">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="DD17">
+        <v>5</v>
+      </c>
+      <c r="DE17">
         <v>35</v>
       </c>
-      <c r="DE17">
-        <v>5</v>
-      </c>
       <c r="DF17">
+        <v>0</v>
+      </c>
+      <c r="DG17">
         <v>35</v>
       </c>
-      <c r="DG17">
-        <v>0</v>
-      </c>
       <c r="DH17">
+        <v>10</v>
+      </c>
+      <c r="DI17">
         <v>35</v>
       </c>
-      <c r="DI17">
-        <v>10</v>
-      </c>
       <c r="DJ17">
+        <v>4</v>
+      </c>
+      <c r="DK17">
         <v>35</v>
       </c>
-      <c r="DK17">
-        <v>4</v>
-      </c>
       <c r="DL17">
+        <v>12</v>
+      </c>
+      <c r="DM17">
         <v>35</v>
       </c>
-      <c r="DM17">
-        <v>12</v>
-      </c>
       <c r="DN17">
+        <v>21</v>
+      </c>
+      <c r="DO17">
         <v>35</v>
       </c>
-      <c r="DO17">
-        <v>21</v>
-      </c>
-      <c r="DP17">
-        <v>35</v>
+      <c r="EF17" t="s">
+        <v>137</v>
       </c>
       <c r="EG17" t="s">
-        <v>138</v>
+        <v>217</v>
       </c>
       <c r="EH17" t="s">
-        <v>219</v>
-      </c>
-      <c r="EI17" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="18" spans="1:139" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:138" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B18" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C18" s="16">
         <v>2023</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G18" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H18" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="I18" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="K18" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L18">
         <v>36</v>
       </c>
       <c r="M18" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="N18">
         <v>13</v>
@@ -4904,123 +4886,123 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="P18" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="U18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="V18" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="W18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="X18" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="Y18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Z18" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AA18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AB18" t="s">
-        <v>227</v>
+        <v>225</v>
+      </c>
+      <c r="DB18">
+        <v>15</v>
       </c>
       <c r="DC18">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="DD18">
+        <v>0</v>
+      </c>
+      <c r="DE18">
         <v>36</v>
       </c>
-      <c r="DE18">
-        <v>0</v>
-      </c>
       <c r="DF18">
+        <v>3</v>
+      </c>
+      <c r="DG18">
         <v>36</v>
       </c>
-      <c r="DG18">
-        <v>3</v>
-      </c>
       <c r="DH18">
+        <v>1</v>
+      </c>
+      <c r="DI18">
         <v>36</v>
       </c>
-      <c r="DI18">
+      <c r="DJ18">
         <v>1</v>
       </c>
-      <c r="DJ18">
+      <c r="DK18">
         <v>36</v>
       </c>
-      <c r="DK18">
-        <v>1</v>
-      </c>
       <c r="DL18">
+        <v>0</v>
+      </c>
+      <c r="DM18">
         <v>36</v>
       </c>
-      <c r="DM18">
-        <v>0</v>
-      </c>
       <c r="DN18">
+        <v>5</v>
+      </c>
+      <c r="DO18">
         <v>36</v>
       </c>
-      <c r="DO18">
-        <v>5</v>
-      </c>
-      <c r="DP18">
-        <v>36</v>
+      <c r="EF18" t="s">
+        <v>210</v>
       </c>
       <c r="EG18" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="EH18" t="s">
-        <v>219</v>
-      </c>
-      <c r="EI18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="19" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B19" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C19" s="16">
         <v>2023</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E19">
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G19" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H19" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="J19" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K19" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="L19">
         <v>68</v>
       </c>
       <c r="M19" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="N19">
         <v>15</v>
@@ -5029,105 +5011,105 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="P19" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="W19" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="X19" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Y19" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Z19" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AA19" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AB19" t="s">
-        <v>232</v>
+        <v>230</v>
+      </c>
+      <c r="DB19">
+        <v>2</v>
       </c>
       <c r="DC19">
-        <v>2</v>
-      </c>
-      <c r="DD19">
         <v>63</v>
       </c>
+      <c r="DH19">
+        <v>1</v>
+      </c>
       <c r="DI19">
+        <v>63</v>
+      </c>
+      <c r="DL19">
         <v>1</v>
       </c>
-      <c r="DJ19">
+      <c r="DM19">
         <v>63</v>
       </c>
-      <c r="DM19">
+      <c r="DN19" s="8">
+        <v>0</v>
+      </c>
+      <c r="DO19">
+        <v>63</v>
+      </c>
+      <c r="DR19">
         <v>1</v>
       </c>
-      <c r="DN19">
-        <v>63</v>
-      </c>
-      <c r="DO19" s="8">
-        <v>0</v>
-      </c>
-      <c r="DP19">
-        <v>63</v>
-      </c>
       <c r="DS19">
-        <v>1</v>
-      </c>
-      <c r="DT19">
         <v>59</v>
       </c>
+      <c r="EF19" t="s">
+        <v>161</v>
+      </c>
       <c r="EG19" t="s">
-        <v>162</v>
+        <v>217</v>
       </c>
       <c r="EH19" t="s">
-        <v>219</v>
-      </c>
-      <c r="EI19" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="20" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B20" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C20" s="16">
         <v>2023</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G20" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H20" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="J20" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K20" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="L20">
         <v>68</v>
       </c>
       <c r="M20" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="N20">
         <v>15</v>
@@ -5136,108 +5118,108 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="P20" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="U20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="V20" t="s">
+        <v>230</v>
+      </c>
+      <c r="W20" t="s">
+        <v>127</v>
+      </c>
+      <c r="X20" t="s">
+        <v>230</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>230</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>164</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>230</v>
+      </c>
+      <c r="DB20">
+        <v>32</v>
+      </c>
+      <c r="DC20">
+        <v>63</v>
+      </c>
+      <c r="DH20">
+        <v>7</v>
+      </c>
+      <c r="DI20">
+        <v>63</v>
+      </c>
+      <c r="DL20">
+        <v>16</v>
+      </c>
+      <c r="DM20">
+        <v>63</v>
+      </c>
+      <c r="DN20">
+        <v>16</v>
+      </c>
+      <c r="DO20">
+        <v>63</v>
+      </c>
+      <c r="DR20">
+        <v>5</v>
+      </c>
+      <c r="DS20">
+        <v>62</v>
+      </c>
+      <c r="EF20" t="s">
+        <v>137</v>
+      </c>
+      <c r="EG20" t="s">
+        <v>217</v>
+      </c>
+      <c r="EH20" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="21" spans="1:138" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
         <v>232</v>
       </c>
-      <c r="W20" t="s">
-        <v>128</v>
-      </c>
-      <c r="X20" t="s">
-        <v>232</v>
-      </c>
-      <c r="Y20" t="s">
-        <v>128</v>
-      </c>
-      <c r="Z20" t="s">
-        <v>232</v>
-      </c>
-      <c r="AA20" t="s">
-        <v>165</v>
-      </c>
-      <c r="AB20" t="s">
-        <v>232</v>
-      </c>
-      <c r="DC20">
-        <v>32</v>
-      </c>
-      <c r="DD20">
-        <v>63</v>
-      </c>
-      <c r="DI20">
-        <v>7</v>
-      </c>
-      <c r="DJ20">
-        <v>63</v>
-      </c>
-      <c r="DM20">
-        <v>16</v>
-      </c>
-      <c r="DN20">
-        <v>63</v>
-      </c>
-      <c r="DO20">
-        <v>16</v>
-      </c>
-      <c r="DP20">
-        <v>63</v>
-      </c>
-      <c r="DS20">
-        <v>5</v>
-      </c>
-      <c r="DT20">
-        <v>62</v>
-      </c>
-      <c r="EG20" t="s">
-        <v>138</v>
-      </c>
-      <c r="EH20" t="s">
-        <v>219</v>
-      </c>
-      <c r="EI20" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="21" spans="1:139" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>234</v>
-      </c>
       <c r="B21" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C21" s="16">
         <v>2021</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I21" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="K21" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L21">
         <v>12</v>
       </c>
       <c r="M21" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -5246,108 +5228,108 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="P21" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="U21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="V21" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="W21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="X21" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Y21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Z21" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AA21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AB21" t="s">
-        <v>140</v>
+        <v>139</v>
+      </c>
+      <c r="DB21">
+        <v>1</v>
       </c>
       <c r="DC21">
+        <v>12</v>
+      </c>
+      <c r="DL21">
         <v>1</v>
       </c>
-      <c r="DD21">
+      <c r="DM21">
         <v>12</v>
       </c>
-      <c r="DM21">
-        <v>1</v>
-      </c>
       <c r="DN21">
+        <v>0</v>
+      </c>
+      <c r="DO21">
         <v>12</v>
       </c>
-      <c r="DO21">
-        <v>0</v>
-      </c>
       <c r="DP21">
+        <v>0</v>
+      </c>
+      <c r="DQ21">
         <v>12</v>
       </c>
-      <c r="DQ21">
-        <v>0</v>
-      </c>
       <c r="DR21">
+        <v>0</v>
+      </c>
+      <c r="DS21">
         <v>12</v>
       </c>
-      <c r="DS21">
-        <v>0</v>
-      </c>
-      <c r="DT21">
-        <v>12</v>
+      <c r="EF21" t="s">
+        <v>137</v>
       </c>
       <c r="EG21" t="s">
-        <v>138</v>
+        <v>217</v>
       </c>
       <c r="EH21" t="s">
-        <v>219</v>
-      </c>
-      <c r="EI21" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="22" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C22" s="16">
         <v>2021</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H22" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I22" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="K22" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L22">
         <v>12</v>
       </c>
       <c r="M22" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -5356,108 +5338,108 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="P22" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="U22" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="V22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="W22" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="X22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Y22" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Z22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AA22" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AB22" t="s">
-        <v>140</v>
+        <v>139</v>
+      </c>
+      <c r="DB22">
+        <v>1</v>
       </c>
       <c r="DC22">
+        <v>12</v>
+      </c>
+      <c r="DL22">
+        <v>0</v>
+      </c>
+      <c r="DM22">
+        <v>12</v>
+      </c>
+      <c r="DN22">
         <v>1</v>
       </c>
-      <c r="DD22">
+      <c r="DO22">
         <v>12</v>
       </c>
-      <c r="DM22">
-        <v>0</v>
-      </c>
-      <c r="DN22">
+      <c r="DP22">
+        <v>0</v>
+      </c>
+      <c r="DQ22">
         <v>12</v>
       </c>
-      <c r="DO22">
-        <v>1</v>
-      </c>
-      <c r="DP22">
+      <c r="DR22">
+        <v>0</v>
+      </c>
+      <c r="DS22">
         <v>12</v>
       </c>
-      <c r="DQ22">
-        <v>0</v>
-      </c>
-      <c r="DR22">
-        <v>12</v>
-      </c>
-      <c r="DS22">
-        <v>0</v>
-      </c>
-      <c r="DT22">
-        <v>12</v>
+      <c r="EF22" t="s">
+        <v>137</v>
       </c>
       <c r="EG22" t="s">
-        <v>138</v>
+        <v>217</v>
       </c>
       <c r="EH22" t="s">
-        <v>219</v>
-      </c>
-      <c r="EI22" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="23" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B23" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C23" s="16">
         <v>2021</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I23" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="K23" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L23">
         <v>24</v>
       </c>
       <c r="M23" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -5466,108 +5448,108 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="P23" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="U23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="V23" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="W23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="X23" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="Y23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Z23" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AA23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AB23" t="s">
-        <v>190</v>
+        <v>188</v>
+      </c>
+      <c r="DB23">
+        <v>1</v>
       </c>
       <c r="DC23">
-        <v>1</v>
-      </c>
-      <c r="DD23">
         <v>24</v>
       </c>
+      <c r="DL23">
+        <v>0</v>
+      </c>
       <c r="DM23">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="DN23">
+        <v>0</v>
+      </c>
+      <c r="DO23">
         <v>24</v>
       </c>
-      <c r="DO23">
-        <v>0</v>
-      </c>
       <c r="DP23">
+        <v>0</v>
+      </c>
+      <c r="DQ23">
         <v>24</v>
       </c>
-      <c r="DQ23">
-        <v>0</v>
-      </c>
       <c r="DR23">
+        <v>0</v>
+      </c>
+      <c r="DS23">
         <v>24</v>
       </c>
-      <c r="DS23">
-        <v>0</v>
-      </c>
-      <c r="DT23">
-        <v>24</v>
+      <c r="EF23" t="s">
+        <v>161</v>
       </c>
       <c r="EG23" t="s">
-        <v>162</v>
+        <v>217</v>
       </c>
       <c r="EH23" t="s">
-        <v>219</v>
-      </c>
-      <c r="EI23" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="24" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B24" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C24" s="16">
         <v>2023</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H24" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I24" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="K24" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L24">
         <v>16</v>
       </c>
       <c r="M24" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="N24">
         <v>12</v>
@@ -5576,72 +5558,72 @@
         <v>2</v>
       </c>
       <c r="P24" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Y24" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Z24" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AA24" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AB24" t="s">
-        <v>151</v>
+        <v>150</v>
+      </c>
+      <c r="DB24" s="6">
+        <v>6</v>
       </c>
       <c r="DC24" s="6">
-        <v>6</v>
-      </c>
-      <c r="DD24" s="6">
         <v>15</v>
       </c>
+      <c r="EF24" t="s">
+        <v>137</v>
+      </c>
       <c r="EG24" t="s">
-        <v>138</v>
+        <v>217</v>
       </c>
       <c r="EH24" t="s">
-        <v>219</v>
-      </c>
-      <c r="EI24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="25" spans="1:139" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:138" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B25" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C25" s="16">
         <v>2023</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H25" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I25" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="K25" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L25">
         <v>16</v>
       </c>
       <c r="M25" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="N25">
         <v>12</v>
@@ -5650,72 +5632,72 @@
         <v>2</v>
       </c>
       <c r="P25" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Y25" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Z25" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AA25" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AB25" t="s">
-        <v>151</v>
+        <v>150</v>
+      </c>
+      <c r="DB25" s="6">
+        <v>1</v>
       </c>
       <c r="DC25" s="6">
-        <v>1</v>
-      </c>
-      <c r="DD25" s="6">
         <v>13</v>
       </c>
+      <c r="EF25" t="s">
+        <v>137</v>
+      </c>
       <c r="EG25" t="s">
-        <v>138</v>
+        <v>217</v>
       </c>
       <c r="EH25" t="s">
-        <v>219</v>
-      </c>
-      <c r="EI25" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="26" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B26" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C26" s="16">
         <v>2023</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G26" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I26" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="K26" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L26">
         <v>16</v>
       </c>
       <c r="M26" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="N26">
         <v>12</v>
@@ -5724,42 +5706,42 @@
         <v>2</v>
       </c>
       <c r="P26" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Y26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Z26" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AA26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AB26" t="s">
-        <v>151</v>
+        <v>150</v>
+      </c>
+      <c r="DB26" s="6">
+        <v>2</v>
       </c>
       <c r="DC26" s="6">
-        <v>2</v>
-      </c>
-      <c r="DD26" s="6">
         <v>14</v>
       </c>
+      <c r="EF26" t="s">
+        <v>161</v>
+      </c>
       <c r="EG26" t="s">
-        <v>162</v>
+        <v>217</v>
       </c>
       <c r="EH26" t="s">
-        <v>219</v>
-      </c>
-      <c r="EI26" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="27" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A27" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C27" s="16">
         <v>2024</v>
@@ -5768,19 +5750,19 @@
         <v>1</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K27" s="11">
         <v>303</v>
@@ -5789,13 +5771,13 @@
         <v>201</v>
       </c>
       <c r="M27" s="10" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="O27" s="10">
         <v>52</v>
       </c>
       <c r="P27" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="S27" s="10">
         <v>29</v>
@@ -5816,25 +5798,25 @@
         <v>201</v>
       </c>
       <c r="AC27" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="AD27" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="AE27" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="AD27" s="11" t="s">
+      <c r="AF27" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="AG27" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="AH27" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="AE27" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="AF27" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="AG27" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="AH27" s="11" t="s">
-        <v>156</v>
-      </c>
       <c r="CJ27" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="CK27" s="10">
         <v>201</v>
@@ -5846,63 +5828,60 @@
         <v>6.4</v>
       </c>
       <c r="CP27" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="CQ27" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="CQ27" s="10" t="s">
-        <v>131</v>
-      </c>
       <c r="CR27" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="CS27" s="10" t="s">
-        <v>250</v>
+        <v>130</v>
+      </c>
+      <c r="DD27" s="11">
+        <v>7</v>
       </c>
       <c r="DE27" s="11">
-        <v>7</v>
+        <v>201</v>
       </c>
       <c r="DF27" s="11">
+        <v>28</v>
+      </c>
+      <c r="DG27" s="11">
         <v>201</v>
       </c>
-      <c r="DG27" s="11">
-        <v>28</v>
-      </c>
-      <c r="DH27" s="11">
+      <c r="DN27" s="11">
+        <v>12</v>
+      </c>
+      <c r="DO27" s="11">
         <v>201</v>
       </c>
-      <c r="DO27" s="11">
-        <v>12</v>
-      </c>
-      <c r="DP27" s="11">
+      <c r="DX27" s="10">
+        <v>30</v>
+      </c>
+      <c r="DY27" s="10">
         <v>201</v>
       </c>
-      <c r="DY27" s="10">
-        <v>30</v>
-      </c>
-      <c r="DZ27" s="10">
+      <c r="ED27" s="10">
+        <v>8</v>
+      </c>
+      <c r="EE27" s="10">
         <v>201</v>
       </c>
-      <c r="EE27" s="10">
-        <v>8</v>
-      </c>
-      <c r="EF27" s="10">
-        <v>201</v>
+      <c r="EF27" t="s">
+        <v>137</v>
       </c>
       <c r="EG27" t="s">
-        <v>138</v>
+        <v>263</v>
       </c>
       <c r="EH27" t="s">
-        <v>266</v>
-      </c>
-      <c r="EI27" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="28" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A28" s="10" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C28" s="16">
         <v>2024</v>
@@ -5911,19 +5890,19 @@
         <v>1</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K28" s="11">
         <v>303</v>
@@ -5932,13 +5911,13 @@
         <v>102</v>
       </c>
       <c r="M28" s="10" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="O28" s="10">
         <v>52</v>
       </c>
       <c r="P28" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="S28" s="10">
         <v>6</v>
@@ -5959,25 +5938,25 @@
         <v>102</v>
       </c>
       <c r="AC28" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="AD28" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="AE28" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="AD28" s="11" t="s">
+      <c r="AF28" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="AG28" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="AH28" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="AE28" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="AF28" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="AG28" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="AH28" s="11" t="s">
-        <v>156</v>
-      </c>
       <c r="CJ28" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="CK28" s="10">
         <v>102</v>
@@ -5989,63 +5968,60 @@
         <v>6.4</v>
       </c>
       <c r="CP28" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="CQ28" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="CQ28" s="10" t="s">
-        <v>131</v>
-      </c>
       <c r="CR28" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="CS28" s="10" t="s">
-        <v>250</v>
+        <v>130</v>
+      </c>
+      <c r="DD28" s="11">
+        <v>12</v>
       </c>
       <c r="DE28" s="11">
-        <v>12</v>
+        <v>102</v>
       </c>
       <c r="DF28" s="11">
+        <v>10</v>
+      </c>
+      <c r="DG28" s="11">
         <v>102</v>
       </c>
-      <c r="DG28" s="11">
-        <v>10</v>
-      </c>
-      <c r="DH28" s="11">
+      <c r="DN28" s="11">
+        <v>21</v>
+      </c>
+      <c r="DO28" s="11">
         <v>102</v>
       </c>
-      <c r="DO28" s="11">
-        <v>21</v>
-      </c>
-      <c r="DP28" s="11">
+      <c r="DX28" s="10">
+        <v>11</v>
+      </c>
+      <c r="DY28" s="10">
         <v>102</v>
       </c>
-      <c r="DY28" s="10">
+      <c r="ED28" s="10">
         <v>11</v>
       </c>
-      <c r="DZ28" s="10">
+      <c r="EE28" s="10">
         <v>102</v>
       </c>
-      <c r="EE28" s="10">
-        <v>11</v>
-      </c>
-      <c r="EF28" s="10">
-        <v>102</v>
+      <c r="EF28" t="s">
+        <v>210</v>
       </c>
       <c r="EG28" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="EH28" t="s">
-        <v>266</v>
-      </c>
-      <c r="EI28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="29" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C29" s="16">
         <v>2024</v>
@@ -6054,19 +6030,19 @@
         <v>1</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G29" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H29">
         <v>150</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="K29" s="9">
         <v>27</v>
@@ -6084,7 +6060,7 @@
         <v>12</v>
       </c>
       <c r="P29" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Q29" s="11">
         <v>0</v>
@@ -6123,25 +6099,25 @@
         <v>12</v>
       </c>
       <c r="AC29" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AD29" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AE29" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="AD29" s="12" t="s">
+      <c r="AF29" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AG29" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AH29" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="AE29" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="AF29" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AG29" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AH29" s="12" t="s">
-        <v>156</v>
-      </c>
       <c r="AI29" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AJ29" s="11">
         <v>6</v>
@@ -6159,16 +6135,16 @@
         <v>6.27</v>
       </c>
       <c r="AO29" s="11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AP29" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ29" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR29" s="11" t="s">
         <v>132</v>
-      </c>
-      <c r="AQ29" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="AR29" s="11" t="s">
-        <v>133</v>
       </c>
       <c r="AS29" s="11">
         <v>6</v>
@@ -6186,16 +6162,16 @@
         <v>3.61</v>
       </c>
       <c r="AX29" s="11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AY29" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AZ29" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BA29" s="11" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="BB29" s="11">
         <v>6</v>
@@ -6213,72 +6189,72 @@
         <v>20.440000000000001</v>
       </c>
       <c r="BG29" s="11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="BH29" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BI29" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
+      </c>
+      <c r="DB29" s="11">
+        <v>4</v>
       </c>
       <c r="DC29" s="11">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="DD29" s="11">
+        <v>1</v>
+      </c>
+      <c r="DE29" s="11">
         <v>12</v>
       </c>
-      <c r="DE29" s="11">
-        <v>1</v>
-      </c>
-      <c r="DF29" s="11">
+      <c r="DH29" s="11">
+        <v>0</v>
+      </c>
+      <c r="DI29" s="11">
         <v>12</v>
       </c>
-      <c r="DI29" s="11">
-        <v>0</v>
-      </c>
       <c r="DJ29" s="11">
+        <v>0</v>
+      </c>
+      <c r="DK29" s="11">
         <v>12</v>
       </c>
-      <c r="DK29" s="11">
-        <v>0</v>
-      </c>
       <c r="DL29" s="11">
+        <v>2</v>
+      </c>
+      <c r="DM29" s="11">
         <v>12</v>
       </c>
-      <c r="DM29" s="11">
+      <c r="DN29" s="11">
+        <v>0</v>
+      </c>
+      <c r="DO29" s="11">
+        <v>12</v>
+      </c>
+      <c r="DX29" s="11">
         <v>2</v>
       </c>
-      <c r="DN29" s="11">
+      <c r="DY29" s="11">
         <v>12</v>
       </c>
-      <c r="DO29" s="11">
-        <v>0</v>
-      </c>
-      <c r="DP29" s="11">
-        <v>12</v>
-      </c>
-      <c r="DY29" s="11">
-        <v>2</v>
-      </c>
-      <c r="DZ29" s="11">
-        <v>12</v>
+      <c r="EF29" t="s">
+        <v>137</v>
       </c>
       <c r="EG29" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="EH29" t="s">
-        <v>161</v>
-      </c>
-      <c r="EI29" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="30" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C30" s="16">
         <v>2024</v>
@@ -6287,19 +6263,19 @@
         <v>1</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G30" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H30">
         <v>0</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="K30" s="9">
         <v>27</v>
@@ -6317,7 +6293,7 @@
         <v>12</v>
       </c>
       <c r="P30" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Q30" s="11">
         <v>1</v>
@@ -6356,25 +6332,25 @@
         <v>15</v>
       </c>
       <c r="AC30" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AD30" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AE30" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="AD30" s="12" t="s">
+      <c r="AF30" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AG30" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AH30" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="AE30" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="AF30" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AG30" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AH30" s="12" t="s">
-        <v>156</v>
-      </c>
       <c r="AI30" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AJ30" s="11">
         <v>10</v>
@@ -6392,16 +6368,16 @@
         <v>13.92</v>
       </c>
       <c r="AO30" s="11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AP30" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ30" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR30" s="11" t="s">
         <v>132</v>
-      </c>
-      <c r="AQ30" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="AR30" s="11" t="s">
-        <v>133</v>
       </c>
       <c r="AS30" s="11">
         <v>10</v>
@@ -6419,16 +6395,16 @@
         <v>5.25</v>
       </c>
       <c r="AX30" s="11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AY30" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AZ30" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BA30" s="11" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="BB30" s="11">
         <v>10</v>
@@ -6446,72 +6422,72 @@
         <v>12.86</v>
       </c>
       <c r="BG30" s="11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="BH30" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BI30" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
+      </c>
+      <c r="DB30" s="11">
+        <v>7</v>
       </c>
       <c r="DC30" s="11">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="DD30" s="11">
+        <v>0</v>
+      </c>
+      <c r="DE30" s="11">
         <v>15</v>
       </c>
-      <c r="DE30" s="11">
-        <v>0</v>
-      </c>
-      <c r="DF30" s="11">
+      <c r="DH30" s="11">
+        <v>0</v>
+      </c>
+      <c r="DI30" s="11">
         <v>15</v>
       </c>
-      <c r="DI30" s="11">
-        <v>0</v>
-      </c>
       <c r="DJ30" s="11">
+        <v>0</v>
+      </c>
+      <c r="DK30" s="11">
         <v>15</v>
       </c>
-      <c r="DK30" s="11">
-        <v>0</v>
-      </c>
       <c r="DL30" s="11">
+        <v>0</v>
+      </c>
+      <c r="DM30" s="11">
         <v>15</v>
       </c>
-      <c r="DM30" s="11">
-        <v>0</v>
-      </c>
       <c r="DN30" s="11">
+        <v>0</v>
+      </c>
+      <c r="DO30" s="11">
         <v>15</v>
       </c>
-      <c r="DO30" s="11">
-        <v>0</v>
-      </c>
-      <c r="DP30" s="11">
+      <c r="DX30" s="11">
+        <v>1</v>
+      </c>
+      <c r="DY30" s="11">
         <v>15</v>
       </c>
-      <c r="DY30" s="11">
-        <v>1</v>
-      </c>
-      <c r="DZ30" s="11">
-        <v>15</v>
+      <c r="EF30" t="s">
+        <v>161</v>
       </c>
       <c r="EG30" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="EH30" t="s">
-        <v>161</v>
-      </c>
-      <c r="EI30" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="31" spans="1:139" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:138" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C31" s="16">
         <v>2024</v>
@@ -6520,19 +6496,19 @@
         <v>1</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G31" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H31" s="9">
         <v>45</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="K31" s="9">
         <v>104</v>
@@ -6550,7 +6526,7 @@
         <v>12</v>
       </c>
       <c r="P31" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Q31" s="11">
         <v>0</v>
@@ -6589,25 +6565,25 @@
         <v>5</v>
       </c>
       <c r="AC31" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AD31" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AE31" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="AD31" s="12" t="s">
+      <c r="AF31" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AG31" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AH31" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="AE31" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="AF31" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AG31" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AH31" s="12" t="s">
-        <v>156</v>
-      </c>
       <c r="AI31" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AJ31" s="11">
         <v>4</v>
@@ -6625,16 +6601,16 @@
         <v>7.2</v>
       </c>
       <c r="AO31" s="11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AP31" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ31" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR31" s="11" t="s">
         <v>132</v>
-      </c>
-      <c r="AQ31" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="AR31" s="11" t="s">
-        <v>133</v>
       </c>
       <c r="AS31" s="11">
         <v>4</v>
@@ -6652,16 +6628,16 @@
         <v>2.6</v>
       </c>
       <c r="AX31" s="11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AY31" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AZ31" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BA31" s="11" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="BB31" s="11">
         <v>4</v>
@@ -6679,72 +6655,72 @@
         <v>10.6</v>
       </c>
       <c r="BG31" s="11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="BH31" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BI31" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
+      </c>
+      <c r="DB31" s="11">
+        <v>2</v>
       </c>
       <c r="DC31" s="11">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="DD31" s="11">
+        <v>0</v>
+      </c>
+      <c r="DE31" s="11">
         <v>5</v>
       </c>
-      <c r="DE31" s="11">
-        <v>0</v>
-      </c>
-      <c r="DF31" s="11">
+      <c r="DH31" s="11">
+        <v>1</v>
+      </c>
+      <c r="DI31" s="11">
         <v>5</v>
       </c>
-      <c r="DI31" s="11">
-        <v>1</v>
-      </c>
       <c r="DJ31" s="11">
+        <v>0</v>
+      </c>
+      <c r="DK31" s="11">
         <v>5</v>
       </c>
-      <c r="DK31" s="11">
-        <v>0</v>
-      </c>
       <c r="DL31" s="11">
+        <v>0</v>
+      </c>
+      <c r="DM31" s="11">
         <v>5</v>
       </c>
-      <c r="DM31" s="11">
-        <v>0</v>
-      </c>
       <c r="DN31" s="11">
+        <v>0</v>
+      </c>
+      <c r="DO31" s="11">
         <v>5</v>
       </c>
-      <c r="DO31" s="11">
-        <v>0</v>
-      </c>
-      <c r="DP31" s="11">
+      <c r="DX31" s="11">
+        <v>0</v>
+      </c>
+      <c r="DY31" s="11">
         <v>5</v>
       </c>
-      <c r="DY31" s="11">
-        <v>0</v>
-      </c>
-      <c r="DZ31" s="11">
-        <v>5</v>
-      </c>
-      <c r="EG31" s="13" t="s">
-        <v>260</v>
+      <c r="EF31" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="EG31" t="s">
+        <v>160</v>
       </c>
       <c r="EH31" t="s">
-        <v>161</v>
-      </c>
-      <c r="EI31" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="32" spans="1:139" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:138" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
+        <v>253</v>
+      </c>
+      <c r="B32" s="10" t="s">
         <v>256</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>259</v>
       </c>
       <c r="C32" s="16">
         <v>2024</v>
@@ -6753,19 +6729,19 @@
         <v>1</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G32" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H32" s="9">
         <v>150</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="K32" s="9">
         <v>104</v>
@@ -6783,7 +6759,7 @@
         <v>12</v>
       </c>
       <c r="P32" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Q32" s="11">
         <v>4</v>
@@ -6822,25 +6798,25 @@
         <v>30</v>
       </c>
       <c r="AC32" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AD32" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AE32" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="AD32" s="12" t="s">
+      <c r="AF32" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AG32" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AH32" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="AE32" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="AF32" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AG32" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AH32" s="12" t="s">
-        <v>156</v>
-      </c>
       <c r="AI32" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AJ32" s="11">
         <v>20</v>
@@ -6858,16 +6834,16 @@
         <v>11.1</v>
       </c>
       <c r="AO32" s="11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AP32" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ32" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR32" s="11" t="s">
         <v>132</v>
-      </c>
-      <c r="AQ32" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="AR32" s="11" t="s">
-        <v>133</v>
       </c>
       <c r="AS32" s="11">
         <v>20</v>
@@ -6885,16 +6861,16 @@
         <v>4.7</v>
       </c>
       <c r="AX32" s="11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AY32" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AZ32" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BA32" s="11" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="BB32" s="11">
         <v>19</v>
@@ -6912,72 +6888,72 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="BG32" s="11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="BH32" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BI32" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
+      </c>
+      <c r="DB32" s="11">
+        <v>8</v>
       </c>
       <c r="DC32" s="11">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="DD32" s="11">
+        <v>1</v>
+      </c>
+      <c r="DE32" s="11">
         <v>30</v>
       </c>
-      <c r="DE32" s="11">
+      <c r="DH32" s="11">
+        <v>2</v>
+      </c>
+      <c r="DI32" s="11">
+        <v>30</v>
+      </c>
+      <c r="DJ32" s="11">
         <v>1</v>
       </c>
-      <c r="DF32" s="11">
+      <c r="DK32" s="11">
         <v>30</v>
       </c>
-      <c r="DI32" s="11">
+      <c r="DL32" s="11">
+        <v>1</v>
+      </c>
+      <c r="DM32" s="11">
+        <v>30</v>
+      </c>
+      <c r="DN32" s="11">
         <v>2</v>
       </c>
-      <c r="DJ32" s="11">
+      <c r="DO32" s="11">
         <v>30</v>
       </c>
-      <c r="DK32" s="11">
-        <v>1</v>
-      </c>
-      <c r="DL32" s="11">
+      <c r="DX32" s="11">
+        <v>0</v>
+      </c>
+      <c r="DY32" s="11">
         <v>30</v>
       </c>
-      <c r="DM32" s="11">
-        <v>1</v>
-      </c>
-      <c r="DN32" s="11">
-        <v>30</v>
-      </c>
-      <c r="DO32" s="11">
-        <v>2</v>
-      </c>
-      <c r="DP32" s="11">
-        <v>30</v>
-      </c>
-      <c r="DY32" s="11">
-        <v>0</v>
-      </c>
-      <c r="DZ32" s="11">
-        <v>30</v>
-      </c>
-      <c r="EG32" s="13" t="s">
-        <v>260</v>
+      <c r="EF32" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="EG32" t="s">
+        <v>160</v>
       </c>
       <c r="EH32" t="s">
-        <v>161</v>
-      </c>
-      <c r="EI32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="33" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C33" s="16">
         <v>2024</v>
@@ -6986,19 +6962,19 @@
         <v>1</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G33" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H33" s="9">
         <v>300</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="K33" s="9">
         <v>104</v>
@@ -7016,7 +6992,7 @@
         <v>12</v>
       </c>
       <c r="P33" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Q33" s="11">
         <v>3</v>
@@ -7055,25 +7031,25 @@
         <v>32</v>
       </c>
       <c r="AC33" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AD33" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AE33" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="AD33" s="12" t="s">
+      <c r="AF33" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AG33" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AH33" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="AE33" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="AF33" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AG33" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AH33" s="12" t="s">
-        <v>156</v>
-      </c>
       <c r="AI33" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AJ33" s="11">
         <v>21</v>
@@ -7091,16 +7067,16 @@
         <v>11.3</v>
       </c>
       <c r="AO33" s="11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AP33" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ33" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR33" s="11" t="s">
         <v>132</v>
-      </c>
-      <c r="AQ33" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="AR33" s="11" t="s">
-        <v>133</v>
       </c>
       <c r="AS33" s="11">
         <v>21</v>
@@ -7118,16 +7094,16 @@
         <v>4.3</v>
       </c>
       <c r="AX33" s="11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AY33" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AZ33" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BA33" s="11" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="BB33" s="11">
         <v>21</v>
@@ -7145,72 +7121,72 @@
         <v>12.4</v>
       </c>
       <c r="BG33" s="11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="BH33" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BI33" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
+      </c>
+      <c r="DB33" s="11">
+        <v>4</v>
       </c>
       <c r="DC33" s="11">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="DD33" s="11">
+        <v>0</v>
+      </c>
+      <c r="DE33" s="11">
         <v>32</v>
       </c>
-      <c r="DE33" s="11">
-        <v>0</v>
-      </c>
-      <c r="DF33" s="11">
+      <c r="DH33" s="11">
+        <v>1</v>
+      </c>
+      <c r="DI33" s="11">
         <v>32</v>
       </c>
-      <c r="DI33" s="11">
+      <c r="DJ33" s="11">
+        <v>0</v>
+      </c>
+      <c r="DK33" s="11">
+        <v>32</v>
+      </c>
+      <c r="DL33" s="11">
         <v>1</v>
       </c>
-      <c r="DJ33" s="11">
+      <c r="DM33" s="11">
         <v>32</v>
       </c>
-      <c r="DK33" s="11">
-        <v>0</v>
-      </c>
-      <c r="DL33" s="11">
+      <c r="DN33" s="11">
+        <v>0</v>
+      </c>
+      <c r="DO33" s="11">
         <v>32</v>
       </c>
-      <c r="DM33" s="11">
-        <v>1</v>
-      </c>
-      <c r="DN33" s="11">
+      <c r="DX33" s="11">
+        <v>0</v>
+      </c>
+      <c r="DY33" s="11">
         <v>32</v>
       </c>
-      <c r="DO33" s="11">
-        <v>0</v>
-      </c>
-      <c r="DP33" s="11">
-        <v>32</v>
-      </c>
-      <c r="DY33" s="11">
-        <v>0</v>
-      </c>
-      <c r="DZ33" s="11">
-        <v>32</v>
-      </c>
-      <c r="EG33" s="13" t="s">
-        <v>260</v>
+      <c r="EF33" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="EG33" t="s">
+        <v>160</v>
       </c>
       <c r="EH33" t="s">
-        <v>161</v>
-      </c>
-      <c r="EI33" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="34" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C34" s="16">
         <v>2024</v>
@@ -7219,19 +7195,19 @@
         <v>1</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G34" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H34" s="9">
         <v>0</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="K34" s="9">
         <v>104</v>
@@ -7249,7 +7225,7 @@
         <v>12</v>
       </c>
       <c r="P34" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Q34" s="11">
         <v>4</v>
@@ -7288,25 +7264,25 @@
         <v>37</v>
       </c>
       <c r="AC34" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AD34" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AE34" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="AD34" s="12" t="s">
+      <c r="AF34" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AG34" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AH34" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="AE34" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="AF34" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AG34" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AH34" s="12" t="s">
-        <v>156</v>
-      </c>
       <c r="AI34" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AJ34" s="11">
         <v>31</v>
@@ -7324,16 +7300,16 @@
         <v>12.2</v>
       </c>
       <c r="AO34" s="11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AP34" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ34" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR34" s="11" t="s">
         <v>132</v>
-      </c>
-      <c r="AQ34" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="AR34" s="11" t="s">
-        <v>133</v>
       </c>
       <c r="AS34" s="11">
         <v>31</v>
@@ -7351,16 +7327,16 @@
         <v>4.5</v>
       </c>
       <c r="AX34" s="11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AY34" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AZ34" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BA34" s="11" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="BB34" s="11">
         <v>31</v>
@@ -7378,96 +7354,96 @@
         <v>13.4</v>
       </c>
       <c r="BG34" s="11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="BH34" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BI34" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
+      </c>
+      <c r="DB34" s="11">
+        <v>9</v>
       </c>
       <c r="DC34" s="11">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="DD34" s="11">
+        <v>0</v>
+      </c>
+      <c r="DE34" s="11">
         <v>37</v>
       </c>
-      <c r="DE34" s="11">
-        <v>0</v>
-      </c>
-      <c r="DF34" s="11">
+      <c r="DH34" s="11">
+        <v>1</v>
+      </c>
+      <c r="DI34" s="11">
         <v>37</v>
       </c>
-      <c r="DI34" s="11">
-        <v>1</v>
-      </c>
       <c r="DJ34" s="11">
+        <v>3</v>
+      </c>
+      <c r="DK34" s="11">
         <v>37</v>
       </c>
-      <c r="DK34" s="11">
-        <v>3</v>
-      </c>
       <c r="DL34" s="11">
+        <v>2</v>
+      </c>
+      <c r="DM34" s="11">
         <v>37</v>
       </c>
-      <c r="DM34" s="11">
+      <c r="DN34" s="11">
         <v>2</v>
       </c>
-      <c r="DN34" s="11">
+      <c r="DO34" s="11">
         <v>37</v>
       </c>
-      <c r="DO34" s="11">
-        <v>2</v>
-      </c>
-      <c r="DP34" s="11">
+      <c r="DX34" s="11">
+        <v>0</v>
+      </c>
+      <c r="DY34" s="11">
         <v>37</v>
       </c>
-      <c r="DY34" s="11">
-        <v>0</v>
-      </c>
-      <c r="DZ34" s="11">
-        <v>37</v>
-      </c>
-      <c r="EG34" s="13" t="s">
-        <v>253</v>
+      <c r="EF34" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="EG34" t="s">
+        <v>160</v>
       </c>
       <c r="EH34" t="s">
-        <v>161</v>
-      </c>
-      <c r="EI34" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="35" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A35" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C35" s="16">
         <v>2024</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E35" s="10">
         <v>1</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H35" s="9">
         <v>150</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K35" s="11">
         <v>31</v>
@@ -7485,7 +7461,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="P35" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Y35" s="11">
         <v>0</v>
@@ -7499,73 +7475,73 @@
       <c r="AB35" s="11">
         <v>29</v>
       </c>
+      <c r="DB35" s="10">
+        <v>20</v>
+      </c>
       <c r="DC35" s="10">
-        <v>20</v>
-      </c>
-      <c r="DD35" s="10">
         <v>29</v>
       </c>
+      <c r="DH35" s="10">
+        <v>4</v>
+      </c>
       <c r="DI35" s="10">
+        <v>29</v>
+      </c>
+      <c r="DL35" s="10">
+        <v>8</v>
+      </c>
+      <c r="DM35" s="10">
+        <v>29</v>
+      </c>
+      <c r="DN35" s="10">
         <v>4</v>
       </c>
-      <c r="DJ35" s="10">
+      <c r="DO35" s="10">
         <v>29</v>
       </c>
-      <c r="DM35" s="10">
-        <v>8</v>
-      </c>
-      <c r="DN35" s="10">
+      <c r="DR35" s="11">
+        <v>0</v>
+      </c>
+      <c r="DS35" s="11">
         <v>29</v>
       </c>
-      <c r="DO35" s="10">
-        <v>4</v>
-      </c>
-      <c r="DP35" s="10">
-        <v>29</v>
-      </c>
-      <c r="DS35" s="11">
-        <v>0</v>
-      </c>
-      <c r="DT35" s="11">
-        <v>29</v>
-      </c>
-      <c r="EG35" s="14" t="s">
-        <v>138</v>
+      <c r="EF35" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="EG35" s="11" t="s">
+        <v>217</v>
       </c>
       <c r="EH35" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="EI35" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="36" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C36" s="16">
         <v>2024</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E36" s="10">
         <v>1</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K36" s="11">
         <v>31</v>
@@ -7583,7 +7559,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="P36" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Y36" s="11">
         <v>0</v>
@@ -7597,44 +7573,44 @@
       <c r="AB36" s="11">
         <v>26</v>
       </c>
+      <c r="DB36" s="10">
+        <v>9</v>
+      </c>
       <c r="DC36" s="10">
-        <v>9</v>
-      </c>
-      <c r="DD36" s="10">
         <v>26</v>
       </c>
+      <c r="DH36" s="10">
+        <v>0</v>
+      </c>
       <c r="DI36" s="10">
-        <v>0</v>
-      </c>
-      <c r="DJ36" s="10">
         <v>26</v>
       </c>
+      <c r="DL36" s="10">
+        <v>0</v>
+      </c>
       <c r="DM36" s="10">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="DN36" s="10">
+        <v>1</v>
+      </c>
+      <c r="DO36" s="10">
         <v>26</v>
       </c>
-      <c r="DO36" s="10">
-        <v>1</v>
-      </c>
-      <c r="DP36" s="10">
+      <c r="DR36" s="11">
+        <v>0</v>
+      </c>
+      <c r="DS36" s="11">
         <v>26</v>
       </c>
-      <c r="DS36" s="11">
-        <v>0</v>
-      </c>
-      <c r="DT36" s="11">
-        <v>26</v>
-      </c>
-      <c r="EG36" s="14" t="s">
-        <v>212</v>
+      <c r="EF36" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="EG36" s="11" t="s">
+        <v>217</v>
       </c>
       <c r="EH36" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="EI36" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
